--- a/resources/M626/spc_cpk_detail.xlsx
+++ b/resources/M626/spc_cpk_detail.xlsx
@@ -2453,10 +2453,10 @@
         <v>46190.79921296296</v>
       </c>
       <c r="J49">
-        <v>1.79803160965662</v>
+        <v>1.798031609656621</v>
       </c>
       <c r="K49">
-        <v>1.79803160965662</v>
+        <v>1.798031609656621</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2523,10 +2523,10 @@
         <v>46190.79921296296</v>
       </c>
       <c r="J51">
-        <v>1.79803160965662</v>
+        <v>1.798031609656621</v>
       </c>
       <c r="K51">
-        <v>1.79803160965662</v>
+        <v>1.798031609656621</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2593,10 +2593,10 @@
         <v>46174.95023148148</v>
       </c>
       <c r="J53">
-        <v>1.590105054959452</v>
+        <v>1.590105054959451</v>
       </c>
       <c r="K53">
-        <v>1.590105054959452</v>
+        <v>1.590105054959451</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2663,10 +2663,10 @@
         <v>46174.95023148148</v>
       </c>
       <c r="J55">
-        <v>1.590105054959452</v>
+        <v>1.590105054959451</v>
       </c>
       <c r="K55">
-        <v>1.590105054959452</v>
+        <v>1.590105054959451</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -4308,10 +4308,10 @@
         <v>46183.9808912037</v>
       </c>
       <c r="J102">
-        <v>1.549513971338663</v>
+        <v>1.549513971338662</v>
       </c>
       <c r="K102">
-        <v>1.549513971338663</v>
+        <v>1.549513971338662</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -4413,10 +4413,10 @@
         <v>46183.9808912037</v>
       </c>
       <c r="J105">
-        <v>1.549513971338663</v>
+        <v>1.549513971338662</v>
       </c>
       <c r="K105">
-        <v>1.549513971338663</v>
+        <v>1.549513971338662</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -4588,10 +4588,10 @@
         <v>46192.85702546296</v>
       </c>
       <c r="J110">
-        <v>1.645824622288867</v>
+        <v>1.645824622288868</v>
       </c>
       <c r="K110">
-        <v>1.645824622288867</v>
+        <v>1.645824622288868</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4693,10 +4693,10 @@
         <v>46192.85702546296</v>
       </c>
       <c r="J113">
-        <v>1.645824622288867</v>
+        <v>1.645824622288868</v>
       </c>
       <c r="K113">
-        <v>1.645824622288867</v>
+        <v>1.645824622288868</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -5568,10 +5568,10 @@
         <v>46193.32494212963</v>
       </c>
       <c r="J138">
-        <v>1.555309054413917</v>
+        <v>1.555309054413916</v>
       </c>
       <c r="K138">
-        <v>1.555309054413917</v>
+        <v>1.555309054413916</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -5638,10 +5638,10 @@
         <v>46193.32494212963</v>
       </c>
       <c r="J140">
-        <v>1.555309054413917</v>
+        <v>1.555309054413916</v>
       </c>
       <c r="K140">
-        <v>1.555309054413917</v>
+        <v>1.555309054413916</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -7738,10 +7738,10 @@
         <v>46187.56212962963</v>
       </c>
       <c r="J200">
-        <v>3.124467950828476</v>
+        <v>3.124467950828475</v>
       </c>
       <c r="K200">
-        <v>3.124467950828476</v>
+        <v>3.124467950828475</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -8088,10 +8088,10 @@
         <v>46174.81490740741</v>
       </c>
       <c r="J210">
-        <v>1.404885478325891</v>
+        <v>1.40488547832589</v>
       </c>
       <c r="K210">
-        <v>1.404885478325891</v>
+        <v>1.40488547832589</v>
       </c>
     </row>
     <row r="211" spans="1:11">
@@ -8158,10 +8158,10 @@
         <v>46176.85328703704</v>
       </c>
       <c r="J212">
-        <v>2.491685225867085</v>
+        <v>2.491685225867086</v>
       </c>
       <c r="K212">
-        <v>2.491685225867085</v>
+        <v>2.491685225867086</v>
       </c>
     </row>
     <row r="213" spans="1:11">
@@ -8998,10 +8998,10 @@
         <v>46181.9305787037</v>
       </c>
       <c r="J236">
-        <v>3.210399360801442</v>
+        <v>3.210399360801443</v>
       </c>
       <c r="K236">
-        <v>3.210399360801442</v>
+        <v>3.210399360801443</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -9068,10 +9068,10 @@
         <v>46183.84069444444</v>
       </c>
       <c r="J238">
-        <v>3.473296225913956</v>
+        <v>3.473296225913955</v>
       </c>
       <c r="K238">
-        <v>3.473296225913956</v>
+        <v>3.473296225913955</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -9348,10 +9348,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J246">
-        <v>1.978853450574098</v>
+        <v>1.978853450574099</v>
       </c>
       <c r="K246">
-        <v>1.978853450574098</v>
+        <v>1.978853450574099</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -10223,10 +10223,10 @@
         <v>46175.98122685185</v>
       </c>
       <c r="J271">
-        <v>4.758989576321312</v>
+        <v>4.758989576321313</v>
       </c>
       <c r="K271">
-        <v>4.758989576321312</v>
+        <v>4.758989576321313</v>
       </c>
     </row>
     <row r="272" spans="1:11">
@@ -10468,10 +10468,10 @@
         <v>46183.84069444444</v>
       </c>
       <c r="J278">
-        <v>4.448379640390239</v>
+        <v>4.44837964039024</v>
       </c>
       <c r="K278">
-        <v>4.448379640390239</v>
+        <v>4.44837964039024</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -10643,10 +10643,10 @@
         <v>46206.61196759259</v>
       </c>
       <c r="J283">
-        <v>4.135629187404322</v>
+        <v>4.135629187404321</v>
       </c>
       <c r="K283">
-        <v>4.135629187404322</v>
+        <v>4.135629187404321</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -10818,10 +10818,10 @@
         <v>46183.84069444444</v>
       </c>
       <c r="J288">
-        <v>2.13289939599393</v>
+        <v>2.132899395993929</v>
       </c>
       <c r="K288">
-        <v>2.13289939599393</v>
+        <v>2.132899395993929</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -11658,10 +11658,10 @@
         <v>46176.85328703704</v>
       </c>
       <c r="J312">
-        <v>4.803816545084888</v>
+        <v>4.803816545084887</v>
       </c>
       <c r="K312">
-        <v>4.803816545084888</v>
+        <v>4.803816545084887</v>
       </c>
     </row>
     <row r="313" spans="1:11">
@@ -11693,10 +11693,10 @@
         <v>46177.79724537037</v>
       </c>
       <c r="J313">
-        <v>4.467542831680012</v>
+        <v>4.46754283168001</v>
       </c>
       <c r="K313">
-        <v>4.467542831680012</v>
+        <v>4.46754283168001</v>
       </c>
     </row>
     <row r="314" spans="1:11">
@@ -11728,10 +11728,10 @@
         <v>46179.84344907408</v>
       </c>
       <c r="J314">
-        <v>3.964382272784407</v>
+        <v>3.964382272784406</v>
       </c>
       <c r="K314">
-        <v>3.964382272784407</v>
+        <v>3.964382272784406</v>
       </c>
     </row>
     <row r="315" spans="1:11">
@@ -11868,10 +11868,10 @@
         <v>46183.84069444444</v>
       </c>
       <c r="J318">
-        <v>4.871659350617075</v>
+        <v>4.871659350617077</v>
       </c>
       <c r="K318">
-        <v>4.871659350617075</v>
+        <v>4.871659350617077</v>
       </c>
     </row>
     <row r="319" spans="1:11">
@@ -11973,10 +11973,10 @@
         <v>46204.48143518518</v>
       </c>
       <c r="J321">
-        <v>5.26681464999815</v>
+        <v>5.266814649998149</v>
       </c>
       <c r="K321">
-        <v>5.26681464999815</v>
+        <v>5.266814649998149</v>
       </c>
     </row>
     <row r="322" spans="1:11">
@@ -12043,10 +12043,10 @@
         <v>46206.61196759259</v>
       </c>
       <c r="J323">
-        <v>4.173442424252206</v>
+        <v>4.173442424252205</v>
       </c>
       <c r="K323">
-        <v>4.173442424252206</v>
+        <v>4.173442424252205</v>
       </c>
     </row>
     <row r="324" spans="1:11">
@@ -12288,10 +12288,10 @@
         <v>46174.94690972222</v>
       </c>
       <c r="J330">
-        <v>7.589856339205542</v>
+        <v>7.589856339205541</v>
       </c>
       <c r="K330">
-        <v>7.589856339205542</v>
+        <v>7.589856339205541</v>
       </c>
     </row>
     <row r="331" spans="1:11">
@@ -12568,10 +12568,10 @@
         <v>46182.96581018518</v>
       </c>
       <c r="J338">
-        <v>7.297598095080794</v>
+        <v>7.297598095080793</v>
       </c>
       <c r="K338">
-        <v>7.297598095080794</v>
+        <v>7.297598095080793</v>
       </c>
     </row>
     <row r="339" spans="1:11">
@@ -12743,10 +12743,10 @@
         <v>46205.74840277778</v>
       </c>
       <c r="J343">
-        <v>5.002728289455207</v>
+        <v>5.002728289455206</v>
       </c>
       <c r="K343">
-        <v>5.002728289455207</v>
+        <v>5.002728289455206</v>
       </c>
     </row>
     <row r="344" spans="1:11">
@@ -12778,10 +12778,10 @@
         <v>46206.6680324074</v>
       </c>
       <c r="J344">
-        <v>6.868403886344061</v>
+        <v>6.868403886344059</v>
       </c>
       <c r="K344">
-        <v>6.868403886344061</v>
+        <v>6.868403886344059</v>
       </c>
     </row>
     <row r="345" spans="1:11">
@@ -13303,10 +13303,10 @@
         <v>46182.96581018518</v>
       </c>
       <c r="J359">
-        <v>1.89253499115685</v>
+        <v>1.892534991156849</v>
       </c>
       <c r="K359">
-        <v>1.89253499115685</v>
+        <v>1.892534991156849</v>
       </c>
     </row>
     <row r="360" spans="1:11">
@@ -13898,10 +13898,10 @@
         <v>46178.9991087963</v>
       </c>
       <c r="J376">
-        <v>9.17126760773591</v>
+        <v>9.171267607735908</v>
       </c>
       <c r="K376">
-        <v>9.17126760773591</v>
+        <v>9.171267607735908</v>
       </c>
     </row>
     <row r="377" spans="1:11">
@@ -14878,10 +14878,10 @@
         <v>46203.9103125</v>
       </c>
       <c r="J404">
-        <v>3.291970900992209</v>
+        <v>3.29197090099221</v>
       </c>
       <c r="K404">
-        <v>3.291970900992209</v>
+        <v>3.29197090099221</v>
       </c>
     </row>
     <row r="405" spans="1:11">
@@ -14983,10 +14983,10 @@
         <v>46206.66802083333</v>
       </c>
       <c r="J407">
-        <v>3.078750218465228</v>
+        <v>3.078750218465227</v>
       </c>
       <c r="K407">
-        <v>3.078750218465228</v>
+        <v>3.078750218465227</v>
       </c>
     </row>
     <row r="408" spans="1:11">
@@ -15963,10 +15963,10 @@
         <v>46175.97753472222</v>
       </c>
       <c r="J435">
-        <v>1.592917901067202</v>
+        <v>1.592917901067203</v>
       </c>
       <c r="K435">
-        <v>1.592917901067202</v>
+        <v>1.592917901067203</v>
       </c>
     </row>
     <row r="436" spans="1:11">
@@ -16348,10 +16348,10 @@
         <v>46184.68292824074</v>
       </c>
       <c r="J446">
-        <v>1.455965109029581</v>
+        <v>1.45596510902958</v>
       </c>
       <c r="K446">
-        <v>1.455965109029581</v>
+        <v>1.45596510902958</v>
       </c>
     </row>
     <row r="447" spans="1:11">
@@ -16978,10 +16978,10 @@
         <v>46182.60833333333</v>
       </c>
       <c r="J464">
-        <v>1.435540527273854</v>
+        <v>1.435540527273855</v>
       </c>
       <c r="K464">
-        <v>1.435540527273854</v>
+        <v>1.435540527273855</v>
       </c>
     </row>
     <row r="465" spans="1:11">
@@ -17118,10 +17118,10 @@
         <v>46207.23274305555</v>
       </c>
       <c r="J468">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="K468">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
     </row>
     <row r="469" spans="1:11">
@@ -17223,10 +17223,10 @@
         <v>46207.23274305555</v>
       </c>
       <c r="J471">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="K471">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
     </row>
     <row r="472" spans="1:11">
@@ -17328,10 +17328,10 @@
         <v>46182.60833333333</v>
       </c>
       <c r="J474">
-        <v>2.502953491729751</v>
+        <v>2.502953491729752</v>
       </c>
       <c r="K474">
-        <v>2.502953491729751</v>
+        <v>2.502953491729752</v>
       </c>
     </row>
     <row r="475" spans="1:11">
@@ -17398,10 +17398,10 @@
         <v>46207.23274305555</v>
       </c>
       <c r="J476">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="K476">
-        <v>1.990153757485191</v>
+        <v>1.990153757485192</v>
       </c>
     </row>
     <row r="477" spans="1:11">
@@ -17853,10 +17853,10 @@
         <v>46180.393125</v>
       </c>
       <c r="J489">
-        <v>2.837561306383012</v>
+        <v>2.837561306383013</v>
       </c>
       <c r="K489">
-        <v>2.837561306383012</v>
+        <v>2.837561306383013</v>
       </c>
     </row>
     <row r="490" spans="1:11">
@@ -17888,10 +17888,10 @@
         <v>46186.12424768518</v>
       </c>
       <c r="J490">
-        <v>2.874004779757791</v>
+        <v>2.87400477975779</v>
       </c>
       <c r="K490">
-        <v>2.874004779757791</v>
+        <v>2.87400477975779</v>
       </c>
     </row>
     <row r="491" spans="1:11">
@@ -18098,10 +18098,10 @@
         <v>46183.154375</v>
       </c>
       <c r="J496">
-        <v>2.645265851074052</v>
+        <v>2.645265851074053</v>
       </c>
       <c r="K496">
-        <v>2.645265851074052</v>
+        <v>2.645265851074053</v>
       </c>
     </row>
     <row r="497" spans="1:11">
@@ -18273,10 +18273,10 @@
         <v>46180.0500462963</v>
       </c>
       <c r="J501">
-        <v>1.54546360424908</v>
+        <v>1.545463604249081</v>
       </c>
       <c r="K501">
-        <v>1.54546360424908</v>
+        <v>1.545463604249081</v>
       </c>
     </row>
     <row r="502" spans="1:11">
@@ -18378,10 +18378,10 @@
         <v>46180.0500462963</v>
       </c>
       <c r="J504">
-        <v>1.54546360424908</v>
+        <v>1.545463604249081</v>
       </c>
       <c r="K504">
-        <v>1.54546360424908</v>
+        <v>1.545463604249081</v>
       </c>
     </row>
     <row r="505" spans="1:11">
@@ -18553,10 +18553,10 @@
         <v>46210.61064814815</v>
       </c>
       <c r="J509">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="K509">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
     </row>
     <row r="510" spans="1:11">
@@ -18658,10 +18658,10 @@
         <v>46210.61064814815</v>
       </c>
       <c r="J512">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="K512">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
     </row>
     <row r="513" spans="1:11">
@@ -18798,10 +18798,10 @@
         <v>46210.61064814815</v>
       </c>
       <c r="J516">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="K516">
-        <v>2.268675743319091</v>
+        <v>2.26867574331909</v>
       </c>
     </row>
     <row r="517" spans="1:11">
@@ -19568,10 +19568,10 @@
         <v>46180.01618055555</v>
       </c>
       <c r="J538">
-        <v>1.61466438302404</v>
+        <v>1.614664383024041</v>
       </c>
       <c r="K538">
-        <v>1.61466438302404</v>
+        <v>1.614664383024041</v>
       </c>
     </row>
     <row r="539" spans="1:11">
@@ -20548,10 +20548,10 @@
         <v>46214.6469212963</v>
       </c>
       <c r="J566">
-        <v>6.264830902260329</v>
+        <v>6.26483090226033</v>
       </c>
       <c r="K566">
-        <v>6.264830902260329</v>
+        <v>6.26483090226033</v>
       </c>
     </row>
     <row r="567" spans="1:11">
@@ -20653,10 +20653,10 @@
         <v>46177.85769675926</v>
       </c>
       <c r="J569">
-        <v>1.259005601685604</v>
+        <v>1.259005601685605</v>
       </c>
       <c r="K569">
-        <v>1.259005601685604</v>
+        <v>1.259005601685605</v>
       </c>
     </row>
     <row r="570" spans="1:11">
@@ -20758,10 +20758,10 @@
         <v>46177.85769675926</v>
       </c>
       <c r="J572">
-        <v>1.259005601685604</v>
+        <v>1.259005601685605</v>
       </c>
       <c r="K572">
-        <v>1.259005601685604</v>
+        <v>1.259005601685605</v>
       </c>
     </row>
     <row r="573" spans="1:11">

--- a/resources/M626/spc_cpk_detail.xlsx
+++ b/resources/M626/spc_cpk_detail.xlsx
@@ -847,10 +847,10 @@
         <v>46230.72840277778</v>
       </c>
       <c r="J2">
-        <v>1.783316479126941</v>
+        <v>1.783316479126942</v>
       </c>
       <c r="K2">
-        <v>1.783316479126941</v>
+        <v>1.783316479126942</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1232,10 +1232,10 @@
         <v>46227.67450231482</v>
       </c>
       <c r="J13">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
       <c r="K13">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1302,10 +1302,10 @@
         <v>46227.67450231482</v>
       </c>
       <c r="J15">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
       <c r="K15">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2002,10 +2002,10 @@
         <v>46184.60541666667</v>
       </c>
       <c r="J35">
-        <v>1.60078530526187</v>
+        <v>1.600785305261871</v>
       </c>
       <c r="K35">
-        <v>1.60078530526187</v>
+        <v>1.600785305261871</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2912,10 +2912,10 @@
         <v>46191.72753472222</v>
       </c>
       <c r="J61">
-        <v>1.522077432746186</v>
+        <v>1.522077432746187</v>
       </c>
       <c r="K61">
-        <v>1.522077432746186</v>
+        <v>1.522077432746187</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -3017,10 +3017,10 @@
         <v>46191.72753472222</v>
       </c>
       <c r="J64">
-        <v>2.621307957323171</v>
+        <v>2.621307957323172</v>
       </c>
       <c r="K64">
-        <v>2.621307957323171</v>
+        <v>2.621307957323172</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3857,10 +3857,10 @@
         <v>46191.74302083333</v>
       </c>
       <c r="J88">
-        <v>1.7003357646203</v>
+        <v>1.700335764620301</v>
       </c>
       <c r="K88">
-        <v>1.7003357646203</v>
+        <v>1.700335764620301</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -3927,10 +3927,10 @@
         <v>46191.74302083333</v>
       </c>
       <c r="J90">
-        <v>1.7003357646203</v>
+        <v>1.700335764620301</v>
       </c>
       <c r="K90">
-        <v>1.7003357646203</v>
+        <v>1.700335764620301</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -4977,10 +4977,10 @@
         <v>46183.9808912037</v>
       </c>
       <c r="J120">
-        <v>1.549513971338662</v>
+        <v>1.549513971338663</v>
       </c>
       <c r="K120">
-        <v>1.549513971338662</v>
+        <v>1.549513971338663</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -5082,10 +5082,10 @@
         <v>46183.9808912037</v>
       </c>
       <c r="J123">
-        <v>1.549513971338662</v>
+        <v>1.549513971338663</v>
       </c>
       <c r="K123">
-        <v>1.549513971338662</v>
+        <v>1.549513971338663</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -5187,10 +5187,10 @@
         <v>46175.90008101852</v>
       </c>
       <c r="J126">
-        <v>1.907125675379762</v>
+        <v>1.907125675379763</v>
       </c>
       <c r="K126">
-        <v>1.907125675379762</v>
+        <v>1.907125675379763</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -5292,10 +5292,10 @@
         <v>46175.90008101852</v>
       </c>
       <c r="J129">
-        <v>1.907125675379762</v>
+        <v>1.907125675379763</v>
       </c>
       <c r="K129">
-        <v>1.907125675379762</v>
+        <v>1.907125675379763</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7077,10 +7077,10 @@
         <v>46176.74538194444</v>
       </c>
       <c r="J180">
-        <v>2.75604192212703</v>
+        <v>2.756041922127031</v>
       </c>
       <c r="K180">
-        <v>2.75604192212703</v>
+        <v>2.756041922127031</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -7147,10 +7147,10 @@
         <v>46176.74538194444</v>
       </c>
       <c r="J182">
-        <v>2.75604192212703</v>
+        <v>2.756041922127031</v>
       </c>
       <c r="K182">
-        <v>2.75604192212703</v>
+        <v>2.756041922127031</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -7917,10 +7917,10 @@
         <v>46195.25652777778</v>
       </c>
       <c r="J204">
-        <v>1.943192331634054</v>
+        <v>1.943192331634055</v>
       </c>
       <c r="K204">
-        <v>1.943192331634054</v>
+        <v>1.943192331634055</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -8022,10 +8022,10 @@
         <v>46195.25652777778</v>
       </c>
       <c r="J207">
-        <v>1.943192331634054</v>
+        <v>1.943192331634055</v>
       </c>
       <c r="K207">
-        <v>1.943192331634054</v>
+        <v>1.943192331634055</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -8407,10 +8407,10 @@
         <v>46187.56212962963</v>
       </c>
       <c r="J218">
-        <v>3.124467950828476</v>
+        <v>3.124467950828475</v>
       </c>
       <c r="K218">
-        <v>3.124467950828476</v>
+        <v>3.124467950828475</v>
       </c>
     </row>
     <row r="219" spans="1:11">
@@ -9492,10 +9492,10 @@
         <v>46179.84344907408</v>
       </c>
       <c r="J249">
-        <v>2.522126018705464</v>
+        <v>2.522126018705463</v>
       </c>
       <c r="K249">
-        <v>2.522126018705464</v>
+        <v>2.522126018705463</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -10332,10 +10332,10 @@
         <v>46183.84069444444</v>
       </c>
       <c r="J273">
-        <v>3.473296225913956</v>
+        <v>3.473296225913955</v>
       </c>
       <c r="K273">
-        <v>3.473296225913956</v>
+        <v>3.473296225913955</v>
       </c>
     </row>
     <row r="274" spans="1:11">
@@ -10612,10 +10612,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J281">
-        <v>1.978853450574098</v>
+        <v>1.978853450574099</v>
       </c>
       <c r="K281">
-        <v>1.978853450574098</v>
+        <v>1.978853450574099</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -11277,10 +11277,10 @@
         <v>46203.94153935185</v>
       </c>
       <c r="J300">
-        <v>4.318794497148454</v>
+        <v>4.318794497148455</v>
       </c>
       <c r="K300">
-        <v>4.318794497148454</v>
+        <v>4.318794497148455</v>
       </c>
     </row>
     <row r="301" spans="1:11">
@@ -11487,10 +11487,10 @@
         <v>46175.98122685185</v>
       </c>
       <c r="J306">
-        <v>4.758989576321312</v>
+        <v>4.758989576321313</v>
       </c>
       <c r="K306">
-        <v>4.758989576321312</v>
+        <v>4.758989576321313</v>
       </c>
     </row>
     <row r="307" spans="1:11">
@@ -11977,10 +11977,10 @@
         <v>46203.94153935185</v>
       </c>
       <c r="J320">
-        <v>1.800625414669072</v>
+        <v>1.800625414669073</v>
       </c>
       <c r="K320">
-        <v>1.800625414669072</v>
+        <v>1.800625414669073</v>
       </c>
     </row>
     <row r="321" spans="1:11">
@@ -12047,10 +12047,10 @@
         <v>46180.88512731482</v>
       </c>
       <c r="J322">
-        <v>1.979439625650374</v>
+        <v>1.979439625650375</v>
       </c>
       <c r="K322">
-        <v>1.979439625650374</v>
+        <v>1.979439625650375</v>
       </c>
     </row>
     <row r="323" spans="1:11">
@@ -12082,10 +12082,10 @@
         <v>46183.84069444444</v>
       </c>
       <c r="J323">
-        <v>2.13289939599393</v>
+        <v>2.132899395993929</v>
       </c>
       <c r="K323">
-        <v>2.13289939599393</v>
+        <v>2.132899395993929</v>
       </c>
     </row>
     <row r="324" spans="1:11">
@@ -12572,10 +12572,10 @@
         <v>46205.77965277778</v>
       </c>
       <c r="J337">
-        <v>2.013994314162455</v>
+        <v>2.013994314162456</v>
       </c>
       <c r="K337">
-        <v>2.013994314162455</v>
+        <v>2.013994314162456</v>
       </c>
     </row>
     <row r="338" spans="1:11">
@@ -13447,10 +13447,10 @@
         <v>46180.86203703703</v>
       </c>
       <c r="J362">
-        <v>6.429124494415824</v>
+        <v>6.429124494415822</v>
       </c>
       <c r="K362">
-        <v>6.429124494415824</v>
+        <v>6.429124494415822</v>
       </c>
     </row>
     <row r="363" spans="1:11">
@@ -13552,10 +13552,10 @@
         <v>46174.94690972222</v>
       </c>
       <c r="J365">
-        <v>7.589856339205541</v>
+        <v>7.589856339205542</v>
       </c>
       <c r="K365">
-        <v>7.589856339205541</v>
+        <v>7.589856339205542</v>
       </c>
     </row>
     <row r="366" spans="1:11">
@@ -13937,10 +13937,10 @@
         <v>46203.91032407407</v>
       </c>
       <c r="J376">
-        <v>6.710504533536466</v>
+        <v>6.710504533536464</v>
       </c>
       <c r="K376">
-        <v>6.710504533536466</v>
+        <v>6.710504533536464</v>
       </c>
     </row>
     <row r="377" spans="1:11">
@@ -13972,10 +13972,10 @@
         <v>46204.45003472222</v>
       </c>
       <c r="J377">
-        <v>5.867270425380308</v>
+        <v>5.867270425380309</v>
       </c>
       <c r="K377">
-        <v>5.867270425380308</v>
+        <v>5.867270425380309</v>
       </c>
     </row>
     <row r="378" spans="1:11">
@@ -14007,10 +14007,10 @@
         <v>46205.74840277778</v>
       </c>
       <c r="J378">
-        <v>5.002728289455207</v>
+        <v>5.002728289455206</v>
       </c>
       <c r="K378">
-        <v>5.002728289455207</v>
+        <v>5.002728289455206</v>
       </c>
     </row>
     <row r="379" spans="1:11">
@@ -14322,10 +14322,10 @@
         <v>46175.99747685185</v>
       </c>
       <c r="J387">
-        <v>2.340653643500904</v>
+        <v>2.340653643500905</v>
       </c>
       <c r="K387">
-        <v>2.340653643500904</v>
+        <v>2.340653643500905</v>
       </c>
     </row>
     <row r="388" spans="1:11">
@@ -14392,10 +14392,10 @@
         <v>46177.64208333333</v>
       </c>
       <c r="J389">
-        <v>2.292708884922962</v>
+        <v>2.292708884922961</v>
       </c>
       <c r="K389">
-        <v>2.292708884922962</v>
+        <v>2.292708884922961</v>
       </c>
     </row>
     <row r="390" spans="1:11">
@@ -14987,10 +14987,10 @@
         <v>46207.33239583333</v>
       </c>
       <c r="J406">
-        <v>5.126003391461595</v>
+        <v>5.126003391461596</v>
       </c>
       <c r="K406">
-        <v>5.126003391461595</v>
+        <v>5.126003391461596</v>
       </c>
     </row>
     <row r="407" spans="1:11">
@@ -15127,10 +15127,10 @@
         <v>46177.64207175926</v>
       </c>
       <c r="J410">
-        <v>4.123180426844028</v>
+        <v>4.123180426844027</v>
       </c>
       <c r="K410">
-        <v>4.123180426844028</v>
+        <v>4.123180426844027</v>
       </c>
     </row>
     <row r="411" spans="1:11">
@@ -15617,10 +15617,10 @@
         <v>46207.33239583333</v>
       </c>
       <c r="J424">
-        <v>3.09010363110375</v>
+        <v>3.090103631103751</v>
       </c>
       <c r="K424">
-        <v>3.09010363110375</v>
+        <v>3.090103631103751</v>
       </c>
     </row>
     <row r="425" spans="1:11">
@@ -15897,10 +15897,10 @@
         <v>46178.9991087963</v>
       </c>
       <c r="J432">
-        <v>4.502718598162202</v>
+        <v>4.502718598162201</v>
       </c>
       <c r="K432">
-        <v>4.502718598162202</v>
+        <v>4.502718598162201</v>
       </c>
     </row>
     <row r="433" spans="1:11">
@@ -16527,10 +16527,10 @@
         <v>46175.99745370371</v>
       </c>
       <c r="J450">
-        <v>3.041971341412588</v>
+        <v>3.041971341412587</v>
       </c>
       <c r="K450">
-        <v>3.041971341412588</v>
+        <v>3.041971341412587</v>
       </c>
     </row>
     <row r="451" spans="1:11">
@@ -17332,10 +17332,10 @@
         <v>46181.3690625</v>
       </c>
       <c r="J473">
-        <v>1.842809472020499</v>
+        <v>1.8428094720205</v>
       </c>
       <c r="K473">
-        <v>1.842809472020499</v>
+        <v>1.8428094720205</v>
       </c>
     </row>
     <row r="474" spans="1:11">
@@ -18592,10 +18592,10 @@
         <v>46182.60833333333</v>
       </c>
       <c r="J509">
-        <v>2.502953491729752</v>
+        <v>2.502953491729751</v>
       </c>
       <c r="K509">
-        <v>2.502953491729752</v>
+        <v>2.502953491729751</v>
       </c>
     </row>
     <row r="510" spans="1:11">
@@ -19362,10 +19362,10 @@
         <v>46183.154375</v>
       </c>
       <c r="J531">
-        <v>2.645265851074053</v>
+        <v>2.645265851074052</v>
       </c>
       <c r="K531">
-        <v>2.645265851074053</v>
+        <v>2.645265851074052</v>
       </c>
     </row>
     <row r="532" spans="1:11">
@@ -19712,10 +19712,10 @@
         <v>46186.45532407407</v>
       </c>
       <c r="J541">
-        <v>1.551775839628436</v>
+        <v>1.551775839628435</v>
       </c>
       <c r="K541">
-        <v>1.551775839628436</v>
+        <v>1.551775839628435</v>
       </c>
     </row>
     <row r="542" spans="1:11">
@@ -20832,10 +20832,10 @@
         <v>46180.01618055555</v>
       </c>
       <c r="J573">
-        <v>1.614664383024041</v>
+        <v>1.61466438302404</v>
       </c>
       <c r="K573">
-        <v>1.614664383024041</v>
+        <v>1.61466438302404</v>
       </c>
     </row>
     <row r="574" spans="1:11">
@@ -21392,10 +21392,10 @@
         <v>46184.93923611111</v>
       </c>
       <c r="J589">
-        <v>4.690250207612562</v>
+        <v>4.690250207612561</v>
       </c>
       <c r="K589">
-        <v>4.690250207612562</v>
+        <v>4.690250207612561</v>
       </c>
     </row>
     <row r="590" spans="1:11">
@@ -21427,10 +21427,10 @@
         <v>46214.6469212963</v>
       </c>
       <c r="J590">
-        <v>4.481333785255095</v>
+        <v>4.481333785255094</v>
       </c>
       <c r="K590">
-        <v>4.481333785255095</v>
+        <v>4.481333785255094</v>
       </c>
     </row>
     <row r="591" spans="1:11">
@@ -21532,10 +21532,10 @@
         <v>46214.6469212963</v>
       </c>
       <c r="J593">
-        <v>4.481333785255095</v>
+        <v>4.481333785255094</v>
       </c>
       <c r="K593">
-        <v>4.481333785255095</v>
+        <v>4.481333785255094</v>
       </c>
     </row>
     <row r="594" spans="1:11">
@@ -21672,10 +21672,10 @@
         <v>46181.84710648148</v>
       </c>
       <c r="J597">
-        <v>4.999309442133119</v>
+        <v>4.99930944213312</v>
       </c>
       <c r="K597">
-        <v>4.999309442133119</v>
+        <v>4.99930944213312</v>
       </c>
     </row>
     <row r="598" spans="1:11">
@@ -21812,10 +21812,10 @@
         <v>46214.6469212963</v>
       </c>
       <c r="J601">
-        <v>6.264830902260329</v>
+        <v>6.26483090226033</v>
       </c>
       <c r="K601">
-        <v>6.264830902260329</v>
+        <v>6.26483090226033</v>
       </c>
     </row>
     <row r="602" spans="1:11">

--- a/resources/M626/spc_cpk_detail.xlsx
+++ b/resources/M626/spc_cpk_detail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="93">
   <si>
     <t>prod_code</t>
   </si>
@@ -94,6 +94,12 @@
     <t>13260</t>
   </si>
   <si>
+    <t>14450</t>
+  </si>
+  <si>
+    <t>14650</t>
+  </si>
+  <si>
     <t>1K140</t>
   </si>
   <si>
@@ -242,6 +248,12 @@
   </si>
   <si>
     <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-W32</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
   </si>
   <si>
     <t>2026-07-25</t>
@@ -642,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K190"/>
+  <dimension ref="A1:K208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -691,13 +703,13 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>101</v>
@@ -709,10 +721,10 @@
         <v>46230.72840277778</v>
       </c>
       <c r="J2">
-        <v>1.783316479126942</v>
+        <v>1.783316479126941</v>
       </c>
       <c r="K2">
-        <v>1.783316479126942</v>
+        <v>1.783316479126941</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -726,13 +738,13 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>203</v>
@@ -761,13 +773,13 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>204</v>
@@ -796,13 +808,13 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>313</v>
@@ -831,13 +843,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>314</v>
@@ -866,13 +878,13 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>101</v>
@@ -901,13 +913,13 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>203</v>
@@ -936,13 +948,13 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>204</v>
@@ -971,13 +983,13 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G10">
         <v>313</v>
@@ -1006,13 +1018,13 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G11">
         <v>314</v>
@@ -1041,13 +1053,13 @@
         <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>101</v>
@@ -1076,13 +1088,13 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G13">
         <v>102</v>
@@ -1111,13 +1123,13 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>203</v>
@@ -1129,10 +1141,10 @@
         <v>46227.67450231482</v>
       </c>
       <c r="J14">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
       <c r="K14">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1146,13 +1158,13 @@
         <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>204</v>
@@ -1181,13 +1193,13 @@
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G16">
         <v>311</v>
@@ -1199,10 +1211,10 @@
         <v>46227.67450231482</v>
       </c>
       <c r="J16">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
       <c r="K16">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1216,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G17">
         <v>314</v>
@@ -1251,13 +1263,13 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G18">
         <v>320</v>
@@ -1286,13 +1298,13 @@
         <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G19">
         <v>101</v>
@@ -1321,13 +1333,13 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G20">
         <v>204</v>
@@ -1356,13 +1368,13 @@
         <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G21">
         <v>315</v>
@@ -1391,13 +1403,13 @@
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G22">
         <v>101</v>
@@ -1409,10 +1421,10 @@
         <v>46231.02504629629</v>
       </c>
       <c r="J22">
-        <v>1.28058509223836</v>
+        <v>1.355116472981333</v>
       </c>
       <c r="K22">
-        <v>1.28058509223836</v>
+        <v>1.355116472981333</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1426,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G23">
         <v>204</v>
@@ -1444,10 +1456,10 @@
         <v>46231.02504629629</v>
       </c>
       <c r="J23">
-        <v>1.28058509223836</v>
+        <v>1.355116472981333</v>
       </c>
       <c r="K23">
-        <v>1.28058509223836</v>
+        <v>1.355116472981333</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1461,13 +1473,13 @@
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G24">
         <v>314</v>
@@ -1479,10 +1491,10 @@
         <v>46230.99207175926</v>
       </c>
       <c r="J24">
-        <v>2.066936758739828</v>
+        <v>2.066936758739829</v>
       </c>
       <c r="K24">
-        <v>2.066936758739828</v>
+        <v>2.066936758739829</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1496,13 +1508,13 @@
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G25">
         <v>315</v>
@@ -1514,10 +1526,10 @@
         <v>46231.02504629629</v>
       </c>
       <c r="J25">
-        <v>1.193277640863846</v>
+        <v>1.27303707618806</v>
       </c>
       <c r="K25">
-        <v>1.193277640863846</v>
+        <v>1.27303707618806</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1531,13 +1543,13 @@
         <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E26" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F26" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G26">
         <v>101</v>
@@ -1566,13 +1578,13 @@
         <v>19</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G27">
         <v>204</v>
@@ -1601,13 +1613,13 @@
         <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G28">
         <v>316</v>
@@ -1636,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F29" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G29">
         <v>101</v>
@@ -1671,13 +1683,13 @@
         <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G30">
         <v>204</v>
@@ -1706,13 +1718,13 @@
         <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F31" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G31">
         <v>316</v>
@@ -1741,13 +1753,13 @@
         <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G32">
         <v>101</v>
@@ -1776,13 +1788,13 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G33">
         <v>204</v>
@@ -1811,13 +1823,13 @@
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E34" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F34" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G34">
         <v>317</v>
@@ -1846,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G35">
         <v>101</v>
@@ -1881,13 +1893,13 @@
         <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E36" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G36">
         <v>204</v>
@@ -1916,13 +1928,13 @@
         <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G37">
         <v>317</v>
@@ -1951,13 +1963,13 @@
         <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G38">
         <v>318</v>
@@ -1986,13 +1998,13 @@
         <v>22</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E39" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F39" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G39">
         <v>101</v>
@@ -2021,13 +2033,13 @@
         <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F40" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G40">
         <v>204</v>
@@ -2056,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F41" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G41">
         <v>318</v>
@@ -2091,13 +2103,13 @@
         <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F42" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G42">
         <v>101</v>
@@ -2126,13 +2138,13 @@
         <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F43" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G43">
         <v>204</v>
@@ -2161,13 +2173,13 @@
         <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F44" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G44">
         <v>317</v>
@@ -2196,13 +2208,13 @@
         <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E45" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F45" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G45">
         <v>101</v>
@@ -2231,13 +2243,13 @@
         <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E46" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F46" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G46">
         <v>204</v>
@@ -2266,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E47" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F47" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G47">
         <v>317</v>
@@ -2301,13 +2313,13 @@
         <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E48" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F48" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G48">
         <v>102</v>
@@ -2336,13 +2348,13 @@
         <v>24</v>
       </c>
       <c r="D49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E49" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F49" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G49">
         <v>204</v>
@@ -2371,13 +2383,13 @@
         <v>24</v>
       </c>
       <c r="D50" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E50" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G50">
         <v>320</v>
@@ -2406,13 +2418,13 @@
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E51" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F51" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G51">
         <v>102</v>
@@ -2441,13 +2453,13 @@
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E52" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F52" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G52">
         <v>204</v>
@@ -2476,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E53" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F53" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G53">
         <v>319</v>
@@ -2511,13 +2523,13 @@
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E54" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F54" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G54">
         <v>320</v>
@@ -2529,10 +2541,10 @@
         <v>46236.78883101852</v>
       </c>
       <c r="J54">
-        <v>1.508683391254824</v>
+        <v>1.508683391254823</v>
       </c>
       <c r="K54">
-        <v>1.508683391254824</v>
+        <v>1.508683391254823</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2546,28 +2558,28 @@
         <v>26</v>
       </c>
       <c r="D55" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E55" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F55" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G55">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H55" s="2">
-        <v>46230.2861574074</v>
+        <v>46237.24145833333</v>
       </c>
       <c r="I55" s="2">
-        <v>46230.31240740741</v>
+        <v>46237.2683912037</v>
       </c>
       <c r="J55">
-        <v>1.738575531706706</v>
+        <v>1.683802188892685</v>
       </c>
       <c r="K55">
-        <v>1.738575531706706</v>
+        <v>1.683802188892685</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2581,28 +2593,28 @@
         <v>26</v>
       </c>
       <c r="D56" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E56" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F56" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="G56">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H56" s="2">
-        <v>46230.2861574074</v>
+        <v>46237.24145833333</v>
       </c>
       <c r="I56" s="2">
-        <v>46230.31240740741</v>
+        <v>46237.2683912037</v>
       </c>
       <c r="J56">
-        <v>1.738575531706706</v>
+        <v>1.683802188892685</v>
       </c>
       <c r="K56">
-        <v>1.738575531706706</v>
+        <v>1.683802188892685</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2616,28 +2628,28 @@
         <v>26</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E57" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F57" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="G57">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="H57" s="2">
-        <v>46230.2861574074</v>
+        <v>46237.24145833333</v>
       </c>
       <c r="I57" s="2">
-        <v>46230.31240740741</v>
+        <v>46237.2683912037</v>
       </c>
       <c r="J57">
-        <v>1.738575531706706</v>
+        <v>1.683802188892685</v>
       </c>
       <c r="K57">
-        <v>1.738575531706706</v>
+        <v>1.683802188892685</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2651,28 +2663,28 @@
         <v>26</v>
       </c>
       <c r="D58" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E58" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F58" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G58">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H58" s="2">
-        <v>46230.2861574074</v>
+        <v>46237.24145833333</v>
       </c>
       <c r="I58" s="2">
-        <v>46230.31240740741</v>
+        <v>46237.2683912037</v>
       </c>
       <c r="J58">
-        <v>3.101191863272319</v>
+        <v>1.510318836283279</v>
       </c>
       <c r="K58">
-        <v>3.101191863272319</v>
+        <v>1.510318836283279</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2686,28 +2698,28 @@
         <v>26</v>
       </c>
       <c r="D59" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E59" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F59" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="G59">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H59" s="2">
-        <v>46230.2861574074</v>
+        <v>46237.24145833333</v>
       </c>
       <c r="I59" s="2">
-        <v>46230.31240740741</v>
+        <v>46237.2683912037</v>
       </c>
       <c r="J59">
-        <v>3.101191863272319</v>
+        <v>1.510318836283279</v>
       </c>
       <c r="K59">
-        <v>3.101191863272319</v>
+        <v>1.510318836283279</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -2721,28 +2733,28 @@
         <v>26</v>
       </c>
       <c r="D60" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E60" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F60" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="G60">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="H60" s="2">
-        <v>46230.2861574074</v>
+        <v>46237.24145833333</v>
       </c>
       <c r="I60" s="2">
-        <v>46230.31240740741</v>
+        <v>46237.2683912037</v>
       </c>
       <c r="J60">
-        <v>3.101191863272319</v>
+        <v>1.510318836283279</v>
       </c>
       <c r="K60">
-        <v>3.101191863272319</v>
+        <v>1.510318836283279</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2756,28 +2768,28 @@
         <v>27</v>
       </c>
       <c r="D61" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E61" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F61" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G61">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H61" s="2">
-        <v>46230.18972222223</v>
+        <v>46237.97503472222</v>
       </c>
       <c r="I61" s="2">
-        <v>46230.22109953704</v>
+        <v>46237.98892361111</v>
       </c>
       <c r="J61">
-        <v>1.945260761826871</v>
+        <v>1.396842844879743</v>
       </c>
       <c r="K61">
-        <v>1.945260761826871</v>
+        <v>1.396842844879743</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -2791,28 +2803,28 @@
         <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E62" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F62" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="G62">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H62" s="2">
-        <v>46230.18972222223</v>
+        <v>46237.97503472222</v>
       </c>
       <c r="I62" s="2">
-        <v>46230.22109953704</v>
+        <v>46237.98892361111</v>
       </c>
       <c r="J62">
-        <v>1.945260761826871</v>
+        <v>1.396842844879743</v>
       </c>
       <c r="K62">
-        <v>1.945260761826871</v>
+        <v>1.396842844879743</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -2826,28 +2838,28 @@
         <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E63" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F63" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="G63">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="H63" s="2">
-        <v>46230.18972222223</v>
+        <v>46237.97503472222</v>
       </c>
       <c r="I63" s="2">
-        <v>46230.22109953704</v>
+        <v>46237.98892361111</v>
       </c>
       <c r="J63">
-        <v>1.945260761826871</v>
+        <v>1.396842844879743</v>
       </c>
       <c r="K63">
-        <v>1.945260761826871</v>
+        <v>1.396842844879743</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -2858,31 +2870,31 @@
         <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D64" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E64" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G64">
         <v>101</v>
       </c>
       <c r="H64" s="2">
-        <v>46230.18972222223</v>
+        <v>46230.2861574074</v>
       </c>
       <c r="I64" s="2">
-        <v>46230.22109953704</v>
+        <v>46230.31240740741</v>
       </c>
       <c r="J64">
-        <v>2.199635212306361</v>
+        <v>1.738575531706706</v>
       </c>
       <c r="K64">
-        <v>2.199635212306361</v>
+        <v>1.738575531706706</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -2893,31 +2905,31 @@
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D65" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E65" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F65" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G65">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="H65" s="2">
-        <v>46230.18972222223</v>
+        <v>46237.71436342593</v>
       </c>
       <c r="I65" s="2">
-        <v>46230.22109953704</v>
+        <v>46237.74181712963</v>
       </c>
       <c r="J65">
-        <v>2.199635212306361</v>
+        <v>1.855801837443607</v>
       </c>
       <c r="K65">
-        <v>2.199635212306361</v>
+        <v>1.855801837443607</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -2928,31 +2940,31 @@
         <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D66" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F66" t="s">
         <v>67</v>
       </c>
       <c r="G66">
-        <v>314</v>
+        <v>204</v>
       </c>
       <c r="H66" s="2">
-        <v>46230.18972222223</v>
+        <v>46230.2861574074</v>
       </c>
       <c r="I66" s="2">
-        <v>46230.22109953704</v>
+        <v>46230.31240740741</v>
       </c>
       <c r="J66">
-        <v>2.199635212306361</v>
+        <v>1.738575531706706</v>
       </c>
       <c r="K66">
-        <v>2.199635212306361</v>
+        <v>1.738575531706706</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -2966,28 +2978,28 @@
         <v>28</v>
       </c>
       <c r="D67" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E67" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F67" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G67">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="H67" s="2">
-        <v>46228.93714120371</v>
+        <v>46237.71436342593</v>
       </c>
       <c r="I67" s="2">
-        <v>46230.8632175926</v>
+        <v>46237.74181712963</v>
       </c>
       <c r="J67">
-        <v>2.196097348217624</v>
+        <v>1.855801837443607</v>
       </c>
       <c r="K67">
-        <v>2.196097348217624</v>
+        <v>1.855801837443607</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3001,28 +3013,28 @@
         <v>28</v>
       </c>
       <c r="D68" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E68" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F68" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G68">
-        <v>203</v>
+        <v>314</v>
       </c>
       <c r="H68" s="2">
-        <v>46228.93714120371</v>
+        <v>46230.2861574074</v>
       </c>
       <c r="I68" s="2">
-        <v>46228.94255787037</v>
+        <v>46230.31240740741</v>
       </c>
       <c r="J68">
-        <v>2.423426358493773</v>
+        <v>1.738575531706706</v>
       </c>
       <c r="K68">
-        <v>2.423426358493773</v>
+        <v>1.738575531706706</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3036,28 +3048,28 @@
         <v>28</v>
       </c>
       <c r="D69" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E69" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F69" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="G69">
-        <v>204</v>
+        <v>321</v>
       </c>
       <c r="H69" s="2">
-        <v>46230.7833912037</v>
+        <v>46237.71436342593</v>
       </c>
       <c r="I69" s="2">
-        <v>46230.8632175926</v>
+        <v>46237.74181712963</v>
       </c>
       <c r="J69">
-        <v>2.081802506775104</v>
+        <v>1.855801837443607</v>
       </c>
       <c r="K69">
-        <v>2.081802506775104</v>
+        <v>1.855801837443607</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3071,28 +3083,28 @@
         <v>28</v>
       </c>
       <c r="D70" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E70" t="s">
         <v>62</v>
       </c>
       <c r="F70" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G70">
-        <v>312</v>
+        <v>101</v>
       </c>
       <c r="H70" s="2">
-        <v>46228.93714120371</v>
+        <v>46230.2861574074</v>
       </c>
       <c r="I70" s="2">
-        <v>46228.94255787037</v>
+        <v>46230.31240740741</v>
       </c>
       <c r="J70">
-        <v>2.423426358493773</v>
+        <v>3.101191863272319</v>
       </c>
       <c r="K70">
-        <v>2.423426358493773</v>
+        <v>3.101191863272319</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3106,28 +3118,28 @@
         <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E71" t="s">
         <v>62</v>
       </c>
       <c r="F71" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G71">
-        <v>314</v>
+        <v>102</v>
       </c>
       <c r="H71" s="2">
-        <v>46230.7833912037</v>
+        <v>46237.71436342593</v>
       </c>
       <c r="I71" s="2">
-        <v>46230.8632175926</v>
+        <v>46237.74181712963</v>
       </c>
       <c r="J71">
-        <v>2.081802506775104</v>
+        <v>3.785401835683741</v>
       </c>
       <c r="K71">
-        <v>2.081802506775104</v>
+        <v>3.785401835683741</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -3135,34 +3147,34 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E72" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F72" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G72">
-        <v>101</v>
+        <v>204</v>
       </c>
       <c r="H72" s="2">
-        <v>46204.07336805556</v>
+        <v>46230.2861574074</v>
       </c>
       <c r="I72" s="2">
-        <v>46207.44892361111</v>
+        <v>46230.31240740741</v>
       </c>
       <c r="J72">
-        <v>2.371006469700295</v>
+        <v>3.101191863272319</v>
       </c>
       <c r="K72">
-        <v>2.371006469700295</v>
+        <v>3.101191863272319</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -3170,34 +3182,34 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D73" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E73" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F73" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G73">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H73" s="2">
-        <v>46204.07336805556</v>
+        <v>46237.71436342593</v>
       </c>
       <c r="I73" s="2">
-        <v>46207.44892361111</v>
+        <v>46237.74181712963</v>
       </c>
       <c r="J73">
-        <v>2.371006469700295</v>
+        <v>3.785401835683741</v>
       </c>
       <c r="K73">
-        <v>2.371006469700295</v>
+        <v>3.785401835683741</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -3205,34 +3217,34 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D74" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E74" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F74" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G74">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="H74" s="2">
-        <v>46204.07336805556</v>
+        <v>46230.2861574074</v>
       </c>
       <c r="I74" s="2">
-        <v>46204.48143518518</v>
+        <v>46230.31240740741</v>
       </c>
       <c r="J74">
-        <v>2.67285918915458</v>
+        <v>3.101191863272319</v>
       </c>
       <c r="K74">
-        <v>2.67285918915458</v>
+        <v>3.101191863272319</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -3240,34 +3252,34 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D75" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E75" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F75" t="s">
         <v>79</v>
       </c>
       <c r="G75">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="H75" s="2">
-        <v>46205.1180787037</v>
+        <v>46237.71436342593</v>
       </c>
       <c r="I75" s="2">
-        <v>46205.77965277778</v>
+        <v>46237.74181712963</v>
       </c>
       <c r="J75">
-        <v>2.353225669816371</v>
+        <v>3.785401835683741</v>
       </c>
       <c r="K75">
-        <v>2.353225669816371</v>
+        <v>3.785401835683741</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3275,34 +3287,34 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C76" t="s">
         <v>29</v>
       </c>
       <c r="D76" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E76" t="s">
         <v>62</v>
       </c>
       <c r="F76" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G76">
-        <v>303</v>
+        <v>101</v>
       </c>
       <c r="H76" s="2">
-        <v>46206.14086805555</v>
+        <v>46230.18972222223</v>
       </c>
       <c r="I76" s="2">
-        <v>46206.61196759259</v>
+        <v>46230.22109953704</v>
       </c>
       <c r="J76">
-        <v>2.508648197643544</v>
+        <v>1.945260761826871</v>
       </c>
       <c r="K76">
-        <v>2.508648197643544</v>
+        <v>1.945260761826871</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -3310,34 +3322,34 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C77" t="s">
         <v>29</v>
       </c>
       <c r="D77" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E77" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F77" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G77">
-        <v>304</v>
+        <v>204</v>
       </c>
       <c r="H77" s="2">
-        <v>46207.44892361111</v>
+        <v>46230.18972222223</v>
       </c>
       <c r="I77" s="2">
-        <v>46207.44892361111</v>
+        <v>46230.22109953704</v>
       </c>
       <c r="J77">
-        <v>2.804250769071384</v>
+        <v>1.945260761826871</v>
       </c>
       <c r="K77">
-        <v>2.804250769071384</v>
+        <v>1.945260761826871</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -3345,34 +3357,34 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C78" t="s">
         <v>29</v>
       </c>
       <c r="D78" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E78" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F78" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G78">
-        <v>101</v>
+        <v>314</v>
       </c>
       <c r="H78" s="2">
-        <v>46204.07336805556</v>
+        <v>46230.18972222223</v>
       </c>
       <c r="I78" s="2">
-        <v>46207.44892361111</v>
+        <v>46230.22109953704</v>
       </c>
       <c r="J78">
-        <v>2.547008202307568</v>
+        <v>1.945260761826871</v>
       </c>
       <c r="K78">
-        <v>2.547008202307568</v>
+        <v>1.945260761826871</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3380,34 +3392,34 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
         <v>29</v>
       </c>
       <c r="D79" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E79" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F79" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="G79">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="H79" s="2">
-        <v>46204.07336805556</v>
+        <v>46230.18972222223</v>
       </c>
       <c r="I79" s="2">
-        <v>46207.44892361111</v>
+        <v>46230.22109953704</v>
       </c>
       <c r="J79">
-        <v>2.547008202307568</v>
+        <v>2.199635212306361</v>
       </c>
       <c r="K79">
-        <v>2.547008202307568</v>
+        <v>2.199635212306361</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -3415,34 +3427,34 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C80" t="s">
         <v>29</v>
       </c>
       <c r="D80" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E80" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F80" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G80">
-        <v>301</v>
+        <v>204</v>
       </c>
       <c r="H80" s="2">
-        <v>46204.07336805556</v>
+        <v>46230.18972222223</v>
       </c>
       <c r="I80" s="2">
-        <v>46204.48143518518</v>
+        <v>46230.22109953704</v>
       </c>
       <c r="J80">
-        <v>2.412718096413623</v>
+        <v>2.199635212306361</v>
       </c>
       <c r="K80">
-        <v>2.412718096413623</v>
+        <v>2.199635212306361</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3450,34 +3462,34 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
         <v>29</v>
       </c>
       <c r="D81" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E81" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F81" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G81">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="H81" s="2">
-        <v>46205.1180787037</v>
+        <v>46230.18972222223</v>
       </c>
       <c r="I81" s="2">
-        <v>46205.77965277778</v>
+        <v>46230.22109953704</v>
       </c>
       <c r="J81">
-        <v>2.757348303637914</v>
+        <v>2.199635212306361</v>
       </c>
       <c r="K81">
-        <v>2.757348303637914</v>
+        <v>2.199635212306361</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3485,10 +3497,10 @@
         <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D82" t="s">
         <v>50</v>
@@ -3497,22 +3509,22 @@
         <v>62</v>
       </c>
       <c r="F82" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G82">
-        <v>303</v>
+        <v>101</v>
       </c>
       <c r="H82" s="2">
-        <v>46206.14086805555</v>
+        <v>46228.93714120371</v>
       </c>
       <c r="I82" s="2">
-        <v>46206.61196759259</v>
+        <v>46230.8632175926</v>
       </c>
       <c r="J82">
-        <v>2.597410666279916</v>
+        <v>2.196097348217624</v>
       </c>
       <c r="K82">
-        <v>2.597410666279916</v>
+        <v>2.196097348217624</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3520,10 +3532,10 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D83" t="s">
         <v>50</v>
@@ -3532,22 +3544,22 @@
         <v>62</v>
       </c>
       <c r="F83" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="G83">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="H83" s="2">
-        <v>46207.44892361111</v>
+        <v>46237.39759259259</v>
       </c>
       <c r="I83" s="2">
-        <v>46207.44892361111</v>
+        <v>46237.40302083334</v>
       </c>
       <c r="J83">
-        <v>2.360111806550468</v>
+        <v>1.699841446416682</v>
       </c>
       <c r="K83">
-        <v>2.360111806550468</v>
+        <v>1.699841446416682</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3555,34 +3567,34 @@
         <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D84" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E84" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F84" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G84">
-        <v>101</v>
+        <v>203</v>
       </c>
       <c r="H84" s="2">
-        <v>46204.07336805556</v>
+        <v>46228.93714120371</v>
       </c>
       <c r="I84" s="2">
-        <v>46207.44892361111</v>
+        <v>46228.94255787037</v>
       </c>
       <c r="J84">
-        <v>1.978853450574098</v>
+        <v>2.423426358493773</v>
       </c>
       <c r="K84">
-        <v>1.978853450574098</v>
+        <v>2.423426358493773</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3590,34 +3602,34 @@
         <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D85" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E85" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F85" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="G85">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H85" s="2">
-        <v>46204.07336805556</v>
+        <v>46230.7833912037</v>
       </c>
       <c r="I85" s="2">
-        <v>46207.44892361111</v>
+        <v>46230.8632175926</v>
       </c>
       <c r="J85">
-        <v>1.978853450574098</v>
+        <v>2.081802506775104</v>
       </c>
       <c r="K85">
-        <v>1.978853450574098</v>
+        <v>2.081802506775104</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -3625,34 +3637,34 @@
         <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D86" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E86" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F86" t="s">
         <v>78</v>
       </c>
       <c r="G86">
-        <v>301</v>
+        <v>205</v>
       </c>
       <c r="H86" s="2">
-        <v>46204.07336805556</v>
+        <v>46237.39759259259</v>
       </c>
       <c r="I86" s="2">
-        <v>46204.48143518518</v>
+        <v>46237.40302083334</v>
       </c>
       <c r="J86">
-        <v>1.973329619411917</v>
+        <v>1.699841446416682</v>
       </c>
       <c r="K86">
-        <v>1.973329619411917</v>
+        <v>1.699841446416682</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -3660,34 +3672,34 @@
         <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D87" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E87" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G87">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="H87" s="2">
-        <v>46205.1180787037</v>
+        <v>46228.93714120371</v>
       </c>
       <c r="I87" s="2">
-        <v>46205.77965277778</v>
+        <v>46228.94255787037</v>
       </c>
       <c r="J87">
-        <v>1.985517299327437</v>
+        <v>2.423426358493773</v>
       </c>
       <c r="K87">
-        <v>1.985517299327437</v>
+        <v>2.423426358493773</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -3695,34 +3707,34 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D88" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E88" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F88" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G88">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="H88" s="2">
-        <v>46206.14086805555</v>
+        <v>46230.7833912037</v>
       </c>
       <c r="I88" s="2">
-        <v>46206.61196759259</v>
+        <v>46230.8632175926</v>
       </c>
       <c r="J88">
-        <v>2.071364974880914</v>
+        <v>2.081802506775104</v>
       </c>
       <c r="K88">
-        <v>2.071364974880914</v>
+        <v>2.081802506775104</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -3730,34 +3742,34 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D89" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E89" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F89" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G89">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="H89" s="2">
-        <v>46207.44892361111</v>
+        <v>46237.39759259259</v>
       </c>
       <c r="I89" s="2">
-        <v>46207.44892361111</v>
+        <v>46237.40302083334</v>
       </c>
       <c r="J89">
-        <v>2.492949601255396</v>
+        <v>1.699841446416682</v>
       </c>
       <c r="K89">
-        <v>2.492949601255396</v>
+        <v>1.699841446416682</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3768,16 +3780,16 @@
         <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E90" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F90" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G90">
         <v>101</v>
@@ -3789,10 +3801,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J90">
-        <v>4.029575489602267</v>
+        <v>2.371006469700295</v>
       </c>
       <c r="K90">
-        <v>4.029575489602267</v>
+        <v>2.371006469700295</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -3803,16 +3815,16 @@
         <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E91" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F91" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G91">
         <v>201</v>
@@ -3824,10 +3836,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J91">
-        <v>4.029575489602267</v>
+        <v>2.371006469700295</v>
       </c>
       <c r="K91">
-        <v>4.029575489602267</v>
+        <v>2.371006469700295</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -3838,16 +3850,16 @@
         <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E92" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F92" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G92">
         <v>301</v>
@@ -3859,10 +3871,10 @@
         <v>46204.48143518518</v>
       </c>
       <c r="J92">
-        <v>4.091144075229255</v>
+        <v>2.67285918915458</v>
       </c>
       <c r="K92">
-        <v>4.091144075229255</v>
+        <v>2.67285918915458</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -3873,16 +3885,16 @@
         <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E93" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F93" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G93">
         <v>302</v>
@@ -3894,10 +3906,10 @@
         <v>46205.77965277778</v>
       </c>
       <c r="J93">
-        <v>3.974895780538705</v>
+        <v>2.353225669816371</v>
       </c>
       <c r="K93">
-        <v>3.974895780538705</v>
+        <v>2.353225669816371</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -3908,16 +3920,16 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E94" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F94" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G94">
         <v>303</v>
@@ -3929,10 +3941,10 @@
         <v>46206.61196759259</v>
       </c>
       <c r="J94">
-        <v>4.135629187404322</v>
+        <v>2.508648197643544</v>
       </c>
       <c r="K94">
-        <v>4.135629187404322</v>
+        <v>2.508648197643544</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -3943,16 +3955,16 @@
         <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D95" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E95" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F95" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G95">
         <v>304</v>
@@ -3964,10 +3976,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J95">
-        <v>3.883137720480742</v>
+        <v>2.804250769071384</v>
       </c>
       <c r="K95">
-        <v>3.883137720480742</v>
+        <v>2.804250769071384</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -3978,16 +3990,16 @@
         <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E96" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F96" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G96">
         <v>101</v>
@@ -3999,10 +4011,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J96">
-        <v>1.798649079442733</v>
+        <v>2.547008202307568</v>
       </c>
       <c r="K96">
-        <v>1.798649079442733</v>
+        <v>2.547008202307568</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -4013,16 +4025,16 @@
         <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D97" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E97" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F97" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G97">
         <v>201</v>
@@ -4034,10 +4046,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J97">
-        <v>1.798649079442733</v>
+        <v>2.547008202307568</v>
       </c>
       <c r="K97">
-        <v>1.798649079442733</v>
+        <v>2.547008202307568</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -4048,16 +4060,16 @@
         <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D98" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E98" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F98" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G98">
         <v>301</v>
@@ -4069,10 +4081,10 @@
         <v>46204.48143518518</v>
       </c>
       <c r="J98">
-        <v>1.413567962158086</v>
+        <v>2.412718096413623</v>
       </c>
       <c r="K98">
-        <v>1.413567962158086</v>
+        <v>2.412718096413623</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -4083,16 +4095,16 @@
         <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D99" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E99" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F99" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G99">
         <v>302</v>
@@ -4104,10 +4116,10 @@
         <v>46205.77965277778</v>
       </c>
       <c r="J99">
-        <v>2.013994314162455</v>
+        <v>2.757348303637914</v>
       </c>
       <c r="K99">
-        <v>2.013994314162455</v>
+        <v>2.757348303637914</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -4118,16 +4130,16 @@
         <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D100" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E100" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F100" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G100">
         <v>303</v>
@@ -4139,10 +4151,10 @@
         <v>46206.61196759259</v>
       </c>
       <c r="J100">
-        <v>2.378746212537681</v>
+        <v>2.597410666279916</v>
       </c>
       <c r="K100">
-        <v>2.378746212537681</v>
+        <v>2.597410666279916</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -4153,16 +4165,16 @@
         <v>13</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E101" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F101" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G101">
         <v>304</v>
@@ -4174,10 +4186,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J101">
-        <v>3.011896468546829</v>
+        <v>2.360111806550468</v>
       </c>
       <c r="K101">
-        <v>3.011896468546829</v>
+        <v>2.360111806550468</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -4188,16 +4200,16 @@
         <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E102" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F102" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G102">
         <v>101</v>
@@ -4209,10 +4221,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J102">
-        <v>4.20316093081487</v>
+        <v>1.978853450574099</v>
       </c>
       <c r="K102">
-        <v>4.20316093081487</v>
+        <v>1.978853450574099</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -4223,16 +4235,16 @@
         <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D103" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E103" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F103" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G103">
         <v>201</v>
@@ -4244,10 +4256,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J103">
-        <v>4.20316093081487</v>
+        <v>1.978853450574099</v>
       </c>
       <c r="K103">
-        <v>4.20316093081487</v>
+        <v>1.978853450574099</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -4258,16 +4270,16 @@
         <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D104" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E104" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F104" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G104">
         <v>301</v>
@@ -4279,10 +4291,10 @@
         <v>46204.48143518518</v>
       </c>
       <c r="J104">
-        <v>5.266814649998151</v>
+        <v>1.973329619411917</v>
       </c>
       <c r="K104">
-        <v>5.266814649998151</v>
+        <v>1.973329619411917</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4293,16 +4305,16 @@
         <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E105" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F105" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G105">
         <v>302</v>
@@ -4314,10 +4326,10 @@
         <v>46205.77965277778</v>
       </c>
       <c r="J105">
-        <v>3.994991709466376</v>
+        <v>1.985517299327437</v>
       </c>
       <c r="K105">
-        <v>3.994991709466376</v>
+        <v>1.985517299327437</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -4328,16 +4340,16 @@
         <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D106" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E106" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F106" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G106">
         <v>303</v>
@@ -4349,10 +4361,10 @@
         <v>46206.61196759259</v>
       </c>
       <c r="J106">
-        <v>4.173442424252205</v>
+        <v>2.071364974880914</v>
       </c>
       <c r="K106">
-        <v>4.173442424252205</v>
+        <v>2.071364974880914</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -4363,16 +4375,16 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E107" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F107" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G107">
         <v>304</v>
@@ -4384,10 +4396,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J107">
-        <v>4.600778541286322</v>
+        <v>2.492949601255396</v>
       </c>
       <c r="K107">
-        <v>4.600778541286322</v>
+        <v>2.492949601255396</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -4398,31 +4410,31 @@
         <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D108" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E108" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F108" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G108">
         <v>101</v>
       </c>
       <c r="H108" s="2">
-        <v>46204.02234953704</v>
+        <v>46204.07336805556</v>
       </c>
       <c r="I108" s="2">
-        <v>46207.3324074074</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="J108">
-        <v>5.690980943853473</v>
+        <v>4.029575489602267</v>
       </c>
       <c r="K108">
-        <v>5.690980943853473</v>
+        <v>4.029575489602267</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -4433,31 +4445,31 @@
         <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E109" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F109" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G109">
         <v>201</v>
       </c>
       <c r="H109" s="2">
-        <v>46204.02234953704</v>
+        <v>46204.07336805556</v>
       </c>
       <c r="I109" s="2">
-        <v>46207.3324074074</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="J109">
-        <v>5.690980943853473</v>
+        <v>4.029575489602267</v>
       </c>
       <c r="K109">
-        <v>5.690980943853473</v>
+        <v>4.029575489602267</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -4468,31 +4480,31 @@
         <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E110" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F110" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G110">
         <v>301</v>
       </c>
       <c r="H110" s="2">
-        <v>46204.02234953704</v>
+        <v>46204.07336805556</v>
       </c>
       <c r="I110" s="2">
-        <v>46204.45003472222</v>
+        <v>46204.48143518518</v>
       </c>
       <c r="J110">
-        <v>5.867270425380308</v>
+        <v>4.091144075229254</v>
       </c>
       <c r="K110">
-        <v>5.867270425380308</v>
+        <v>4.091144075229254</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4503,31 +4515,31 @@
         <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D111" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E111" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F111" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G111">
         <v>302</v>
       </c>
       <c r="H111" s="2">
-        <v>46205.02739583333</v>
+        <v>46205.1180787037</v>
       </c>
       <c r="I111" s="2">
-        <v>46205.74840277778</v>
+        <v>46205.77965277778</v>
       </c>
       <c r="J111">
-        <v>5.002728289455207</v>
+        <v>3.974895780538705</v>
       </c>
       <c r="K111">
-        <v>5.002728289455207</v>
+        <v>3.974895780538705</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4538,31 +4550,31 @@
         <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D112" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E112" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F112" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G112">
         <v>303</v>
       </c>
       <c r="H112" s="2">
-        <v>46206.09667824074</v>
+        <v>46206.14086805555</v>
       </c>
       <c r="I112" s="2">
-        <v>46206.6680324074</v>
+        <v>46206.61196759259</v>
       </c>
       <c r="J112">
-        <v>6.868403886344061</v>
+        <v>4.135629187404322</v>
       </c>
       <c r="K112">
-        <v>6.868403886344061</v>
+        <v>4.135629187404322</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -4573,31 +4585,31 @@
         <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E113" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F113" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G113">
         <v>304</v>
       </c>
       <c r="H113" s="2">
-        <v>46207.26863425926</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="I113" s="2">
-        <v>46207.3324074074</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="J113">
-        <v>7.350097511109873</v>
+        <v>3.883137720480742</v>
       </c>
       <c r="K113">
-        <v>7.350097511109873</v>
+        <v>3.883137720480742</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -4608,31 +4620,31 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D114" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E114" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F114" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G114">
         <v>101</v>
       </c>
       <c r="H114" s="2">
-        <v>46204.02234953704</v>
+        <v>46204.07336805556</v>
       </c>
       <c r="I114" s="2">
-        <v>46207.3324074074</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="J114">
-        <v>2.208761678473779</v>
+        <v>1.798649079442733</v>
       </c>
       <c r="K114">
-        <v>2.208761678473779</v>
+        <v>1.798649079442733</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -4643,31 +4655,31 @@
         <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D115" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E115" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F115" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G115">
         <v>201</v>
       </c>
       <c r="H115" s="2">
-        <v>46204.02234953704</v>
+        <v>46204.07336805556</v>
       </c>
       <c r="I115" s="2">
-        <v>46207.3324074074</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="J115">
-        <v>2.208761678473779</v>
+        <v>1.798649079442733</v>
       </c>
       <c r="K115">
-        <v>2.208761678473779</v>
+        <v>1.798649079442733</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -4678,31 +4690,31 @@
         <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D116" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E116" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F116" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G116">
         <v>301</v>
       </c>
       <c r="H116" s="2">
-        <v>46204.02234953704</v>
+        <v>46204.07336805556</v>
       </c>
       <c r="I116" s="2">
-        <v>46204.45003472222</v>
+        <v>46204.48143518518</v>
       </c>
       <c r="J116">
-        <v>2.274661641857774</v>
+        <v>1.413567962158086</v>
       </c>
       <c r="K116">
-        <v>2.274661641857774</v>
+        <v>1.413567962158086</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -4713,31 +4725,31 @@
         <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D117" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E117" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F117" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G117">
         <v>302</v>
       </c>
       <c r="H117" s="2">
-        <v>46205.02739583333</v>
+        <v>46205.1180787037</v>
       </c>
       <c r="I117" s="2">
-        <v>46205.74840277778</v>
+        <v>46205.77965277778</v>
       </c>
       <c r="J117">
-        <v>2.296125331809375</v>
+        <v>2.013994314162456</v>
       </c>
       <c r="K117">
-        <v>2.296125331809375</v>
+        <v>2.013994314162456</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -4748,31 +4760,31 @@
         <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D118" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E118" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F118" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G118">
         <v>303</v>
       </c>
       <c r="H118" s="2">
-        <v>46206.09667824074</v>
+        <v>46206.14086805555</v>
       </c>
       <c r="I118" s="2">
-        <v>46206.6680324074</v>
+        <v>46206.61196759259</v>
       </c>
       <c r="J118">
-        <v>2.021466357144072</v>
+        <v>2.378746212537681</v>
       </c>
       <c r="K118">
-        <v>2.021466357144072</v>
+        <v>2.378746212537681</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -4783,31 +4795,31 @@
         <v>13</v>
       </c>
       <c r="C119" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E119" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F119" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G119">
         <v>304</v>
       </c>
       <c r="H119" s="2">
-        <v>46207.26863425926</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="I119" s="2">
-        <v>46207.3324074074</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="J119">
-        <v>2.425228097784526</v>
+        <v>3.011896468546829</v>
       </c>
       <c r="K119">
-        <v>2.425228097784526</v>
+        <v>3.011896468546829</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -4818,31 +4830,31 @@
         <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D120" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E120" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F120" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G120">
         <v>101</v>
       </c>
       <c r="H120" s="2">
-        <v>46204.02232638889</v>
+        <v>46204.07336805556</v>
       </c>
       <c r="I120" s="2">
-        <v>46207.33239583333</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="J120">
-        <v>5.037977720289904</v>
+        <v>4.20316093081487</v>
       </c>
       <c r="K120">
-        <v>5.037977720289904</v>
+        <v>4.20316093081487</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -4853,31 +4865,31 @@
         <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D121" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E121" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F121" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G121">
         <v>201</v>
       </c>
       <c r="H121" s="2">
-        <v>46204.02232638889</v>
+        <v>46204.07336805556</v>
       </c>
       <c r="I121" s="2">
-        <v>46207.33239583333</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="J121">
-        <v>5.037977720289904</v>
+        <v>4.20316093081487</v>
       </c>
       <c r="K121">
-        <v>5.037977720289904</v>
+        <v>4.20316093081487</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -4888,31 +4900,31 @@
         <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D122" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E122" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F122" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G122">
         <v>301</v>
       </c>
       <c r="H122" s="2">
-        <v>46204.02232638889</v>
+        <v>46204.07336805556</v>
       </c>
       <c r="I122" s="2">
-        <v>46204.45002314815</v>
+        <v>46204.48143518518</v>
       </c>
       <c r="J122">
-        <v>5.08846397087053</v>
+        <v>5.26681464999815</v>
       </c>
       <c r="K122">
-        <v>5.08846397087053</v>
+        <v>5.26681464999815</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -4923,31 +4935,31 @@
         <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D123" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E123" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F123" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G123">
         <v>302</v>
       </c>
       <c r="H123" s="2">
-        <v>46205.02738425926</v>
+        <v>46205.1180787037</v>
       </c>
       <c r="I123" s="2">
-        <v>46205.74839120371</v>
+        <v>46205.77965277778</v>
       </c>
       <c r="J123">
-        <v>5.850465480446287</v>
+        <v>3.994991709466376</v>
       </c>
       <c r="K123">
-        <v>5.850465480446287</v>
+        <v>3.994991709466376</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -4958,31 +4970,31 @@
         <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D124" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E124" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F124" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G124">
         <v>303</v>
       </c>
       <c r="H124" s="2">
-        <v>46206.09666666666</v>
+        <v>46206.14086805555</v>
       </c>
       <c r="I124" s="2">
-        <v>46206.66802083333</v>
+        <v>46206.61196759259</v>
       </c>
       <c r="J124">
-        <v>5.3490013510671</v>
+        <v>4.173442424252205</v>
       </c>
       <c r="K124">
-        <v>5.3490013510671</v>
+        <v>4.173442424252205</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -4993,31 +5005,31 @@
         <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D125" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E125" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F125" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G125">
         <v>304</v>
       </c>
       <c r="H125" s="2">
-        <v>46207.26862268519</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="I125" s="2">
-        <v>46207.33239583333</v>
+        <v>46207.44892361111</v>
       </c>
       <c r="J125">
-        <v>6.303252623230003</v>
+        <v>4.600778541286321</v>
       </c>
       <c r="K125">
-        <v>6.303252623230003</v>
+        <v>4.600778541286321</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5028,31 +5040,31 @@
         <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D126" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E126" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F126" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G126">
         <v>101</v>
       </c>
       <c r="H126" s="2">
-        <v>46204.02232638889</v>
+        <v>46204.02234953704</v>
       </c>
       <c r="I126" s="2">
-        <v>46207.33239583333</v>
+        <v>46207.3324074074</v>
       </c>
       <c r="J126">
-        <v>3.09010363110375</v>
+        <v>5.690980943853473</v>
       </c>
       <c r="K126">
-        <v>3.09010363110375</v>
+        <v>5.690980943853473</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -5063,31 +5075,31 @@
         <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D127" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E127" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F127" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G127">
         <v>201</v>
       </c>
       <c r="H127" s="2">
-        <v>46204.02232638889</v>
+        <v>46204.02234953704</v>
       </c>
       <c r="I127" s="2">
-        <v>46207.33239583333</v>
+        <v>46207.3324074074</v>
       </c>
       <c r="J127">
-        <v>3.09010363110375</v>
+        <v>5.690980943853473</v>
       </c>
       <c r="K127">
-        <v>3.09010363110375</v>
+        <v>5.690980943853473</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -5098,31 +5110,31 @@
         <v>13</v>
       </c>
       <c r="C128" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D128" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E128" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F128" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G128">
         <v>301</v>
       </c>
       <c r="H128" s="2">
-        <v>46204.02232638889</v>
+        <v>46204.02234953704</v>
       </c>
       <c r="I128" s="2">
-        <v>46204.45002314815</v>
+        <v>46204.45003472222</v>
       </c>
       <c r="J128">
-        <v>3.055046313277442</v>
+        <v>5.867270425380308</v>
       </c>
       <c r="K128">
-        <v>3.055046313277442</v>
+        <v>5.867270425380308</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -5133,31 +5145,31 @@
         <v>13</v>
       </c>
       <c r="C129" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D129" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E129" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F129" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G129">
         <v>302</v>
       </c>
       <c r="H129" s="2">
-        <v>46205.02738425926</v>
+        <v>46205.02739583333</v>
       </c>
       <c r="I129" s="2">
-        <v>46205.74839120371</v>
+        <v>46205.74840277778</v>
       </c>
       <c r="J129">
-        <v>3.205586147890944</v>
+        <v>5.002728289455206</v>
       </c>
       <c r="K129">
-        <v>3.205586147890944</v>
+        <v>5.002728289455206</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -5168,31 +5180,31 @@
         <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D130" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E130" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F130" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G130">
         <v>303</v>
       </c>
       <c r="H130" s="2">
-        <v>46206.09666666666</v>
+        <v>46206.09667824074</v>
       </c>
       <c r="I130" s="2">
-        <v>46206.66802083333</v>
+        <v>46206.6680324074</v>
       </c>
       <c r="J130">
-        <v>3.078750218465227</v>
+        <v>6.868403886344059</v>
       </c>
       <c r="K130">
-        <v>3.078750218465227</v>
+        <v>6.868403886344059</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -5203,31 +5215,31 @@
         <v>13</v>
       </c>
       <c r="C131" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D131" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E131" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F131" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G131">
         <v>304</v>
       </c>
       <c r="H131" s="2">
-        <v>46207.26862268519</v>
+        <v>46207.26863425926</v>
       </c>
       <c r="I131" s="2">
-        <v>46207.33239583333</v>
+        <v>46207.3324074074</v>
       </c>
       <c r="J131">
-        <v>3.349614353845518</v>
+        <v>7.350097511109873</v>
       </c>
       <c r="K131">
-        <v>3.349614353845518</v>
+        <v>7.350097511109873</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -5238,31 +5250,31 @@
         <v>13</v>
       </c>
       <c r="C132" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D132" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E132" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F132" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G132">
         <v>101</v>
       </c>
       <c r="H132" s="2">
-        <v>46204.02231481481</v>
+        <v>46204.02234953704</v>
       </c>
       <c r="I132" s="2">
-        <v>46207.33238425926</v>
+        <v>46207.3324074074</v>
       </c>
       <c r="J132">
-        <v>1.865612698518206</v>
+        <v>2.208761678473779</v>
       </c>
       <c r="K132">
-        <v>1.865612698518206</v>
+        <v>2.208761678473779</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -5273,31 +5285,31 @@
         <v>13</v>
       </c>
       <c r="C133" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D133" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E133" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F133" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G133">
         <v>201</v>
       </c>
       <c r="H133" s="2">
-        <v>46204.02231481481</v>
+        <v>46204.02234953704</v>
       </c>
       <c r="I133" s="2">
-        <v>46207.33238425926</v>
+        <v>46207.3324074074</v>
       </c>
       <c r="J133">
-        <v>1.865612698518206</v>
+        <v>2.208761678473779</v>
       </c>
       <c r="K133">
-        <v>1.865612698518206</v>
+        <v>2.208761678473779</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -5308,31 +5320,31 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D134" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E134" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F134" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G134">
         <v>301</v>
       </c>
       <c r="H134" s="2">
-        <v>46204.02231481481</v>
+        <v>46204.02234953704</v>
       </c>
       <c r="I134" s="2">
-        <v>46204.45001157407</v>
+        <v>46204.45003472222</v>
       </c>
       <c r="J134">
-        <v>1.809970793828339</v>
+        <v>2.274661641857774</v>
       </c>
       <c r="K134">
-        <v>1.809970793828339</v>
+        <v>2.274661641857774</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -5343,31 +5355,31 @@
         <v>13</v>
       </c>
       <c r="C135" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D135" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E135" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F135" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G135">
         <v>302</v>
       </c>
       <c r="H135" s="2">
-        <v>46205.02737268519</v>
+        <v>46205.02739583333</v>
       </c>
       <c r="I135" s="2">
-        <v>46205.74837962963</v>
+        <v>46205.74840277778</v>
       </c>
       <c r="J135">
-        <v>1.905368949999892</v>
+        <v>2.296125331809375</v>
       </c>
       <c r="K135">
-        <v>1.905368949999892</v>
+        <v>2.296125331809375</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -5378,31 +5390,31 @@
         <v>13</v>
       </c>
       <c r="C136" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D136" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E136" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F136" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G136">
         <v>303</v>
       </c>
       <c r="H136" s="2">
-        <v>46206.0966550926</v>
+        <v>46206.09667824074</v>
       </c>
       <c r="I136" s="2">
-        <v>46206.66800925926</v>
+        <v>46206.6680324074</v>
       </c>
       <c r="J136">
-        <v>1.823397200919778</v>
+        <v>2.021466357144072</v>
       </c>
       <c r="K136">
-        <v>1.823397200919778</v>
+        <v>2.021466357144072</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -5413,31 +5425,31 @@
         <v>13</v>
       </c>
       <c r="C137" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D137" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E137" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F137" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G137">
         <v>304</v>
       </c>
       <c r="H137" s="2">
-        <v>46207.26861111111</v>
+        <v>46207.26863425926</v>
       </c>
       <c r="I137" s="2">
-        <v>46207.33238425926</v>
+        <v>46207.3324074074</v>
       </c>
       <c r="J137">
-        <v>1.972364653958022</v>
+        <v>2.425228097784525</v>
       </c>
       <c r="K137">
-        <v>1.972364653958022</v>
+        <v>2.425228097784525</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -5445,34 +5457,34 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C138" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D138" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="E138" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F138" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G138">
         <v>101</v>
       </c>
       <c r="H138" s="2">
-        <v>46207.11439814815</v>
+        <v>46204.02232638889</v>
       </c>
       <c r="I138" s="2">
-        <v>46208.49990740741</v>
+        <v>46207.33239583333</v>
       </c>
       <c r="J138">
-        <v>1.718623046793465</v>
+        <v>5.037977720289904</v>
       </c>
       <c r="K138">
-        <v>1.718623046793465</v>
+        <v>5.037977720289904</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -5480,34 +5492,34 @@
         <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C139" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D139" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="E139" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F139" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G139">
         <v>201</v>
       </c>
       <c r="H139" s="2">
-        <v>46207.11439814815</v>
+        <v>46204.02232638889</v>
       </c>
       <c r="I139" s="2">
-        <v>46208.49990740741</v>
+        <v>46207.33239583333</v>
       </c>
       <c r="J139">
-        <v>1.718623046793465</v>
+        <v>5.037977720289904</v>
       </c>
       <c r="K139">
-        <v>1.718623046793465</v>
+        <v>5.037977720289904</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -5515,34 +5527,34 @@
         <v>11</v>
       </c>
       <c r="B140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C140" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D140" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="E140" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F140" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G140">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H140" s="2">
-        <v>46207.11439814815</v>
+        <v>46204.02232638889</v>
       </c>
       <c r="I140" s="2">
-        <v>46207.13734953704</v>
+        <v>46204.45002314815</v>
       </c>
       <c r="J140">
-        <v>1.970153994820802</v>
+        <v>5.08846397087053</v>
       </c>
       <c r="K140">
-        <v>1.970153994820802</v>
+        <v>5.08846397087053</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -5550,34 +5562,34 @@
         <v>11</v>
       </c>
       <c r="B141" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C141" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D141" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="E141" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F141" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G141">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H141" s="2">
-        <v>46208.47668981482</v>
+        <v>46205.02738425926</v>
       </c>
       <c r="I141" s="2">
-        <v>46208.49990740741</v>
+        <v>46205.74839120371</v>
       </c>
       <c r="J141">
-        <v>1.735084218293082</v>
+        <v>5.850465480446287</v>
       </c>
       <c r="K141">
-        <v>1.735084218293082</v>
+        <v>5.850465480446287</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -5585,34 +5597,34 @@
         <v>11</v>
       </c>
       <c r="B142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C142" t="s">
         <v>32</v>
       </c>
       <c r="D142" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E142" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F142" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="G142">
-        <v>101</v>
+        <v>303</v>
       </c>
       <c r="H142" s="2">
-        <v>46204.54361111111</v>
+        <v>46206.09666666666</v>
       </c>
       <c r="I142" s="2">
-        <v>46208.3160300926</v>
+        <v>46206.66802083333</v>
       </c>
       <c r="J142">
-        <v>1.528077702610358</v>
+        <v>5.3490013510671</v>
       </c>
       <c r="K142">
-        <v>1.528077702610358</v>
+        <v>5.3490013510671</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -5620,34 +5632,34 @@
         <v>11</v>
       </c>
       <c r="B143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C143" t="s">
         <v>32</v>
       </c>
       <c r="D143" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E143" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F143" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G143">
-        <v>201</v>
+        <v>304</v>
       </c>
       <c r="H143" s="2">
-        <v>46204.54361111111</v>
+        <v>46207.26862268519</v>
       </c>
       <c r="I143" s="2">
-        <v>46208.3160300926</v>
+        <v>46207.33239583333</v>
       </c>
       <c r="J143">
-        <v>1.528077702610358</v>
+        <v>6.303252623230005</v>
       </c>
       <c r="K143">
-        <v>1.528077702610358</v>
+        <v>6.303252623230005</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -5655,34 +5667,34 @@
         <v>11</v>
       </c>
       <c r="B144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
         <v>32</v>
       </c>
       <c r="D144" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E144" t="s">
         <v>62</v>
       </c>
       <c r="F144" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G144">
-        <v>301</v>
+        <v>101</v>
       </c>
       <c r="H144" s="2">
-        <v>46204.54361111111</v>
+        <v>46204.02232638889</v>
       </c>
       <c r="I144" s="2">
-        <v>46204.55734953703</v>
+        <v>46207.33239583333</v>
       </c>
       <c r="J144">
-        <v>1.544236547921107</v>
+        <v>3.09010363110375</v>
       </c>
       <c r="K144">
-        <v>1.544236547921107</v>
+        <v>3.09010363110375</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -5690,34 +5702,34 @@
         <v>11</v>
       </c>
       <c r="B145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C145" t="s">
         <v>32</v>
       </c>
       <c r="D145" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E145" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F145" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G145">
-        <v>303</v>
+        <v>201</v>
       </c>
       <c r="H145" s="2">
-        <v>46206.9258449074</v>
+        <v>46204.02232638889</v>
       </c>
       <c r="I145" s="2">
-        <v>46206.93956018519</v>
+        <v>46207.33239583333</v>
       </c>
       <c r="J145">
-        <v>1.603204582758952</v>
+        <v>3.09010363110375</v>
       </c>
       <c r="K145">
-        <v>1.603204582758952</v>
+        <v>3.09010363110375</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -5725,34 +5737,34 @@
         <v>11</v>
       </c>
       <c r="B146" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C146" t="s">
         <v>32</v>
       </c>
       <c r="D146" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E146" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F146" t="s">
         <v>82</v>
       </c>
       <c r="G146">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="H146" s="2">
-        <v>46208.30229166667</v>
+        <v>46204.02232638889</v>
       </c>
       <c r="I146" s="2">
-        <v>46208.3160300926</v>
+        <v>46204.45002314815</v>
       </c>
       <c r="J146">
-        <v>1.409765383271333</v>
+        <v>3.055046313277442</v>
       </c>
       <c r="K146">
-        <v>1.409765383271333</v>
+        <v>3.055046313277442</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -5760,34 +5772,34 @@
         <v>11</v>
       </c>
       <c r="B147" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C147" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D147" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E147" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F147" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="G147">
-        <v>101</v>
+        <v>302</v>
       </c>
       <c r="H147" s="2">
-        <v>46207.23271990741</v>
+        <v>46205.02738425926</v>
       </c>
       <c r="I147" s="2">
-        <v>46207.23274305555</v>
+        <v>46205.74839120371</v>
       </c>
       <c r="J147">
-        <v>1.461178078579722</v>
+        <v>3.205586147890944</v>
       </c>
       <c r="K147">
-        <v>1.461178078579722</v>
+        <v>3.205586147890944</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -5795,34 +5807,34 @@
         <v>11</v>
       </c>
       <c r="B148" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C148" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D148" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E148" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F148" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G148">
-        <v>201</v>
+        <v>303</v>
       </c>
       <c r="H148" s="2">
-        <v>46207.23271990741</v>
+        <v>46206.09666666666</v>
       </c>
       <c r="I148" s="2">
-        <v>46207.23274305555</v>
+        <v>46206.66802083333</v>
       </c>
       <c r="J148">
-        <v>1.461178078579722</v>
+        <v>3.078750218465227</v>
       </c>
       <c r="K148">
-        <v>1.461178078579722</v>
+        <v>3.078750218465227</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -5830,34 +5842,34 @@
         <v>11</v>
       </c>
       <c r="B149" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C149" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D149" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E149" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F149" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G149">
         <v>304</v>
       </c>
       <c r="H149" s="2">
-        <v>46207.23271990741</v>
+        <v>46207.26862268519</v>
       </c>
       <c r="I149" s="2">
-        <v>46207.23274305555</v>
+        <v>46207.33239583333</v>
       </c>
       <c r="J149">
-        <v>1.461178078579722</v>
+        <v>3.349614353845518</v>
       </c>
       <c r="K149">
-        <v>1.461178078579722</v>
+        <v>3.349614353845518</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -5865,34 +5877,34 @@
         <v>11</v>
       </c>
       <c r="B150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C150" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D150" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E150" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F150" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G150">
         <v>101</v>
       </c>
       <c r="H150" s="2">
-        <v>46207.23271990741</v>
+        <v>46204.02231481481</v>
       </c>
       <c r="I150" s="2">
-        <v>46207.23274305555</v>
+        <v>46207.33238425926</v>
       </c>
       <c r="J150">
-        <v>1.990153757485192</v>
+        <v>1.865612698518206</v>
       </c>
       <c r="K150">
-        <v>1.990153757485192</v>
+        <v>1.865612698518206</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -5900,34 +5912,34 @@
         <v>11</v>
       </c>
       <c r="B151" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C151" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D151" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E151" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F151" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G151">
         <v>201</v>
       </c>
       <c r="H151" s="2">
-        <v>46207.23271990741</v>
+        <v>46204.02231481481</v>
       </c>
       <c r="I151" s="2">
-        <v>46207.23274305555</v>
+        <v>46207.33238425926</v>
       </c>
       <c r="J151">
-        <v>1.990153757485192</v>
+        <v>1.865612698518206</v>
       </c>
       <c r="K151">
-        <v>1.990153757485192</v>
+        <v>1.865612698518206</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -5935,34 +5947,34 @@
         <v>11</v>
       </c>
       <c r="B152" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C152" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D152" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E152" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F152" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G152">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H152" s="2">
-        <v>46207.23271990741</v>
+        <v>46204.02231481481</v>
       </c>
       <c r="I152" s="2">
-        <v>46207.23274305555</v>
+        <v>46204.45001157407</v>
       </c>
       <c r="J152">
-        <v>1.990153757485192</v>
+        <v>1.809970793828339</v>
       </c>
       <c r="K152">
-        <v>1.990153757485192</v>
+        <v>1.809970793828339</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -5970,34 +5982,34 @@
         <v>11</v>
       </c>
       <c r="B153" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C153" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D153" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E153" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F153" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="G153">
-        <v>101</v>
+        <v>302</v>
       </c>
       <c r="H153" s="2">
-        <v>46207.66858796297</v>
+        <v>46205.02737268519</v>
       </c>
       <c r="I153" s="2">
-        <v>46207.68778935185</v>
+        <v>46205.74837962963</v>
       </c>
       <c r="J153">
-        <v>2.128471896743432</v>
+        <v>1.905368949999892</v>
       </c>
       <c r="K153">
-        <v>2.128471896743432</v>
+        <v>1.905368949999892</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -6005,34 +6017,34 @@
         <v>11</v>
       </c>
       <c r="B154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C154" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D154" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E154" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F154" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G154">
-        <v>201</v>
+        <v>303</v>
       </c>
       <c r="H154" s="2">
-        <v>46207.66858796297</v>
+        <v>46206.0966550926</v>
       </c>
       <c r="I154" s="2">
-        <v>46207.68778935185</v>
+        <v>46206.66800925926</v>
       </c>
       <c r="J154">
-        <v>2.128471896743432</v>
+        <v>1.823397200919778</v>
       </c>
       <c r="K154">
-        <v>2.128471896743432</v>
+        <v>1.823397200919778</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -6040,34 +6052,34 @@
         <v>11</v>
       </c>
       <c r="B155" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C155" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D155" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E155" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F155" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G155">
         <v>304</v>
       </c>
       <c r="H155" s="2">
-        <v>46207.66858796297</v>
+        <v>46207.26861111111</v>
       </c>
       <c r="I155" s="2">
-        <v>46207.68778935185</v>
+        <v>46207.33238425926</v>
       </c>
       <c r="J155">
-        <v>2.128471896743432</v>
+        <v>1.972364653958022</v>
       </c>
       <c r="K155">
-        <v>2.128471896743432</v>
+        <v>1.972364653958022</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -6078,31 +6090,31 @@
         <v>14</v>
       </c>
       <c r="C156" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D156" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E156" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F156" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G156">
         <v>101</v>
       </c>
       <c r="H156" s="2">
-        <v>46209.17533564815</v>
+        <v>46207.11439814815</v>
       </c>
       <c r="I156" s="2">
-        <v>46209.19881944444</v>
+        <v>46208.49990740741</v>
       </c>
       <c r="J156">
-        <v>3.287749400794237</v>
+        <v>1.718623046793465</v>
       </c>
       <c r="K156">
-        <v>3.287749400794237</v>
+        <v>1.718623046793465</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -6113,31 +6125,31 @@
         <v>14</v>
       </c>
       <c r="C157" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D157" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E157" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F157" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G157">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H157" s="2">
-        <v>46209.17533564815</v>
+        <v>46207.11439814815</v>
       </c>
       <c r="I157" s="2">
-        <v>46209.19881944444</v>
+        <v>46208.49990740741</v>
       </c>
       <c r="J157">
-        <v>3.287749400794237</v>
+        <v>1.718623046793465</v>
       </c>
       <c r="K157">
-        <v>3.287749400794237</v>
+        <v>1.718623046793465</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -6148,31 +6160,31 @@
         <v>14</v>
       </c>
       <c r="C158" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D158" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E158" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F158" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G158">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H158" s="2">
-        <v>46209.17533564815</v>
+        <v>46207.11439814815</v>
       </c>
       <c r="I158" s="2">
-        <v>46209.19881944444</v>
+        <v>46207.13734953704</v>
       </c>
       <c r="J158">
-        <v>3.287749400794237</v>
+        <v>1.970153994820802</v>
       </c>
       <c r="K158">
-        <v>3.287749400794237</v>
+        <v>1.970153994820802</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6183,31 +6195,31 @@
         <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D159" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E159" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F159" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="G159">
-        <v>101</v>
+        <v>305</v>
       </c>
       <c r="H159" s="2">
-        <v>46210.58523148148</v>
+        <v>46208.47668981482</v>
       </c>
       <c r="I159" s="2">
-        <v>46210.61064814815</v>
+        <v>46208.49990740741</v>
       </c>
       <c r="J159">
-        <v>1.647806404612758</v>
+        <v>1.735084218293082</v>
       </c>
       <c r="K159">
-        <v>1.647806404612758</v>
+        <v>1.735084218293082</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -6218,31 +6230,31 @@
         <v>14</v>
       </c>
       <c r="C160" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D160" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E160" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F160" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G160">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="H160" s="2">
-        <v>46210.58523148148</v>
+        <v>46204.54361111111</v>
       </c>
       <c r="I160" s="2">
-        <v>46210.61064814815</v>
+        <v>46208.3160300926</v>
       </c>
       <c r="J160">
-        <v>1.647806404612758</v>
+        <v>1.528077702610358</v>
       </c>
       <c r="K160">
-        <v>1.647806404612758</v>
+        <v>1.528077702610358</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -6253,31 +6265,31 @@
         <v>14</v>
       </c>
       <c r="C161" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D161" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E161" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F161" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G161">
-        <v>307</v>
+        <v>201</v>
       </c>
       <c r="H161" s="2">
-        <v>46210.58523148148</v>
+        <v>46204.54361111111</v>
       </c>
       <c r="I161" s="2">
-        <v>46210.61064814815</v>
+        <v>46208.3160300926</v>
       </c>
       <c r="J161">
-        <v>1.647806404612758</v>
+        <v>1.528077702610358</v>
       </c>
       <c r="K161">
-        <v>1.647806404612758</v>
+        <v>1.528077702610358</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -6288,31 +6300,31 @@
         <v>14</v>
       </c>
       <c r="C162" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D162" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E162" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F162" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="G162">
-        <v>101</v>
+        <v>301</v>
       </c>
       <c r="H162" s="2">
-        <v>46210.58523148148</v>
+        <v>46204.54361111111</v>
       </c>
       <c r="I162" s="2">
-        <v>46210.61064814815</v>
+        <v>46204.55734953703</v>
       </c>
       <c r="J162">
-        <v>2.26867574331909</v>
+        <v>1.544236547921107</v>
       </c>
       <c r="K162">
-        <v>2.26867574331909</v>
+        <v>1.544236547921107</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -6323,31 +6335,31 @@
         <v>14</v>
       </c>
       <c r="C163" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D163" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E163" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F163" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G163">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="H163" s="2">
-        <v>46210.58523148148</v>
+        <v>46206.9258449074</v>
       </c>
       <c r="I163" s="2">
-        <v>46210.61064814815</v>
+        <v>46206.93956018519</v>
       </c>
       <c r="J163">
-        <v>2.26867574331909</v>
+        <v>1.603204582758952</v>
       </c>
       <c r="K163">
-        <v>2.26867574331909</v>
+        <v>1.603204582758952</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -6358,31 +6370,31 @@
         <v>14</v>
       </c>
       <c r="C164" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D164" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E164" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F164" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G164">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H164" s="2">
-        <v>46210.58523148148</v>
+        <v>46208.30229166667</v>
       </c>
       <c r="I164" s="2">
-        <v>46210.61064814815</v>
+        <v>46208.3160300926</v>
       </c>
       <c r="J164">
-        <v>2.26867574331909</v>
+        <v>1.409765383271333</v>
       </c>
       <c r="K164">
-        <v>2.26867574331909</v>
+        <v>1.409765383271333</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -6393,31 +6405,31 @@
         <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D165" t="s">
         <v>47</v>
       </c>
       <c r="E165" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F165" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G165">
         <v>101</v>
       </c>
       <c r="H165" s="2">
-        <v>46210.86798611111</v>
+        <v>46207.23271990741</v>
       </c>
       <c r="I165" s="2">
-        <v>46210.88290509259</v>
+        <v>46207.23274305555</v>
       </c>
       <c r="J165">
-        <v>2.721736457511896</v>
+        <v>1.461178078579722</v>
       </c>
       <c r="K165">
-        <v>2.721736457511896</v>
+        <v>1.461178078579722</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -6428,31 +6440,31 @@
         <v>14</v>
       </c>
       <c r="C166" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D166" t="s">
         <v>47</v>
       </c>
       <c r="E166" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F166" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G166">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H166" s="2">
-        <v>46210.86798611111</v>
+        <v>46207.23271990741</v>
       </c>
       <c r="I166" s="2">
-        <v>46210.88290509259</v>
+        <v>46207.23274305555</v>
       </c>
       <c r="J166">
-        <v>2.721736457511896</v>
+        <v>1.461178078579722</v>
       </c>
       <c r="K166">
-        <v>2.721736457511896</v>
+        <v>1.461178078579722</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -6463,31 +6475,31 @@
         <v>14</v>
       </c>
       <c r="C167" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D167" t="s">
         <v>47</v>
       </c>
       <c r="E167" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F167" t="s">
         <v>85</v>
       </c>
       <c r="G167">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H167" s="2">
-        <v>46210.86798611111</v>
+        <v>46207.23271990741</v>
       </c>
       <c r="I167" s="2">
-        <v>46210.88290509259</v>
+        <v>46207.23274305555</v>
       </c>
       <c r="J167">
-        <v>2.721736457511896</v>
+        <v>1.461178078579722</v>
       </c>
       <c r="K167">
-        <v>2.721736457511896</v>
+        <v>1.461178078579722</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -6498,31 +6510,31 @@
         <v>14</v>
       </c>
       <c r="C168" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D168" t="s">
         <v>48</v>
       </c>
       <c r="E168" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F168" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G168">
         <v>101</v>
       </c>
       <c r="H168" s="2">
-        <v>46206.20539351852</v>
+        <v>46207.23271990741</v>
       </c>
       <c r="I168" s="2">
-        <v>46207.26991898148</v>
+        <v>46207.23274305555</v>
       </c>
       <c r="J168">
-        <v>1.718217672992258</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="K168">
-        <v>1.718217672992258</v>
+        <v>1.990153757485192</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -6533,31 +6545,31 @@
         <v>14</v>
       </c>
       <c r="C169" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D169" t="s">
         <v>48</v>
       </c>
       <c r="E169" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F169" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G169">
         <v>201</v>
       </c>
       <c r="H169" s="2">
-        <v>46206.20539351852</v>
+        <v>46207.23271990741</v>
       </c>
       <c r="I169" s="2">
-        <v>46207.26991898148</v>
+        <v>46207.23274305555</v>
       </c>
       <c r="J169">
-        <v>1.718217672992258</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="K169">
-        <v>1.718217672992258</v>
+        <v>1.990153757485192</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -6568,31 +6580,31 @@
         <v>14</v>
       </c>
       <c r="C170" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D170" t="s">
         <v>48</v>
       </c>
       <c r="E170" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F170" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G170">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H170" s="2">
-        <v>46206.20539351852</v>
+        <v>46207.23271990741</v>
       </c>
       <c r="I170" s="2">
-        <v>46206.21914351852</v>
+        <v>46207.23274305555</v>
       </c>
       <c r="J170">
-        <v>1.66438975798056</v>
+        <v>1.990153757485192</v>
       </c>
       <c r="K170">
-        <v>1.66438975798056</v>
+        <v>1.990153757485192</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -6603,31 +6615,31 @@
         <v>14</v>
       </c>
       <c r="C171" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D171" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E171" t="s">
         <v>62</v>
       </c>
       <c r="F171" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="G171">
-        <v>304</v>
+        <v>101</v>
       </c>
       <c r="H171" s="2">
-        <v>46207.25616898148</v>
+        <v>46207.66858796297</v>
       </c>
       <c r="I171" s="2">
-        <v>46207.26991898148</v>
+        <v>46207.68778935185</v>
       </c>
       <c r="J171">
-        <v>1.77599308064014</v>
+        <v>2.128471896743432</v>
       </c>
       <c r="K171">
-        <v>1.77599308064014</v>
+        <v>2.128471896743432</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -6638,31 +6650,31 @@
         <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D172" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E172" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F172" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="G172">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="H172" s="2">
-        <v>46207.46722222222</v>
+        <v>46207.66858796297</v>
       </c>
       <c r="I172" s="2">
-        <v>46211.70959490741</v>
+        <v>46207.68778935185</v>
       </c>
       <c r="J172">
-        <v>1.834107090255503</v>
+        <v>2.128471896743432</v>
       </c>
       <c r="K172">
-        <v>1.834107090255503</v>
+        <v>2.128471896743432</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -6673,31 +6685,31 @@
         <v>14</v>
       </c>
       <c r="C173" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D173" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E173" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F173" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G173">
-        <v>201</v>
+        <v>304</v>
       </c>
       <c r="H173" s="2">
-        <v>46207.46722222222</v>
+        <v>46207.66858796297</v>
       </c>
       <c r="I173" s="2">
-        <v>46207.50067129629</v>
+        <v>46207.68778935185</v>
       </c>
       <c r="J173">
-        <v>1.655153302224898</v>
+        <v>2.128471896743432</v>
       </c>
       <c r="K173">
-        <v>1.655153302224898</v>
+        <v>2.128471896743432</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -6708,31 +6720,31 @@
         <v>14</v>
       </c>
       <c r="C174" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D174" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E174" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F174" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G174">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="H174" s="2">
-        <v>46211.69054398148</v>
+        <v>46209.17533564815</v>
       </c>
       <c r="I174" s="2">
-        <v>46211.70959490741</v>
+        <v>46209.19881944444</v>
       </c>
       <c r="J174">
-        <v>2.077295089828365</v>
+        <v>3.287749400794237</v>
       </c>
       <c r="K174">
-        <v>2.077295089828365</v>
+        <v>3.287749400794237</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -6743,31 +6755,31 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D175" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E175" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F175" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G175">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="H175" s="2">
-        <v>46207.46722222222</v>
+        <v>46209.17533564815</v>
       </c>
       <c r="I175" s="2">
-        <v>46207.50067129629</v>
+        <v>46209.19881944444</v>
       </c>
       <c r="J175">
-        <v>1.655153302224898</v>
+        <v>3.287749400794237</v>
       </c>
       <c r="K175">
-        <v>1.655153302224898</v>
+        <v>3.287749400794237</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -6778,31 +6790,31 @@
         <v>14</v>
       </c>
       <c r="C176" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D176" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E176" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F176" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G176">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H176" s="2">
-        <v>46211.69054398148</v>
+        <v>46209.17533564815</v>
       </c>
       <c r="I176" s="2">
-        <v>46211.70959490741</v>
+        <v>46209.19881944444</v>
       </c>
       <c r="J176">
-        <v>2.077295089828365</v>
+        <v>3.287749400794237</v>
       </c>
       <c r="K176">
-        <v>2.077295089828365</v>
+        <v>3.287749400794237</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -6813,31 +6825,31 @@
         <v>14</v>
       </c>
       <c r="C177" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D177" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E177" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F177" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G177">
         <v>101</v>
       </c>
       <c r="H177" s="2">
-        <v>46207.46722222222</v>
+        <v>46210.58523148148</v>
       </c>
       <c r="I177" s="2">
-        <v>46211.70959490741</v>
+        <v>46210.61064814815</v>
       </c>
       <c r="J177">
-        <v>2.231945425056128</v>
+        <v>1.647806404612758</v>
       </c>
       <c r="K177">
-        <v>2.231945425056128</v>
+        <v>1.647806404612758</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -6848,31 +6860,31 @@
         <v>14</v>
       </c>
       <c r="C178" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D178" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E178" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F178" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G178">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H178" s="2">
-        <v>46207.46722222222</v>
+        <v>46210.58523148148</v>
       </c>
       <c r="I178" s="2">
-        <v>46207.50067129629</v>
+        <v>46210.61064814815</v>
       </c>
       <c r="J178">
-        <v>2.095109041186042</v>
+        <v>1.647806404612758</v>
       </c>
       <c r="K178">
-        <v>2.095109041186042</v>
+        <v>1.647806404612758</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -6883,31 +6895,31 @@
         <v>14</v>
       </c>
       <c r="C179" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D179" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E179" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F179" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G179">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="H179" s="2">
-        <v>46211.69054398148</v>
+        <v>46210.58523148148</v>
       </c>
       <c r="I179" s="2">
-        <v>46211.70959490741</v>
+        <v>46210.61064814815</v>
       </c>
       <c r="J179">
-        <v>2.439675648934623</v>
+        <v>1.647806404612758</v>
       </c>
       <c r="K179">
-        <v>2.439675648934623</v>
+        <v>1.647806404612758</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -6918,31 +6930,31 @@
         <v>14</v>
       </c>
       <c r="C180" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D180" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E180" t="s">
         <v>62</v>
       </c>
       <c r="F180" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="G180">
-        <v>304</v>
+        <v>101</v>
       </c>
       <c r="H180" s="2">
-        <v>46207.46722222222</v>
+        <v>46210.58523148148</v>
       </c>
       <c r="I180" s="2">
-        <v>46207.50067129629</v>
+        <v>46210.61064814815</v>
       </c>
       <c r="J180">
-        <v>2.095109041186042</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="K180">
-        <v>2.095109041186042</v>
+        <v>2.26867574331909</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -6953,31 +6965,31 @@
         <v>14</v>
       </c>
       <c r="C181" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D181" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E181" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F181" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G181">
-        <v>308</v>
+        <v>202</v>
       </c>
       <c r="H181" s="2">
-        <v>46211.69054398148</v>
+        <v>46210.58523148148</v>
       </c>
       <c r="I181" s="2">
-        <v>46211.70959490741</v>
+        <v>46210.61064814815</v>
       </c>
       <c r="J181">
-        <v>2.439675648934623</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="K181">
-        <v>2.439675648934623</v>
+        <v>2.26867574331909</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -6988,31 +7000,31 @@
         <v>14</v>
       </c>
       <c r="C182" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D182" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E182" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F182" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="G182">
-        <v>101</v>
+        <v>307</v>
       </c>
       <c r="H182" s="2">
-        <v>46209.54386574074</v>
+        <v>46210.58523148148</v>
       </c>
       <c r="I182" s="2">
-        <v>46214.6469212963</v>
+        <v>46210.61064814815</v>
       </c>
       <c r="J182">
-        <v>4.481333785255095</v>
+        <v>2.26867574331909</v>
       </c>
       <c r="K182">
-        <v>4.481333785255095</v>
+        <v>2.26867574331909</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -7023,31 +7035,31 @@
         <v>14</v>
       </c>
       <c r="C183" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D183" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E183" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F183" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G183">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="H183" s="2">
-        <v>46209.54386574074</v>
+        <v>46210.86798611111</v>
       </c>
       <c r="I183" s="2">
-        <v>46214.6469212963</v>
+        <v>46210.88290509259</v>
       </c>
       <c r="J183">
-        <v>4.481333785255095</v>
+        <v>2.721736457511896</v>
       </c>
       <c r="K183">
-        <v>4.481333785255095</v>
+        <v>2.721736457511896</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -7058,31 +7070,31 @@
         <v>14</v>
       </c>
       <c r="C184" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D184" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E184" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F184" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G184">
-        <v>306</v>
+        <v>202</v>
       </c>
       <c r="H184" s="2">
-        <v>46209.54386574074</v>
+        <v>46210.86798611111</v>
       </c>
       <c r="I184" s="2">
-        <v>46209.56375</v>
+        <v>46210.88290509259</v>
       </c>
       <c r="J184">
-        <v>4.85241903773101</v>
+        <v>2.721736457511896</v>
       </c>
       <c r="K184">
-        <v>4.85241903773101</v>
+        <v>2.721736457511896</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -7093,31 +7105,31 @@
         <v>14</v>
       </c>
       <c r="C185" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D185" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E185" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F185" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G185">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H185" s="2">
-        <v>46212.04517361111</v>
+        <v>46210.86798611111</v>
       </c>
       <c r="I185" s="2">
-        <v>46212.06122685185</v>
+        <v>46210.88290509259</v>
       </c>
       <c r="J185">
-        <v>6.128563787472934</v>
+        <v>2.721736457511896</v>
       </c>
       <c r="K185">
-        <v>6.128563787472934</v>
+        <v>2.721736457511896</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -7131,28 +7143,28 @@
         <v>40</v>
       </c>
       <c r="D186" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E186" t="s">
         <v>62</v>
       </c>
       <c r="F186" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="G186">
-        <v>310</v>
+        <v>101</v>
       </c>
       <c r="H186" s="2">
-        <v>46214.64324074074</v>
+        <v>46206.20539351852</v>
       </c>
       <c r="I186" s="2">
-        <v>46214.6469212963</v>
+        <v>46207.26991898148</v>
       </c>
       <c r="J186">
-        <v>6.264830902260329</v>
+        <v>1.718217672992258</v>
       </c>
       <c r="K186">
-        <v>6.264830902260329</v>
+        <v>1.718217672992258</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -7163,31 +7175,31 @@
         <v>14</v>
       </c>
       <c r="C187" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D187" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E187" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F187" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="G187">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="H187" s="2">
-        <v>46209.94287037037</v>
+        <v>46206.20539351852</v>
       </c>
       <c r="I187" s="2">
-        <v>46212.06846064814</v>
+        <v>46207.26991898148</v>
       </c>
       <c r="J187">
-        <v>1.583345850457788</v>
+        <v>1.718217672992258</v>
       </c>
       <c r="K187">
-        <v>1.583345850457788</v>
+        <v>1.718217672992258</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -7198,31 +7210,31 @@
         <v>14</v>
       </c>
       <c r="C188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D188" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E188" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F188" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G188">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="H188" s="2">
-        <v>46209.94287037037</v>
+        <v>46206.20539351852</v>
       </c>
       <c r="I188" s="2">
-        <v>46212.06846064814</v>
+        <v>46206.21914351852</v>
       </c>
       <c r="J188">
-        <v>1.583345850457788</v>
+        <v>1.66438975798056</v>
       </c>
       <c r="K188">
-        <v>1.583345850457788</v>
+        <v>1.66438975798056</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -7233,31 +7245,31 @@
         <v>14</v>
       </c>
       <c r="C189" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D189" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E189" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F189" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G189">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H189" s="2">
-        <v>46209.94287037037</v>
+        <v>46207.25616898148</v>
       </c>
       <c r="I189" s="2">
-        <v>46209.95513888889</v>
+        <v>46207.26991898148</v>
       </c>
       <c r="J189">
-        <v>1.886380431790312</v>
+        <v>1.77599308064014</v>
       </c>
       <c r="K189">
-        <v>1.886380431790312</v>
+        <v>1.77599308064014</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -7271,27 +7283,657 @@
         <v>41</v>
       </c>
       <c r="D190" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E190" t="s">
         <v>62</v>
       </c>
       <c r="F190" t="s">
+        <v>65</v>
+      </c>
+      <c r="G190">
+        <v>101</v>
+      </c>
+      <c r="H190" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I190" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J190">
+        <v>1.834107090255503</v>
+      </c>
+      <c r="K190">
+        <v>1.834107090255503</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11">
+      <c r="A191" t="s">
+        <v>11</v>
+      </c>
+      <c r="B191" t="s">
+        <v>14</v>
+      </c>
+      <c r="C191" t="s">
+        <v>41</v>
+      </c>
+      <c r="D191" t="s">
+        <v>47</v>
+      </c>
+      <c r="E191" t="s">
+        <v>63</v>
+      </c>
+      <c r="F191" t="s">
+        <v>81</v>
+      </c>
+      <c r="G191">
+        <v>201</v>
+      </c>
+      <c r="H191" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I191" s="2">
+        <v>46207.50067129629</v>
+      </c>
+      <c r="J191">
+        <v>1.655153302224898</v>
+      </c>
+      <c r="K191">
+        <v>1.655153302224898</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11">
+      <c r="A192" t="s">
+        <v>11</v>
+      </c>
+      <c r="B192" t="s">
+        <v>14</v>
+      </c>
+      <c r="C192" t="s">
+        <v>41</v>
+      </c>
+      <c r="D192" t="s">
+        <v>47</v>
+      </c>
+      <c r="E192" t="s">
+        <v>63</v>
+      </c>
+      <c r="F192" t="s">
         <v>87</v>
       </c>
-      <c r="G190">
+      <c r="G192">
+        <v>202</v>
+      </c>
+      <c r="H192" s="2">
+        <v>46211.69054398148</v>
+      </c>
+      <c r="I192" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J192">
+        <v>2.077295089828365</v>
+      </c>
+      <c r="K192">
+        <v>2.077295089828365</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11">
+      <c r="A193" t="s">
+        <v>11</v>
+      </c>
+      <c r="B193" t="s">
+        <v>14</v>
+      </c>
+      <c r="C193" t="s">
+        <v>41</v>
+      </c>
+      <c r="D193" t="s">
+        <v>47</v>
+      </c>
+      <c r="E193" t="s">
+        <v>64</v>
+      </c>
+      <c r="F193" t="s">
+        <v>85</v>
+      </c>
+      <c r="G193">
+        <v>304</v>
+      </c>
+      <c r="H193" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I193" s="2">
+        <v>46207.50067129629</v>
+      </c>
+      <c r="J193">
+        <v>1.655153302224898</v>
+      </c>
+      <c r="K193">
+        <v>1.655153302224898</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11">
+      <c r="A194" t="s">
+        <v>11</v>
+      </c>
+      <c r="B194" t="s">
+        <v>14</v>
+      </c>
+      <c r="C194" t="s">
+        <v>41</v>
+      </c>
+      <c r="D194" t="s">
+        <v>47</v>
+      </c>
+      <c r="E194" t="s">
+        <v>64</v>
+      </c>
+      <c r="F194" t="s">
+        <v>90</v>
+      </c>
+      <c r="G194">
+        <v>308</v>
+      </c>
+      <c r="H194" s="2">
+        <v>46211.69054398148</v>
+      </c>
+      <c r="I194" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J194">
+        <v>2.077295089828365</v>
+      </c>
+      <c r="K194">
+        <v>2.077295089828365</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11">
+      <c r="A195" t="s">
+        <v>11</v>
+      </c>
+      <c r="B195" t="s">
+        <v>14</v>
+      </c>
+      <c r="C195" t="s">
+        <v>41</v>
+      </c>
+      <c r="D195" t="s">
+        <v>48</v>
+      </c>
+      <c r="E195" t="s">
+        <v>62</v>
+      </c>
+      <c r="F195" t="s">
+        <v>65</v>
+      </c>
+      <c r="G195">
+        <v>101</v>
+      </c>
+      <c r="H195" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I195" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J195">
+        <v>2.231945425056128</v>
+      </c>
+      <c r="K195">
+        <v>2.231945425056128</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11">
+      <c r="A196" t="s">
+        <v>11</v>
+      </c>
+      <c r="B196" t="s">
+        <v>14</v>
+      </c>
+      <c r="C196" t="s">
+        <v>41</v>
+      </c>
+      <c r="D196" t="s">
+        <v>48</v>
+      </c>
+      <c r="E196" t="s">
+        <v>63</v>
+      </c>
+      <c r="F196" t="s">
+        <v>81</v>
+      </c>
+      <c r="G196">
+        <v>201</v>
+      </c>
+      <c r="H196" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I196" s="2">
+        <v>46207.50067129629</v>
+      </c>
+      <c r="J196">
+        <v>2.095109041186042</v>
+      </c>
+      <c r="K196">
+        <v>2.095109041186042</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11">
+      <c r="A197" t="s">
+        <v>11</v>
+      </c>
+      <c r="B197" t="s">
+        <v>14</v>
+      </c>
+      <c r="C197" t="s">
+        <v>41</v>
+      </c>
+      <c r="D197" t="s">
+        <v>48</v>
+      </c>
+      <c r="E197" t="s">
+        <v>63</v>
+      </c>
+      <c r="F197" t="s">
+        <v>87</v>
+      </c>
+      <c r="G197">
+        <v>202</v>
+      </c>
+      <c r="H197" s="2">
+        <v>46211.69054398148</v>
+      </c>
+      <c r="I197" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J197">
+        <v>2.439675648934623</v>
+      </c>
+      <c r="K197">
+        <v>2.439675648934623</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11">
+      <c r="A198" t="s">
+        <v>11</v>
+      </c>
+      <c r="B198" t="s">
+        <v>14</v>
+      </c>
+      <c r="C198" t="s">
+        <v>41</v>
+      </c>
+      <c r="D198" t="s">
+        <v>48</v>
+      </c>
+      <c r="E198" t="s">
+        <v>64</v>
+      </c>
+      <c r="F198" t="s">
+        <v>85</v>
+      </c>
+      <c r="G198">
+        <v>304</v>
+      </c>
+      <c r="H198" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I198" s="2">
+        <v>46207.50067129629</v>
+      </c>
+      <c r="J198">
+        <v>2.095109041186042</v>
+      </c>
+      <c r="K198">
+        <v>2.095109041186042</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11">
+      <c r="A199" t="s">
+        <v>11</v>
+      </c>
+      <c r="B199" t="s">
+        <v>14</v>
+      </c>
+      <c r="C199" t="s">
+        <v>41</v>
+      </c>
+      <c r="D199" t="s">
+        <v>48</v>
+      </c>
+      <c r="E199" t="s">
+        <v>64</v>
+      </c>
+      <c r="F199" t="s">
+        <v>90</v>
+      </c>
+      <c r="G199">
+        <v>308</v>
+      </c>
+      <c r="H199" s="2">
+        <v>46211.69054398148</v>
+      </c>
+      <c r="I199" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J199">
+        <v>2.439675648934623</v>
+      </c>
+      <c r="K199">
+        <v>2.439675648934623</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11">
+      <c r="A200" t="s">
+        <v>11</v>
+      </c>
+      <c r="B200" t="s">
+        <v>14</v>
+      </c>
+      <c r="C200" t="s">
+        <v>42</v>
+      </c>
+      <c r="D200" t="s">
+        <v>49</v>
+      </c>
+      <c r="E200" t="s">
+        <v>62</v>
+      </c>
+      <c r="F200" t="s">
+        <v>65</v>
+      </c>
+      <c r="G200">
+        <v>101</v>
+      </c>
+      <c r="H200" s="2">
+        <v>46209.54386574074</v>
+      </c>
+      <c r="I200" s="2">
+        <v>46214.6469212963</v>
+      </c>
+      <c r="J200">
+        <v>4.481333785255095</v>
+      </c>
+      <c r="K200">
+        <v>4.481333785255095</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11">
+      <c r="A201" t="s">
+        <v>11</v>
+      </c>
+      <c r="B201" t="s">
+        <v>14</v>
+      </c>
+      <c r="C201" t="s">
+        <v>42</v>
+      </c>
+      <c r="D201" t="s">
+        <v>49</v>
+      </c>
+      <c r="E201" t="s">
+        <v>63</v>
+      </c>
+      <c r="F201" t="s">
+        <v>87</v>
+      </c>
+      <c r="G201">
+        <v>202</v>
+      </c>
+      <c r="H201" s="2">
+        <v>46209.54386574074</v>
+      </c>
+      <c r="I201" s="2">
+        <v>46214.6469212963</v>
+      </c>
+      <c r="J201">
+        <v>4.481333785255095</v>
+      </c>
+      <c r="K201">
+        <v>4.481333785255095</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11">
+      <c r="A202" t="s">
+        <v>11</v>
+      </c>
+      <c r="B202" t="s">
+        <v>14</v>
+      </c>
+      <c r="C202" t="s">
+        <v>42</v>
+      </c>
+      <c r="D202" t="s">
+        <v>49</v>
+      </c>
+      <c r="E202" t="s">
+        <v>64</v>
+      </c>
+      <c r="F202" t="s">
+        <v>88</v>
+      </c>
+      <c r="G202">
+        <v>306</v>
+      </c>
+      <c r="H202" s="2">
+        <v>46209.54386574074</v>
+      </c>
+      <c r="I202" s="2">
+        <v>46209.56375</v>
+      </c>
+      <c r="J202">
+        <v>4.852419037731009</v>
+      </c>
+      <c r="K202">
+        <v>4.852419037731009</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11">
+      <c r="A203" t="s">
+        <v>11</v>
+      </c>
+      <c r="B203" t="s">
+        <v>14</v>
+      </c>
+      <c r="C203" t="s">
+        <v>42</v>
+      </c>
+      <c r="D203" t="s">
+        <v>49</v>
+      </c>
+      <c r="E203" t="s">
+        <v>64</v>
+      </c>
+      <c r="F203" t="s">
+        <v>91</v>
+      </c>
+      <c r="G203">
         <v>309</v>
       </c>
-      <c r="H190" s="2">
+      <c r="H203" s="2">
+        <v>46212.04517361111</v>
+      </c>
+      <c r="I203" s="2">
+        <v>46212.06122685185</v>
+      </c>
+      <c r="J203">
+        <v>6.128563787472934</v>
+      </c>
+      <c r="K203">
+        <v>6.128563787472934</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11">
+      <c r="A204" t="s">
+        <v>11</v>
+      </c>
+      <c r="B204" t="s">
+        <v>14</v>
+      </c>
+      <c r="C204" t="s">
+        <v>42</v>
+      </c>
+      <c r="D204" t="s">
+        <v>49</v>
+      </c>
+      <c r="E204" t="s">
+        <v>64</v>
+      </c>
+      <c r="F204" t="s">
+        <v>92</v>
+      </c>
+      <c r="G204">
+        <v>310</v>
+      </c>
+      <c r="H204" s="2">
+        <v>46214.64324074074</v>
+      </c>
+      <c r="I204" s="2">
+        <v>46214.6469212963</v>
+      </c>
+      <c r="J204">
+        <v>6.26483090226033</v>
+      </c>
+      <c r="K204">
+        <v>6.26483090226033</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11">
+      <c r="A205" t="s">
+        <v>11</v>
+      </c>
+      <c r="B205" t="s">
+        <v>14</v>
+      </c>
+      <c r="C205" t="s">
+        <v>43</v>
+      </c>
+      <c r="D205" t="s">
+        <v>44</v>
+      </c>
+      <c r="E205" t="s">
+        <v>62</v>
+      </c>
+      <c r="F205" t="s">
+        <v>65</v>
+      </c>
+      <c r="G205">
+        <v>101</v>
+      </c>
+      <c r="H205" s="2">
+        <v>46209.94287037037</v>
+      </c>
+      <c r="I205" s="2">
+        <v>46212.06846064814</v>
+      </c>
+      <c r="J205">
+        <v>1.583345850457788</v>
+      </c>
+      <c r="K205">
+        <v>1.583345850457788</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11">
+      <c r="A206" t="s">
+        <v>11</v>
+      </c>
+      <c r="B206" t="s">
+        <v>14</v>
+      </c>
+      <c r="C206" t="s">
+        <v>43</v>
+      </c>
+      <c r="D206" t="s">
+        <v>44</v>
+      </c>
+      <c r="E206" t="s">
+        <v>63</v>
+      </c>
+      <c r="F206" t="s">
+        <v>87</v>
+      </c>
+      <c r="G206">
+        <v>202</v>
+      </c>
+      <c r="H206" s="2">
+        <v>46209.94287037037</v>
+      </c>
+      <c r="I206" s="2">
+        <v>46212.06846064814</v>
+      </c>
+      <c r="J206">
+        <v>1.583345850457788</v>
+      </c>
+      <c r="K206">
+        <v>1.583345850457788</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11">
+      <c r="A207" t="s">
+        <v>11</v>
+      </c>
+      <c r="B207" t="s">
+        <v>14</v>
+      </c>
+      <c r="C207" t="s">
+        <v>43</v>
+      </c>
+      <c r="D207" t="s">
+        <v>44</v>
+      </c>
+      <c r="E207" t="s">
+        <v>64</v>
+      </c>
+      <c r="F207" t="s">
+        <v>88</v>
+      </c>
+      <c r="G207">
+        <v>306</v>
+      </c>
+      <c r="H207" s="2">
+        <v>46209.94287037037</v>
+      </c>
+      <c r="I207" s="2">
+        <v>46209.95513888889</v>
+      </c>
+      <c r="J207">
+        <v>1.886380431790312</v>
+      </c>
+      <c r="K207">
+        <v>1.886380431790312</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11">
+      <c r="A208" t="s">
+        <v>11</v>
+      </c>
+      <c r="B208" t="s">
+        <v>14</v>
+      </c>
+      <c r="C208" t="s">
+        <v>43</v>
+      </c>
+      <c r="D208" t="s">
+        <v>44</v>
+      </c>
+      <c r="E208" t="s">
+        <v>64</v>
+      </c>
+      <c r="F208" t="s">
+        <v>91</v>
+      </c>
+      <c r="G208">
+        <v>309</v>
+      </c>
+      <c r="H208" s="2">
         <v>46212.05592592592</v>
       </c>
-      <c r="I190" s="2">
+      <c r="I208" s="2">
         <v>46212.06846064814</v>
       </c>
-      <c r="J190">
+      <c r="J208">
         <v>1.611175198849116</v>
       </c>
-      <c r="K190">
+      <c r="K208">
         <v>1.611175198849116</v>
       </c>
     </row>

--- a/resources/M626/spc_cpk_detail.xlsx
+++ b/resources/M626/spc_cpk_detail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="98">
   <si>
     <t>prod_code</t>
   </si>
@@ -55,12 +55,162 @@
     <t>ARRAY</t>
   </si>
   <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
     <t>10140</t>
   </si>
   <si>
+    <t>10840</t>
+  </si>
+  <si>
+    <t>10841</t>
+  </si>
+  <si>
+    <t>11140</t>
+  </si>
+  <si>
+    <t>11450</t>
+  </si>
+  <si>
+    <t>11650</t>
+  </si>
+  <si>
+    <t>12140</t>
+  </si>
+  <si>
+    <t>12260</t>
+  </si>
+  <si>
+    <t>12450</t>
+  </si>
+  <si>
+    <t>13140</t>
+  </si>
+  <si>
+    <t>13260</t>
+  </si>
+  <si>
+    <t>13650</t>
+  </si>
+  <si>
+    <t>14140</t>
+  </si>
+  <si>
+    <t>14450</t>
+  </si>
+  <si>
+    <t>14650</t>
+  </si>
+  <si>
+    <t>1K140</t>
+  </si>
+  <si>
+    <t>1K141</t>
+  </si>
+  <si>
+    <t>1K260</t>
+  </si>
+  <si>
+    <t>21230</t>
+  </si>
+  <si>
+    <t>21240</t>
+  </si>
+  <si>
+    <t>41140</t>
+  </si>
+  <si>
+    <t>41260</t>
+  </si>
+  <si>
+    <t>41450</t>
+  </si>
+  <si>
+    <t>41650</t>
+  </si>
+  <si>
+    <t>42140</t>
+  </si>
+  <si>
+    <t>42450</t>
+  </si>
+  <si>
+    <t>42650</t>
+  </si>
+  <si>
+    <t>43260</t>
+  </si>
+  <si>
+    <t>43450</t>
+  </si>
+  <si>
+    <t>43650</t>
+  </si>
+  <si>
+    <t>44040</t>
+  </si>
+  <si>
     <t>SE_L1T</t>
   </si>
   <si>
+    <t>SE_L1T_UNI</t>
+  </si>
+  <si>
+    <t>SE_L2T</t>
+  </si>
+  <si>
+    <t>OVL1_X</t>
+  </si>
+  <si>
+    <t>OVL1_Y</t>
+  </si>
+  <si>
+    <t>CD1</t>
+  </si>
+  <si>
+    <t>4PP_Rs</t>
+  </si>
+  <si>
+    <t>SE_L2T_UNI</t>
+  </si>
+  <si>
+    <t>B_0_CIE_Y</t>
+  </si>
+  <si>
+    <t>Bi_0</t>
+  </si>
+  <si>
+    <t>G_0_CIE_X</t>
+  </si>
+  <si>
+    <t>G_0_E</t>
+  </si>
+  <si>
+    <t>R_0_CIE_X</t>
+  </si>
+  <si>
+    <t>R_0_E</t>
+  </si>
+  <si>
+    <t>SE_CVD1_N_1</t>
+  </si>
+  <si>
+    <t>SE_CVD1_T_TOTAL</t>
+  </si>
+  <si>
+    <t>SE_CVD2_N_2</t>
+  </si>
+  <si>
+    <t>SE_CVD2_T_TOTAL</t>
+  </si>
+  <si>
+    <t>SR_IJP1_T_1</t>
+  </si>
+  <si>
     <t>month</t>
   </si>
   <si>
@@ -92,6 +242,72 @@
   </si>
   <si>
     <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-W27</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-W28</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
   </si>
 </sst>
 </file>
@@ -453,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K246"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -499,16 +715,16 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G2">
         <v>101</v>
@@ -534,16 +750,16 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="G3">
         <v>102</v>
@@ -569,16 +785,16 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G4">
         <v>203</v>
@@ -604,16 +820,16 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="G5">
         <v>204</v>
@@ -639,16 +855,16 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="G6">
         <v>205</v>
@@ -674,16 +890,16 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G7">
         <v>313</v>
@@ -709,16 +925,16 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="G8">
         <v>314</v>
@@ -744,16 +960,16 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G9">
         <v>322</v>
@@ -769,6 +985,8301 @@
       </c>
       <c r="K9">
         <v>1.573823940369902</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10">
+        <v>101</v>
+      </c>
+      <c r="H10" s="2">
+        <v>46229.25797453704</v>
+      </c>
+      <c r="I10" s="2">
+        <v>46230.72840277778</v>
+      </c>
+      <c r="J10">
+        <v>2.114471685643166</v>
+      </c>
+      <c r="K10">
+        <v>2.114471685643166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11">
+        <v>102</v>
+      </c>
+      <c r="H11" s="2">
+        <v>46238.87356481481</v>
+      </c>
+      <c r="I11" s="2">
+        <v>46238.89697916667</v>
+      </c>
+      <c r="J11">
+        <v>1.142303932752751</v>
+      </c>
+      <c r="K11">
+        <v>1.142303932752751</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12">
+        <v>203</v>
+      </c>
+      <c r="H12" s="2">
+        <v>46229.25797453704</v>
+      </c>
+      <c r="I12" s="2">
+        <v>46229.28137731482</v>
+      </c>
+      <c r="J12">
+        <v>2.568225869520761</v>
+      </c>
+      <c r="K12">
+        <v>2.568225869520761</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13">
+        <v>204</v>
+      </c>
+      <c r="H13" s="2">
+        <v>46230.70472222222</v>
+      </c>
+      <c r="I13" s="2">
+        <v>46230.72840277778</v>
+      </c>
+      <c r="J13">
+        <v>3.432082291370995</v>
+      </c>
+      <c r="K13">
+        <v>3.432082291370995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14">
+        <v>205</v>
+      </c>
+      <c r="H14" s="2">
+        <v>46238.87356481481</v>
+      </c>
+      <c r="I14" s="2">
+        <v>46238.89697916667</v>
+      </c>
+      <c r="J14">
+        <v>1.142303932752751</v>
+      </c>
+      <c r="K14">
+        <v>1.142303932752751</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15">
+        <v>313</v>
+      </c>
+      <c r="H15" s="2">
+        <v>46229.25797453704</v>
+      </c>
+      <c r="I15" s="2">
+        <v>46229.28137731482</v>
+      </c>
+      <c r="J15">
+        <v>2.568225869520761</v>
+      </c>
+      <c r="K15">
+        <v>2.568225869520761</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16">
+        <v>314</v>
+      </c>
+      <c r="H16" s="2">
+        <v>46230.70472222222</v>
+      </c>
+      <c r="I16" s="2">
+        <v>46230.72840277778</v>
+      </c>
+      <c r="J16">
+        <v>3.432082291370995</v>
+      </c>
+      <c r="K16">
+        <v>3.432082291370995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17">
+        <v>322</v>
+      </c>
+      <c r="H17" s="2">
+        <v>46238.87356481481</v>
+      </c>
+      <c r="I17" s="2">
+        <v>46238.89697916667</v>
+      </c>
+      <c r="J17">
+        <v>1.142303932752751</v>
+      </c>
+      <c r="K17">
+        <v>1.142303932752751</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18">
+        <v>101</v>
+      </c>
+      <c r="H18" s="2">
+        <v>46227.65413194444</v>
+      </c>
+      <c r="I18" s="2">
+        <v>46230.690625</v>
+      </c>
+      <c r="J18">
+        <v>2.857014697210175</v>
+      </c>
+      <c r="K18">
+        <v>2.857014697210175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19">
+        <v>102</v>
+      </c>
+      <c r="H19" s="2">
+        <v>46236.92053240741</v>
+      </c>
+      <c r="I19" s="2">
+        <v>46239.94694444445</v>
+      </c>
+      <c r="J19">
+        <v>2.317833835322944</v>
+      </c>
+      <c r="K19">
+        <v>2.317833835322944</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20">
+        <v>203</v>
+      </c>
+      <c r="H20" s="2">
+        <v>46227.65413194444</v>
+      </c>
+      <c r="I20" s="2">
+        <v>46227.67450231482</v>
+      </c>
+      <c r="J20">
+        <v>2.610324736578181</v>
+      </c>
+      <c r="K20">
+        <v>2.610324736578181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21">
+        <v>204</v>
+      </c>
+      <c r="H21" s="2">
+        <v>46230.67019675926</v>
+      </c>
+      <c r="I21" s="2">
+        <v>46236.9412037037</v>
+      </c>
+      <c r="J21">
+        <v>2.747286676522166</v>
+      </c>
+      <c r="K21">
+        <v>2.747286676522166</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22">
+        <v>205</v>
+      </c>
+      <c r="H22" s="2">
+        <v>46238.16710648148</v>
+      </c>
+      <c r="I22" s="2">
+        <v>46239.94694444445</v>
+      </c>
+      <c r="J22">
+        <v>2.236868217249275</v>
+      </c>
+      <c r="K22">
+        <v>2.236868217249275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23">
+        <v>311</v>
+      </c>
+      <c r="H23" s="2">
+        <v>46227.65413194444</v>
+      </c>
+      <c r="I23" s="2">
+        <v>46227.67450231482</v>
+      </c>
+      <c r="J23">
+        <v>2.610324736578181</v>
+      </c>
+      <c r="K23">
+        <v>2.610324736578181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24">
+        <v>314</v>
+      </c>
+      <c r="H24" s="2">
+        <v>46230.67019675926</v>
+      </c>
+      <c r="I24" s="2">
+        <v>46230.690625</v>
+      </c>
+      <c r="J24">
+        <v>3.18504489087568</v>
+      </c>
+      <c r="K24">
+        <v>3.18504489087568</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25">
+        <v>320</v>
+      </c>
+      <c r="H25" s="2">
+        <v>46236.92053240741</v>
+      </c>
+      <c r="I25" s="2">
+        <v>46236.9412037037</v>
+      </c>
+      <c r="J25">
+        <v>2.51050409594928</v>
+      </c>
+      <c r="K25">
+        <v>2.51050409594928</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26">
+        <v>322</v>
+      </c>
+      <c r="H26" s="2">
+        <v>46238.16710648148</v>
+      </c>
+      <c r="I26" s="2">
+        <v>46238.18784722222</v>
+      </c>
+      <c r="J26">
+        <v>2.007375883971602</v>
+      </c>
+      <c r="K26">
+        <v>2.007375883971602</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" t="s">
+        <v>78</v>
+      </c>
+      <c r="G27">
+        <v>323</v>
+      </c>
+      <c r="H27" s="2">
+        <v>46239.92627314815</v>
+      </c>
+      <c r="I27" s="2">
+        <v>46239.94694444445</v>
+      </c>
+      <c r="J27">
+        <v>2.567108211495932</v>
+      </c>
+      <c r="K27">
+        <v>2.567108211495932</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28">
+        <v>101</v>
+      </c>
+      <c r="H28" s="2">
+        <v>46231.38151620371</v>
+      </c>
+      <c r="I28" s="2">
+        <v>46231.49174768518</v>
+      </c>
+      <c r="J28">
+        <v>2.328525056544569</v>
+      </c>
+      <c r="K28">
+        <v>2.328525056544569</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29">
+        <v>102</v>
+      </c>
+      <c r="H29" s="2">
+        <v>46238.72258101852</v>
+      </c>
+      <c r="I29" s="2">
+        <v>46238.74269675926</v>
+      </c>
+      <c r="J29">
+        <v>2.941426094557433</v>
+      </c>
+      <c r="K29">
+        <v>2.941426094557433</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" t="s">
+        <v>66</v>
+      </c>
+      <c r="F30" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30">
+        <v>204</v>
+      </c>
+      <c r="H30" s="2">
+        <v>46231.38151620371</v>
+      </c>
+      <c r="I30" s="2">
+        <v>46231.49174768518</v>
+      </c>
+      <c r="J30">
+        <v>2.328525056544569</v>
+      </c>
+      <c r="K30">
+        <v>2.328525056544569</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" t="s">
+        <v>66</v>
+      </c>
+      <c r="F31" t="s">
+        <v>72</v>
+      </c>
+      <c r="G31">
+        <v>205</v>
+      </c>
+      <c r="H31" s="2">
+        <v>46238.72258101852</v>
+      </c>
+      <c r="I31" s="2">
+        <v>46238.74269675926</v>
+      </c>
+      <c r="J31">
+        <v>2.941426094557433</v>
+      </c>
+      <c r="K31">
+        <v>2.941426094557433</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32" t="s">
+        <v>79</v>
+      </c>
+      <c r="G32">
+        <v>315</v>
+      </c>
+      <c r="H32" s="2">
+        <v>46231.38151620371</v>
+      </c>
+      <c r="I32" s="2">
+        <v>46231.49174768518</v>
+      </c>
+      <c r="J32">
+        <v>2.328525056544569</v>
+      </c>
+      <c r="K32">
+        <v>2.328525056544569</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33">
+        <v>322</v>
+      </c>
+      <c r="H33" s="2">
+        <v>46238.72258101852</v>
+      </c>
+      <c r="I33" s="2">
+        <v>46238.74269675926</v>
+      </c>
+      <c r="J33">
+        <v>2.941426094557433</v>
+      </c>
+      <c r="K33">
+        <v>2.941426094557433</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" t="s">
+        <v>68</v>
+      </c>
+      <c r="G34">
+        <v>101</v>
+      </c>
+      <c r="H34" s="2">
+        <v>46230.99207175926</v>
+      </c>
+      <c r="I34" s="2">
+        <v>46231.02504629629</v>
+      </c>
+      <c r="J34">
+        <v>1.355116472981333</v>
+      </c>
+      <c r="K34">
+        <v>1.355116472981333</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" t="s">
+        <v>66</v>
+      </c>
+      <c r="F35" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35">
+        <v>204</v>
+      </c>
+      <c r="H35" s="2">
+        <v>46230.99207175926</v>
+      </c>
+      <c r="I35" s="2">
+        <v>46231.02504629629</v>
+      </c>
+      <c r="J35">
+        <v>1.355116472981333</v>
+      </c>
+      <c r="K35">
+        <v>1.355116472981333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36">
+        <v>314</v>
+      </c>
+      <c r="H36" s="2">
+        <v>46230.99207175926</v>
+      </c>
+      <c r="I36" s="2">
+        <v>46230.99207175926</v>
+      </c>
+      <c r="J36">
+        <v>2.066936758739828</v>
+      </c>
+      <c r="K36">
+        <v>2.066936758739828</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G37">
+        <v>315</v>
+      </c>
+      <c r="H37" s="2">
+        <v>46231.00037037037</v>
+      </c>
+      <c r="I37" s="2">
+        <v>46231.02504629629</v>
+      </c>
+      <c r="J37">
+        <v>1.27303707618806</v>
+      </c>
+      <c r="K37">
+        <v>1.27303707618806</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" t="s">
+        <v>68</v>
+      </c>
+      <c r="G38">
+        <v>101</v>
+      </c>
+      <c r="H38" s="2">
+        <v>46232.64699074074</v>
+      </c>
+      <c r="I38" s="2">
+        <v>46232.67614583333</v>
+      </c>
+      <c r="J38">
+        <v>1.689085678154552</v>
+      </c>
+      <c r="K38">
+        <v>1.689085678154552</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" t="s">
+        <v>65</v>
+      </c>
+      <c r="F39" t="s">
+        <v>69</v>
+      </c>
+      <c r="G39">
+        <v>102</v>
+      </c>
+      <c r="H39" s="2">
+        <v>46239.42922453704</v>
+      </c>
+      <c r="I39" s="2">
+        <v>46239.44978009259</v>
+      </c>
+      <c r="J39">
+        <v>1.573401321507338</v>
+      </c>
+      <c r="K39">
+        <v>1.573401321507338</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" t="s">
+        <v>66</v>
+      </c>
+      <c r="F40" t="s">
+        <v>71</v>
+      </c>
+      <c r="G40">
+        <v>204</v>
+      </c>
+      <c r="H40" s="2">
+        <v>46232.64699074074</v>
+      </c>
+      <c r="I40" s="2">
+        <v>46232.67614583333</v>
+      </c>
+      <c r="J40">
+        <v>1.689085678154552</v>
+      </c>
+      <c r="K40">
+        <v>1.689085678154552</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" t="s">
+        <v>66</v>
+      </c>
+      <c r="F41" t="s">
+        <v>72</v>
+      </c>
+      <c r="G41">
+        <v>205</v>
+      </c>
+      <c r="H41" s="2">
+        <v>46239.42922453704</v>
+      </c>
+      <c r="I41" s="2">
+        <v>46239.44978009259</v>
+      </c>
+      <c r="J41">
+        <v>1.573401321507338</v>
+      </c>
+      <c r="K41">
+        <v>1.573401321507338</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" t="s">
+        <v>67</v>
+      </c>
+      <c r="F42" t="s">
+        <v>80</v>
+      </c>
+      <c r="G42">
+        <v>316</v>
+      </c>
+      <c r="H42" s="2">
+        <v>46232.64699074074</v>
+      </c>
+      <c r="I42" s="2">
+        <v>46232.67614583333</v>
+      </c>
+      <c r="J42">
+        <v>1.689085678154552</v>
+      </c>
+      <c r="K42">
+        <v>1.689085678154552</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" t="s">
+        <v>49</v>
+      </c>
+      <c r="E43" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" t="s">
+        <v>78</v>
+      </c>
+      <c r="G43">
+        <v>323</v>
+      </c>
+      <c r="H43" s="2">
+        <v>46239.42922453704</v>
+      </c>
+      <c r="I43" s="2">
+        <v>46239.44978009259</v>
+      </c>
+      <c r="J43">
+        <v>1.573401321507338</v>
+      </c>
+      <c r="K43">
+        <v>1.573401321507338</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" t="s">
+        <v>50</v>
+      </c>
+      <c r="E44" t="s">
+        <v>65</v>
+      </c>
+      <c r="F44" t="s">
+        <v>68</v>
+      </c>
+      <c r="G44">
+        <v>101</v>
+      </c>
+      <c r="H44" s="2">
+        <v>46232.64699074074</v>
+      </c>
+      <c r="I44" s="2">
+        <v>46232.67614583333</v>
+      </c>
+      <c r="J44">
+        <v>1.448969911965588</v>
+      </c>
+      <c r="K44">
+        <v>1.448969911965588</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" t="s">
+        <v>65</v>
+      </c>
+      <c r="F45" t="s">
+        <v>69</v>
+      </c>
+      <c r="G45">
+        <v>102</v>
+      </c>
+      <c r="H45" s="2">
+        <v>46239.42922453704</v>
+      </c>
+      <c r="I45" s="2">
+        <v>46239.44978009259</v>
+      </c>
+      <c r="J45">
+        <v>1.359936468560095</v>
+      </c>
+      <c r="K45">
+        <v>1.359936468560095</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46" t="s">
+        <v>66</v>
+      </c>
+      <c r="F46" t="s">
+        <v>71</v>
+      </c>
+      <c r="G46">
+        <v>204</v>
+      </c>
+      <c r="H46" s="2">
+        <v>46232.64699074074</v>
+      </c>
+      <c r="I46" s="2">
+        <v>46232.67614583333</v>
+      </c>
+      <c r="J46">
+        <v>1.448969911965588</v>
+      </c>
+      <c r="K46">
+        <v>1.448969911965588</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" t="s">
+        <v>66</v>
+      </c>
+      <c r="F47" t="s">
+        <v>72</v>
+      </c>
+      <c r="G47">
+        <v>205</v>
+      </c>
+      <c r="H47" s="2">
+        <v>46239.42922453704</v>
+      </c>
+      <c r="I47" s="2">
+        <v>46239.44978009259</v>
+      </c>
+      <c r="J47">
+        <v>1.359936468560095</v>
+      </c>
+      <c r="K47">
+        <v>1.359936468560095</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" t="s">
+        <v>50</v>
+      </c>
+      <c r="E48" t="s">
+        <v>67</v>
+      </c>
+      <c r="F48" t="s">
+        <v>80</v>
+      </c>
+      <c r="G48">
+        <v>316</v>
+      </c>
+      <c r="H48" s="2">
+        <v>46232.64699074074</v>
+      </c>
+      <c r="I48" s="2">
+        <v>46232.67614583333</v>
+      </c>
+      <c r="J48">
+        <v>1.448969911965588</v>
+      </c>
+      <c r="K48">
+        <v>1.448969911965588</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" t="s">
+        <v>50</v>
+      </c>
+      <c r="E49" t="s">
+        <v>67</v>
+      </c>
+      <c r="F49" t="s">
+        <v>78</v>
+      </c>
+      <c r="G49">
+        <v>323</v>
+      </c>
+      <c r="H49" s="2">
+        <v>46239.42922453704</v>
+      </c>
+      <c r="I49" s="2">
+        <v>46239.44978009259</v>
+      </c>
+      <c r="J49">
+        <v>1.359936468560095</v>
+      </c>
+      <c r="K49">
+        <v>1.359936468560095</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" t="s">
+        <v>51</v>
+      </c>
+      <c r="E50" t="s">
+        <v>65</v>
+      </c>
+      <c r="F50" t="s">
+        <v>68</v>
+      </c>
+      <c r="G50">
+        <v>101</v>
+      </c>
+      <c r="H50" s="2">
+        <v>46233.43511574074</v>
+      </c>
+      <c r="I50" s="2">
+        <v>46233.44659722222</v>
+      </c>
+      <c r="J50">
+        <v>2.091238629017446</v>
+      </c>
+      <c r="K50">
+        <v>2.091238629017446</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" t="s">
+        <v>51</v>
+      </c>
+      <c r="E51" t="s">
+        <v>66</v>
+      </c>
+      <c r="F51" t="s">
+        <v>71</v>
+      </c>
+      <c r="G51">
+        <v>204</v>
+      </c>
+      <c r="H51" s="2">
+        <v>46233.43511574074</v>
+      </c>
+      <c r="I51" s="2">
+        <v>46233.44659722222</v>
+      </c>
+      <c r="J51">
+        <v>2.091238629017446</v>
+      </c>
+      <c r="K51">
+        <v>2.091238629017446</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52" t="s">
+        <v>67</v>
+      </c>
+      <c r="F52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G52">
+        <v>317</v>
+      </c>
+      <c r="H52" s="2">
+        <v>46233.43511574074</v>
+      </c>
+      <c r="I52" s="2">
+        <v>46233.44659722222</v>
+      </c>
+      <c r="J52">
+        <v>2.091238629017446</v>
+      </c>
+      <c r="K52">
+        <v>2.091238629017446</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" t="s">
+        <v>65</v>
+      </c>
+      <c r="F53" t="s">
+        <v>68</v>
+      </c>
+      <c r="G53">
+        <v>101</v>
+      </c>
+      <c r="H53" s="2">
+        <v>46233.43431712963</v>
+      </c>
+      <c r="I53" s="2">
+        <v>46234.12956018518</v>
+      </c>
+      <c r="J53">
+        <v>1.572584646537667</v>
+      </c>
+      <c r="K53">
+        <v>1.572584646537667</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" t="s">
+        <v>66</v>
+      </c>
+      <c r="F54" t="s">
+        <v>71</v>
+      </c>
+      <c r="G54">
+        <v>204</v>
+      </c>
+      <c r="H54" s="2">
+        <v>46233.43431712963</v>
+      </c>
+      <c r="I54" s="2">
+        <v>46234.12956018518</v>
+      </c>
+      <c r="J54">
+        <v>1.572584646537667</v>
+      </c>
+      <c r="K54">
+        <v>1.572584646537667</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" t="s">
+        <v>46</v>
+      </c>
+      <c r="E55" t="s">
+        <v>67</v>
+      </c>
+      <c r="F55" t="s">
+        <v>81</v>
+      </c>
+      <c r="G55">
+        <v>317</v>
+      </c>
+      <c r="H55" s="2">
+        <v>46233.43431712963</v>
+      </c>
+      <c r="I55" s="2">
+        <v>46233.45982638889</v>
+      </c>
+      <c r="J55">
+        <v>1.555987159748071</v>
+      </c>
+      <c r="K55">
+        <v>1.555987159748071</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" t="s">
+        <v>46</v>
+      </c>
+      <c r="E56" t="s">
+        <v>67</v>
+      </c>
+      <c r="F56" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56">
+        <v>318</v>
+      </c>
+      <c r="H56" s="2">
+        <v>46234.10409722223</v>
+      </c>
+      <c r="I56" s="2">
+        <v>46234.12956018518</v>
+      </c>
+      <c r="J56">
+        <v>1.59320100523079</v>
+      </c>
+      <c r="K56">
+        <v>1.59320100523079</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>52</v>
+      </c>
+      <c r="E57" t="s">
+        <v>65</v>
+      </c>
+      <c r="F57" t="s">
+        <v>68</v>
+      </c>
+      <c r="G57">
+        <v>101</v>
+      </c>
+      <c r="H57" s="2">
+        <v>46234.04664351852</v>
+      </c>
+      <c r="I57" s="2">
+        <v>46234.05206018518</v>
+      </c>
+      <c r="J57">
+        <v>2.414612658349697</v>
+      </c>
+      <c r="K57">
+        <v>2.414612658349697</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
+        <v>52</v>
+      </c>
+      <c r="E58" t="s">
+        <v>66</v>
+      </c>
+      <c r="F58" t="s">
+        <v>71</v>
+      </c>
+      <c r="G58">
+        <v>204</v>
+      </c>
+      <c r="H58" s="2">
+        <v>46234.04664351852</v>
+      </c>
+      <c r="I58" s="2">
+        <v>46234.05206018518</v>
+      </c>
+      <c r="J58">
+        <v>2.414612658349697</v>
+      </c>
+      <c r="K58">
+        <v>2.414612658349697</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>52</v>
+      </c>
+      <c r="E59" t="s">
+        <v>67</v>
+      </c>
+      <c r="F59" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59">
+        <v>318</v>
+      </c>
+      <c r="H59" s="2">
+        <v>46234.04664351852</v>
+      </c>
+      <c r="I59" s="2">
+        <v>46234.05206018518</v>
+      </c>
+      <c r="J59">
+        <v>2.414612658349697</v>
+      </c>
+      <c r="K59">
+        <v>2.414612658349697</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" t="s">
+        <v>49</v>
+      </c>
+      <c r="E60" t="s">
+        <v>65</v>
+      </c>
+      <c r="F60" t="s">
+        <v>68</v>
+      </c>
+      <c r="G60">
+        <v>101</v>
+      </c>
+      <c r="H60" s="2">
+        <v>46233.89488425926</v>
+      </c>
+      <c r="I60" s="2">
+        <v>46233.92318287037</v>
+      </c>
+      <c r="J60">
+        <v>1.538698881093973</v>
+      </c>
+      <c r="K60">
+        <v>1.538698881093973</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" t="s">
+        <v>49</v>
+      </c>
+      <c r="E61" t="s">
+        <v>66</v>
+      </c>
+      <c r="F61" t="s">
+        <v>71</v>
+      </c>
+      <c r="G61">
+        <v>204</v>
+      </c>
+      <c r="H61" s="2">
+        <v>46233.89488425926</v>
+      </c>
+      <c r="I61" s="2">
+        <v>46233.92318287037</v>
+      </c>
+      <c r="J61">
+        <v>1.538698881093973</v>
+      </c>
+      <c r="K61">
+        <v>1.538698881093973</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" t="s">
+        <v>49</v>
+      </c>
+      <c r="E62" t="s">
+        <v>67</v>
+      </c>
+      <c r="F62" t="s">
+        <v>81</v>
+      </c>
+      <c r="G62">
+        <v>317</v>
+      </c>
+      <c r="H62" s="2">
+        <v>46233.89488425926</v>
+      </c>
+      <c r="I62" s="2">
+        <v>46233.92318287037</v>
+      </c>
+      <c r="J62">
+        <v>1.538698881093973</v>
+      </c>
+      <c r="K62">
+        <v>1.538698881093973</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" t="s">
+        <v>50</v>
+      </c>
+      <c r="E63" t="s">
+        <v>65</v>
+      </c>
+      <c r="F63" t="s">
+        <v>68</v>
+      </c>
+      <c r="G63">
+        <v>101</v>
+      </c>
+      <c r="H63" s="2">
+        <v>46233.89488425926</v>
+      </c>
+      <c r="I63" s="2">
+        <v>46233.92318287037</v>
+      </c>
+      <c r="J63">
+        <v>1.213053007796703</v>
+      </c>
+      <c r="K63">
+        <v>1.213053007796703</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" t="s">
+        <v>23</v>
+      </c>
+      <c r="D64" t="s">
+        <v>50</v>
+      </c>
+      <c r="E64" t="s">
+        <v>66</v>
+      </c>
+      <c r="F64" t="s">
+        <v>71</v>
+      </c>
+      <c r="G64">
+        <v>204</v>
+      </c>
+      <c r="H64" s="2">
+        <v>46233.89488425926</v>
+      </c>
+      <c r="I64" s="2">
+        <v>46233.92318287037</v>
+      </c>
+      <c r="J64">
+        <v>1.213053007796703</v>
+      </c>
+      <c r="K64">
+        <v>1.213053007796703</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" t="s">
+        <v>50</v>
+      </c>
+      <c r="E65" t="s">
+        <v>67</v>
+      </c>
+      <c r="F65" t="s">
+        <v>81</v>
+      </c>
+      <c r="G65">
+        <v>317</v>
+      </c>
+      <c r="H65" s="2">
+        <v>46233.89488425926</v>
+      </c>
+      <c r="I65" s="2">
+        <v>46233.92318287037</v>
+      </c>
+      <c r="J65">
+        <v>1.213053007796703</v>
+      </c>
+      <c r="K65">
+        <v>1.213053007796703</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" t="s">
+        <v>46</v>
+      </c>
+      <c r="E66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F66" t="s">
+        <v>69</v>
+      </c>
+      <c r="G66">
+        <v>102</v>
+      </c>
+      <c r="H66" s="2">
+        <v>46236.06453703704</v>
+      </c>
+      <c r="I66" s="2">
+        <v>46236.09925925926</v>
+      </c>
+      <c r="J66">
+        <v>2.267353328482443</v>
+      </c>
+      <c r="K66">
+        <v>2.267353328482443</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" t="s">
+        <v>46</v>
+      </c>
+      <c r="E67" t="s">
+        <v>66</v>
+      </c>
+      <c r="F67" t="s">
+        <v>71</v>
+      </c>
+      <c r="G67">
+        <v>204</v>
+      </c>
+      <c r="H67" s="2">
+        <v>46236.06453703704</v>
+      </c>
+      <c r="I67" s="2">
+        <v>46236.09925925926</v>
+      </c>
+      <c r="J67">
+        <v>2.267353328482443</v>
+      </c>
+      <c r="K67">
+        <v>2.267353328482443</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" t="s">
+        <v>46</v>
+      </c>
+      <c r="E68" t="s">
+        <v>67</v>
+      </c>
+      <c r="F68" t="s">
+        <v>77</v>
+      </c>
+      <c r="G68">
+        <v>320</v>
+      </c>
+      <c r="H68" s="2">
+        <v>46236.06453703704</v>
+      </c>
+      <c r="I68" s="2">
+        <v>46236.09925925926</v>
+      </c>
+      <c r="J68">
+        <v>2.267353328482443</v>
+      </c>
+      <c r="K68">
+        <v>2.267353328482443</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" t="s">
+        <v>25</v>
+      </c>
+      <c r="D69" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" t="s">
+        <v>65</v>
+      </c>
+      <c r="F69" t="s">
+        <v>69</v>
+      </c>
+      <c r="G69">
+        <v>102</v>
+      </c>
+      <c r="H69" s="2">
+        <v>46235.49434027778</v>
+      </c>
+      <c r="I69" s="2">
+        <v>46236.78883101852</v>
+      </c>
+      <c r="J69">
+        <v>1.750040761231219</v>
+      </c>
+      <c r="K69">
+        <v>1.750040761231219</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" t="s">
+        <v>52</v>
+      </c>
+      <c r="E70" t="s">
+        <v>66</v>
+      </c>
+      <c r="F70" t="s">
+        <v>71</v>
+      </c>
+      <c r="G70">
+        <v>204</v>
+      </c>
+      <c r="H70" s="2">
+        <v>46235.49434027778</v>
+      </c>
+      <c r="I70" s="2">
+        <v>46236.78883101852</v>
+      </c>
+      <c r="J70">
+        <v>1.750040761231219</v>
+      </c>
+      <c r="K70">
+        <v>1.750040761231219</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" t="s">
+        <v>52</v>
+      </c>
+      <c r="E71" t="s">
+        <v>67</v>
+      </c>
+      <c r="F71" t="s">
+        <v>83</v>
+      </c>
+      <c r="G71">
+        <v>319</v>
+      </c>
+      <c r="H71" s="2">
+        <v>46235.49434027778</v>
+      </c>
+      <c r="I71" s="2">
+        <v>46235.5078587963</v>
+      </c>
+      <c r="J71">
+        <v>1.874048601779144</v>
+      </c>
+      <c r="K71">
+        <v>1.874048601779144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" t="s">
+        <v>25</v>
+      </c>
+      <c r="D72" t="s">
+        <v>52</v>
+      </c>
+      <c r="E72" t="s">
+        <v>67</v>
+      </c>
+      <c r="F72" t="s">
+        <v>77</v>
+      </c>
+      <c r="G72">
+        <v>320</v>
+      </c>
+      <c r="H72" s="2">
+        <v>46236.78341435185</v>
+      </c>
+      <c r="I72" s="2">
+        <v>46236.78883101852</v>
+      </c>
+      <c r="J72">
+        <v>1.508683391254823</v>
+      </c>
+      <c r="K72">
+        <v>1.508683391254823</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>26</v>
+      </c>
+      <c r="D73" t="s">
+        <v>51</v>
+      </c>
+      <c r="E73" t="s">
+        <v>65</v>
+      </c>
+      <c r="F73" t="s">
+        <v>69</v>
+      </c>
+      <c r="G73">
+        <v>102</v>
+      </c>
+      <c r="H73" s="2">
+        <v>46238.68201388889</v>
+      </c>
+      <c r="I73" s="2">
+        <v>46238.68879629629</v>
+      </c>
+      <c r="J73">
+        <v>2.905559116600224</v>
+      </c>
+      <c r="K73">
+        <v>2.905559116600224</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" t="s">
+        <v>51</v>
+      </c>
+      <c r="E74" t="s">
+        <v>66</v>
+      </c>
+      <c r="F74" t="s">
+        <v>72</v>
+      </c>
+      <c r="G74">
+        <v>205</v>
+      </c>
+      <c r="H74" s="2">
+        <v>46238.68201388889</v>
+      </c>
+      <c r="I74" s="2">
+        <v>46238.68879629629</v>
+      </c>
+      <c r="J74">
+        <v>2.905559116600224</v>
+      </c>
+      <c r="K74">
+        <v>2.905559116600224</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" t="s">
+        <v>26</v>
+      </c>
+      <c r="D75" t="s">
+        <v>51</v>
+      </c>
+      <c r="E75" t="s">
+        <v>67</v>
+      </c>
+      <c r="F75" t="s">
+        <v>75</v>
+      </c>
+      <c r="G75">
+        <v>322</v>
+      </c>
+      <c r="H75" s="2">
+        <v>46238.68201388889</v>
+      </c>
+      <c r="I75" s="2">
+        <v>46238.68879629629</v>
+      </c>
+      <c r="J75">
+        <v>2.905559116600224</v>
+      </c>
+      <c r="K75">
+        <v>2.905559116600224</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" t="s">
+        <v>27</v>
+      </c>
+      <c r="D76" t="s">
+        <v>46</v>
+      </c>
+      <c r="E76" t="s">
+        <v>65</v>
+      </c>
+      <c r="F76" t="s">
+        <v>69</v>
+      </c>
+      <c r="G76">
+        <v>102</v>
+      </c>
+      <c r="H76" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I76" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J76">
+        <v>2.853604283911435</v>
+      </c>
+      <c r="K76">
+        <v>2.853604283911435</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77" t="s">
+        <v>46</v>
+      </c>
+      <c r="E77" t="s">
+        <v>66</v>
+      </c>
+      <c r="F77" t="s">
+        <v>72</v>
+      </c>
+      <c r="G77">
+        <v>205</v>
+      </c>
+      <c r="H77" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I77" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J77">
+        <v>2.853604283911435</v>
+      </c>
+      <c r="K77">
+        <v>2.853604283911435</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" t="s">
+        <v>27</v>
+      </c>
+      <c r="D78" t="s">
+        <v>46</v>
+      </c>
+      <c r="E78" t="s">
+        <v>67</v>
+      </c>
+      <c r="F78" t="s">
+        <v>75</v>
+      </c>
+      <c r="G78">
+        <v>322</v>
+      </c>
+      <c r="H78" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I78" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J78">
+        <v>2.853604283911435</v>
+      </c>
+      <c r="K78">
+        <v>2.853604283911435</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" t="s">
+        <v>27</v>
+      </c>
+      <c r="D79" t="s">
+        <v>47</v>
+      </c>
+      <c r="E79" t="s">
+        <v>65</v>
+      </c>
+      <c r="F79" t="s">
+        <v>69</v>
+      </c>
+      <c r="G79">
+        <v>102</v>
+      </c>
+      <c r="H79" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I79" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J79">
+        <v>4.973991129375084</v>
+      </c>
+      <c r="K79">
+        <v>4.973991129375084</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" t="s">
+        <v>27</v>
+      </c>
+      <c r="D80" t="s">
+        <v>47</v>
+      </c>
+      <c r="E80" t="s">
+        <v>66</v>
+      </c>
+      <c r="F80" t="s">
+        <v>72</v>
+      </c>
+      <c r="G80">
+        <v>205</v>
+      </c>
+      <c r="H80" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I80" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J80">
+        <v>4.973991129375084</v>
+      </c>
+      <c r="K80">
+        <v>4.973991129375084</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" t="s">
+        <v>27</v>
+      </c>
+      <c r="D81" t="s">
+        <v>47</v>
+      </c>
+      <c r="E81" t="s">
+        <v>67</v>
+      </c>
+      <c r="F81" t="s">
+        <v>75</v>
+      </c>
+      <c r="G81">
+        <v>322</v>
+      </c>
+      <c r="H81" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I81" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J81">
+        <v>4.973991129375084</v>
+      </c>
+      <c r="K81">
+        <v>4.973991129375084</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" t="s">
+        <v>27</v>
+      </c>
+      <c r="D82" t="s">
+        <v>48</v>
+      </c>
+      <c r="E82" t="s">
+        <v>65</v>
+      </c>
+      <c r="F82" t="s">
+        <v>69</v>
+      </c>
+      <c r="G82">
+        <v>102</v>
+      </c>
+      <c r="H82" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I82" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J82">
+        <v>1.199874216297309</v>
+      </c>
+      <c r="K82">
+        <v>1.199874216297309</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" t="s">
+        <v>48</v>
+      </c>
+      <c r="E83" t="s">
+        <v>66</v>
+      </c>
+      <c r="F83" t="s">
+        <v>72</v>
+      </c>
+      <c r="G83">
+        <v>205</v>
+      </c>
+      <c r="H83" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I83" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J83">
+        <v>1.199874216297309</v>
+      </c>
+      <c r="K83">
+        <v>1.199874216297309</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" t="s">
+        <v>27</v>
+      </c>
+      <c r="D84" t="s">
+        <v>48</v>
+      </c>
+      <c r="E84" t="s">
+        <v>67</v>
+      </c>
+      <c r="F84" t="s">
+        <v>75</v>
+      </c>
+      <c r="G84">
+        <v>322</v>
+      </c>
+      <c r="H84" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I84" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J84">
+        <v>1.199874216297309</v>
+      </c>
+      <c r="K84">
+        <v>1.199874216297309</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" t="s">
+        <v>53</v>
+      </c>
+      <c r="E85" t="s">
+        <v>65</v>
+      </c>
+      <c r="F85" t="s">
+        <v>69</v>
+      </c>
+      <c r="G85">
+        <v>102</v>
+      </c>
+      <c r="H85" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I85" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J85">
+        <v>4.562852441438126</v>
+      </c>
+      <c r="K85">
+        <v>4.562852441438126</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86" t="s">
+        <v>27</v>
+      </c>
+      <c r="D86" t="s">
+        <v>53</v>
+      </c>
+      <c r="E86" t="s">
+        <v>66</v>
+      </c>
+      <c r="F86" t="s">
+        <v>72</v>
+      </c>
+      <c r="G86">
+        <v>205</v>
+      </c>
+      <c r="H86" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I86" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J86">
+        <v>4.562852441438126</v>
+      </c>
+      <c r="K86">
+        <v>4.562852441438126</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" t="s">
+        <v>27</v>
+      </c>
+      <c r="D87" t="s">
+        <v>53</v>
+      </c>
+      <c r="E87" t="s">
+        <v>67</v>
+      </c>
+      <c r="F87" t="s">
+        <v>75</v>
+      </c>
+      <c r="G87">
+        <v>322</v>
+      </c>
+      <c r="H87" s="2">
+        <v>46238.71278935186</v>
+      </c>
+      <c r="I87" s="2">
+        <v>46238.74305555555</v>
+      </c>
+      <c r="J87">
+        <v>4.562852441438126</v>
+      </c>
+      <c r="K87">
+        <v>4.562852441438126</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>28</v>
+      </c>
+      <c r="D88" t="s">
+        <v>49</v>
+      </c>
+      <c r="E88" t="s">
+        <v>65</v>
+      </c>
+      <c r="F88" t="s">
+        <v>69</v>
+      </c>
+      <c r="G88">
+        <v>102</v>
+      </c>
+      <c r="H88" s="2">
+        <v>46237.24145833333</v>
+      </c>
+      <c r="I88" s="2">
+        <v>46237.2683912037</v>
+      </c>
+      <c r="J88">
+        <v>1.683802188892685</v>
+      </c>
+      <c r="K88">
+        <v>1.683802188892685</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" t="s">
+        <v>28</v>
+      </c>
+      <c r="D89" t="s">
+        <v>49</v>
+      </c>
+      <c r="E89" t="s">
+        <v>66</v>
+      </c>
+      <c r="F89" t="s">
+        <v>72</v>
+      </c>
+      <c r="G89">
+        <v>205</v>
+      </c>
+      <c r="H89" s="2">
+        <v>46237.24145833333</v>
+      </c>
+      <c r="I89" s="2">
+        <v>46237.2683912037</v>
+      </c>
+      <c r="J89">
+        <v>1.683802188892685</v>
+      </c>
+      <c r="K89">
+        <v>1.683802188892685</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" t="s">
+        <v>28</v>
+      </c>
+      <c r="D90" t="s">
+        <v>49</v>
+      </c>
+      <c r="E90" t="s">
+        <v>67</v>
+      </c>
+      <c r="F90" t="s">
+        <v>84</v>
+      </c>
+      <c r="G90">
+        <v>321</v>
+      </c>
+      <c r="H90" s="2">
+        <v>46237.24145833333</v>
+      </c>
+      <c r="I90" s="2">
+        <v>46237.2683912037</v>
+      </c>
+      <c r="J90">
+        <v>1.683802188892685</v>
+      </c>
+      <c r="K90">
+        <v>1.683802188892685</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" t="s">
+        <v>28</v>
+      </c>
+      <c r="D91" t="s">
+        <v>50</v>
+      </c>
+      <c r="E91" t="s">
+        <v>65</v>
+      </c>
+      <c r="F91" t="s">
+        <v>69</v>
+      </c>
+      <c r="G91">
+        <v>102</v>
+      </c>
+      <c r="H91" s="2">
+        <v>46237.24145833333</v>
+      </c>
+      <c r="I91" s="2">
+        <v>46237.2683912037</v>
+      </c>
+      <c r="J91">
+        <v>1.510318836283279</v>
+      </c>
+      <c r="K91">
+        <v>1.510318836283279</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" t="s">
+        <v>28</v>
+      </c>
+      <c r="D92" t="s">
+        <v>50</v>
+      </c>
+      <c r="E92" t="s">
+        <v>66</v>
+      </c>
+      <c r="F92" t="s">
+        <v>72</v>
+      </c>
+      <c r="G92">
+        <v>205</v>
+      </c>
+      <c r="H92" s="2">
+        <v>46237.24145833333</v>
+      </c>
+      <c r="I92" s="2">
+        <v>46237.2683912037</v>
+      </c>
+      <c r="J92">
+        <v>1.510318836283279</v>
+      </c>
+      <c r="K92">
+        <v>1.510318836283279</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" t="s">
+        <v>28</v>
+      </c>
+      <c r="D93" t="s">
+        <v>50</v>
+      </c>
+      <c r="E93" t="s">
+        <v>67</v>
+      </c>
+      <c r="F93" t="s">
+        <v>84</v>
+      </c>
+      <c r="G93">
+        <v>321</v>
+      </c>
+      <c r="H93" s="2">
+        <v>46237.24145833333</v>
+      </c>
+      <c r="I93" s="2">
+        <v>46237.2683912037</v>
+      </c>
+      <c r="J93">
+        <v>1.510318836283279</v>
+      </c>
+      <c r="K93">
+        <v>1.510318836283279</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" t="s">
+        <v>29</v>
+      </c>
+      <c r="D94" t="s">
+        <v>51</v>
+      </c>
+      <c r="E94" t="s">
+        <v>65</v>
+      </c>
+      <c r="F94" t="s">
+        <v>69</v>
+      </c>
+      <c r="G94">
+        <v>102</v>
+      </c>
+      <c r="H94" s="2">
+        <v>46237.97503472222</v>
+      </c>
+      <c r="I94" s="2">
+        <v>46238.01177083333</v>
+      </c>
+      <c r="J94">
+        <v>1.461372609944064</v>
+      </c>
+      <c r="K94">
+        <v>1.461372609944064</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" t="s">
+        <v>29</v>
+      </c>
+      <c r="D95" t="s">
+        <v>51</v>
+      </c>
+      <c r="E95" t="s">
+        <v>66</v>
+      </c>
+      <c r="F95" t="s">
+        <v>72</v>
+      </c>
+      <c r="G95">
+        <v>205</v>
+      </c>
+      <c r="H95" s="2">
+        <v>46237.97503472222</v>
+      </c>
+      <c r="I95" s="2">
+        <v>46238.01177083333</v>
+      </c>
+      <c r="J95">
+        <v>1.461372609944064</v>
+      </c>
+      <c r="K95">
+        <v>1.461372609944064</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" t="s">
+        <v>11</v>
+      </c>
+      <c r="B96" t="s">
+        <v>12</v>
+      </c>
+      <c r="C96" t="s">
+        <v>29</v>
+      </c>
+      <c r="D96" t="s">
+        <v>51</v>
+      </c>
+      <c r="E96" t="s">
+        <v>67</v>
+      </c>
+      <c r="F96" t="s">
+        <v>84</v>
+      </c>
+      <c r="G96">
+        <v>321</v>
+      </c>
+      <c r="H96" s="2">
+        <v>46237.97503472222</v>
+      </c>
+      <c r="I96" s="2">
+        <v>46237.98892361111</v>
+      </c>
+      <c r="J96">
+        <v>1.396842844879743</v>
+      </c>
+      <c r="K96">
+        <v>1.396842844879743</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" t="s">
+        <v>12</v>
+      </c>
+      <c r="C97" t="s">
+        <v>29</v>
+      </c>
+      <c r="D97" t="s">
+        <v>51</v>
+      </c>
+      <c r="E97" t="s">
+        <v>67</v>
+      </c>
+      <c r="F97" t="s">
+        <v>75</v>
+      </c>
+      <c r="G97">
+        <v>322</v>
+      </c>
+      <c r="H97" s="2">
+        <v>46238.01177083333</v>
+      </c>
+      <c r="I97" s="2">
+        <v>46238.01177083333</v>
+      </c>
+      <c r="J97">
+        <v>1.611002678122785</v>
+      </c>
+      <c r="K97">
+        <v>1.611002678122785</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" t="s">
+        <v>11</v>
+      </c>
+      <c r="B98" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" t="s">
+        <v>30</v>
+      </c>
+      <c r="D98" t="s">
+        <v>46</v>
+      </c>
+      <c r="E98" t="s">
+        <v>65</v>
+      </c>
+      <c r="F98" t="s">
+        <v>68</v>
+      </c>
+      <c r="G98">
+        <v>101</v>
+      </c>
+      <c r="H98" s="2">
+        <v>46230.2861574074</v>
+      </c>
+      <c r="I98" s="2">
+        <v>46230.31240740741</v>
+      </c>
+      <c r="J98">
+        <v>1.738575531706706</v>
+      </c>
+      <c r="K98">
+        <v>1.738575531706706</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99" t="s">
+        <v>30</v>
+      </c>
+      <c r="D99" t="s">
+        <v>46</v>
+      </c>
+      <c r="E99" t="s">
+        <v>65</v>
+      </c>
+      <c r="F99" t="s">
+        <v>69</v>
+      </c>
+      <c r="G99">
+        <v>102</v>
+      </c>
+      <c r="H99" s="2">
+        <v>46237.71436342593</v>
+      </c>
+      <c r="I99" s="2">
+        <v>46239.94284722222</v>
+      </c>
+      <c r="J99">
+        <v>1.924317845875284</v>
+      </c>
+      <c r="K99">
+        <v>1.924317845875284</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" t="s">
+        <v>30</v>
+      </c>
+      <c r="D100" t="s">
+        <v>46</v>
+      </c>
+      <c r="E100" t="s">
+        <v>66</v>
+      </c>
+      <c r="F100" t="s">
+        <v>71</v>
+      </c>
+      <c r="G100">
+        <v>204</v>
+      </c>
+      <c r="H100" s="2">
+        <v>46230.2861574074</v>
+      </c>
+      <c r="I100" s="2">
+        <v>46230.31240740741</v>
+      </c>
+      <c r="J100">
+        <v>1.738575531706706</v>
+      </c>
+      <c r="K100">
+        <v>1.738575531706706</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" t="s">
+        <v>30</v>
+      </c>
+      <c r="D101" t="s">
+        <v>46</v>
+      </c>
+      <c r="E101" t="s">
+        <v>66</v>
+      </c>
+      <c r="F101" t="s">
+        <v>72</v>
+      </c>
+      <c r="G101">
+        <v>205</v>
+      </c>
+      <c r="H101" s="2">
+        <v>46237.71436342593</v>
+      </c>
+      <c r="I101" s="2">
+        <v>46239.94284722222</v>
+      </c>
+      <c r="J101">
+        <v>1.924317845875284</v>
+      </c>
+      <c r="K101">
+        <v>1.924317845875284</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" t="s">
+        <v>30</v>
+      </c>
+      <c r="D102" t="s">
+        <v>46</v>
+      </c>
+      <c r="E102" t="s">
+        <v>67</v>
+      </c>
+      <c r="F102" t="s">
+        <v>74</v>
+      </c>
+      <c r="G102">
+        <v>314</v>
+      </c>
+      <c r="H102" s="2">
+        <v>46230.2861574074</v>
+      </c>
+      <c r="I102" s="2">
+        <v>46230.31240740741</v>
+      </c>
+      <c r="J102">
+        <v>1.738575531706706</v>
+      </c>
+      <c r="K102">
+        <v>1.738575531706706</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" t="s">
+        <v>12</v>
+      </c>
+      <c r="C103" t="s">
+        <v>30</v>
+      </c>
+      <c r="D103" t="s">
+        <v>46</v>
+      </c>
+      <c r="E103" t="s">
+        <v>67</v>
+      </c>
+      <c r="F103" t="s">
+        <v>84</v>
+      </c>
+      <c r="G103">
+        <v>321</v>
+      </c>
+      <c r="H103" s="2">
+        <v>46237.71436342593</v>
+      </c>
+      <c r="I103" s="2">
+        <v>46237.74181712963</v>
+      </c>
+      <c r="J103">
+        <v>1.855801837443607</v>
+      </c>
+      <c r="K103">
+        <v>1.855801837443607</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" t="s">
+        <v>12</v>
+      </c>
+      <c r="C104" t="s">
+        <v>30</v>
+      </c>
+      <c r="D104" t="s">
+        <v>46</v>
+      </c>
+      <c r="E104" t="s">
+        <v>67</v>
+      </c>
+      <c r="F104" t="s">
+        <v>78</v>
+      </c>
+      <c r="G104">
+        <v>323</v>
+      </c>
+      <c r="H104" s="2">
+        <v>46239.90753472222</v>
+      </c>
+      <c r="I104" s="2">
+        <v>46239.94284722222</v>
+      </c>
+      <c r="J104">
+        <v>1.979784724914562</v>
+      </c>
+      <c r="K104">
+        <v>1.979784724914562</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" t="s">
+        <v>12</v>
+      </c>
+      <c r="C105" t="s">
+        <v>30</v>
+      </c>
+      <c r="D105" t="s">
+        <v>47</v>
+      </c>
+      <c r="E105" t="s">
+        <v>65</v>
+      </c>
+      <c r="F105" t="s">
+        <v>68</v>
+      </c>
+      <c r="G105">
+        <v>101</v>
+      </c>
+      <c r="H105" s="2">
+        <v>46230.2861574074</v>
+      </c>
+      <c r="I105" s="2">
+        <v>46230.31240740741</v>
+      </c>
+      <c r="J105">
+        <v>3.101191863272319</v>
+      </c>
+      <c r="K105">
+        <v>3.101191863272319</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106" t="s">
+        <v>30</v>
+      </c>
+      <c r="D106" t="s">
+        <v>47</v>
+      </c>
+      <c r="E106" t="s">
+        <v>65</v>
+      </c>
+      <c r="F106" t="s">
+        <v>69</v>
+      </c>
+      <c r="G106">
+        <v>102</v>
+      </c>
+      <c r="H106" s="2">
+        <v>46237.71436342593</v>
+      </c>
+      <c r="I106" s="2">
+        <v>46239.94284722222</v>
+      </c>
+      <c r="J106">
+        <v>4.880702753274994</v>
+      </c>
+      <c r="K106">
+        <v>4.880702753274994</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" t="s">
+        <v>11</v>
+      </c>
+      <c r="B107" t="s">
+        <v>12</v>
+      </c>
+      <c r="C107" t="s">
+        <v>30</v>
+      </c>
+      <c r="D107" t="s">
+        <v>47</v>
+      </c>
+      <c r="E107" t="s">
+        <v>66</v>
+      </c>
+      <c r="F107" t="s">
+        <v>71</v>
+      </c>
+      <c r="G107">
+        <v>204</v>
+      </c>
+      <c r="H107" s="2">
+        <v>46230.2861574074</v>
+      </c>
+      <c r="I107" s="2">
+        <v>46230.31240740741</v>
+      </c>
+      <c r="J107">
+        <v>3.101191863272319</v>
+      </c>
+      <c r="K107">
+        <v>3.101191863272319</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" t="s">
+        <v>11</v>
+      </c>
+      <c r="B108" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" t="s">
+        <v>30</v>
+      </c>
+      <c r="D108" t="s">
+        <v>47</v>
+      </c>
+      <c r="E108" t="s">
+        <v>66</v>
+      </c>
+      <c r="F108" t="s">
+        <v>72</v>
+      </c>
+      <c r="G108">
+        <v>205</v>
+      </c>
+      <c r="H108" s="2">
+        <v>46237.71436342593</v>
+      </c>
+      <c r="I108" s="2">
+        <v>46239.94284722222</v>
+      </c>
+      <c r="J108">
+        <v>4.880702753274994</v>
+      </c>
+      <c r="K108">
+        <v>4.880702753274994</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" t="s">
+        <v>11</v>
+      </c>
+      <c r="B109" t="s">
+        <v>12</v>
+      </c>
+      <c r="C109" t="s">
+        <v>30</v>
+      </c>
+      <c r="D109" t="s">
+        <v>47</v>
+      </c>
+      <c r="E109" t="s">
+        <v>67</v>
+      </c>
+      <c r="F109" t="s">
+        <v>74</v>
+      </c>
+      <c r="G109">
+        <v>314</v>
+      </c>
+      <c r="H109" s="2">
+        <v>46230.2861574074</v>
+      </c>
+      <c r="I109" s="2">
+        <v>46230.31240740741</v>
+      </c>
+      <c r="J109">
+        <v>3.101191863272319</v>
+      </c>
+      <c r="K109">
+        <v>3.101191863272319</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" t="s">
+        <v>11</v>
+      </c>
+      <c r="B110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" t="s">
+        <v>30</v>
+      </c>
+      <c r="D110" t="s">
+        <v>47</v>
+      </c>
+      <c r="E110" t="s">
+        <v>67</v>
+      </c>
+      <c r="F110" t="s">
+        <v>84</v>
+      </c>
+      <c r="G110">
+        <v>321</v>
+      </c>
+      <c r="H110" s="2">
+        <v>46237.71436342593</v>
+      </c>
+      <c r="I110" s="2">
+        <v>46237.74181712963</v>
+      </c>
+      <c r="J110">
+        <v>3.785401835683741</v>
+      </c>
+      <c r="K110">
+        <v>3.785401835683741</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" t="s">
+        <v>11</v>
+      </c>
+      <c r="B111" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" t="s">
+        <v>30</v>
+      </c>
+      <c r="D111" t="s">
+        <v>47</v>
+      </c>
+      <c r="E111" t="s">
+        <v>67</v>
+      </c>
+      <c r="F111" t="s">
+        <v>78</v>
+      </c>
+      <c r="G111">
+        <v>323</v>
+      </c>
+      <c r="H111" s="2">
+        <v>46239.90753472222</v>
+      </c>
+      <c r="I111" s="2">
+        <v>46239.94284722222</v>
+      </c>
+      <c r="J111">
+        <v>6.742342510216055</v>
+      </c>
+      <c r="K111">
+        <v>6.742342510216055</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" t="s">
+        <v>11</v>
+      </c>
+      <c r="B112" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" t="s">
+        <v>31</v>
+      </c>
+      <c r="D112" t="s">
+        <v>46</v>
+      </c>
+      <c r="E112" t="s">
+        <v>65</v>
+      </c>
+      <c r="F112" t="s">
+        <v>68</v>
+      </c>
+      <c r="G112">
+        <v>101</v>
+      </c>
+      <c r="H112" s="2">
+        <v>46230.18972222223</v>
+      </c>
+      <c r="I112" s="2">
+        <v>46230.22109953704</v>
+      </c>
+      <c r="J112">
+        <v>1.945260761826871</v>
+      </c>
+      <c r="K112">
+        <v>1.945260761826871</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" t="s">
+        <v>11</v>
+      </c>
+      <c r="B113" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" t="s">
+        <v>31</v>
+      </c>
+      <c r="D113" t="s">
+        <v>46</v>
+      </c>
+      <c r="E113" t="s">
+        <v>66</v>
+      </c>
+      <c r="F113" t="s">
+        <v>71</v>
+      </c>
+      <c r="G113">
+        <v>204</v>
+      </c>
+      <c r="H113" s="2">
+        <v>46230.18972222223</v>
+      </c>
+      <c r="I113" s="2">
+        <v>46230.22109953704</v>
+      </c>
+      <c r="J113">
+        <v>1.945260761826871</v>
+      </c>
+      <c r="K113">
+        <v>1.945260761826871</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" t="s">
+        <v>11</v>
+      </c>
+      <c r="B114" t="s">
+        <v>12</v>
+      </c>
+      <c r="C114" t="s">
+        <v>31</v>
+      </c>
+      <c r="D114" t="s">
+        <v>46</v>
+      </c>
+      <c r="E114" t="s">
+        <v>67</v>
+      </c>
+      <c r="F114" t="s">
+        <v>74</v>
+      </c>
+      <c r="G114">
+        <v>314</v>
+      </c>
+      <c r="H114" s="2">
+        <v>46230.18972222223</v>
+      </c>
+      <c r="I114" s="2">
+        <v>46230.22109953704</v>
+      </c>
+      <c r="J114">
+        <v>1.945260761826871</v>
+      </c>
+      <c r="K114">
+        <v>1.945260761826871</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" t="s">
+        <v>11</v>
+      </c>
+      <c r="B115" t="s">
+        <v>12</v>
+      </c>
+      <c r="C115" t="s">
+        <v>31</v>
+      </c>
+      <c r="D115" t="s">
+        <v>47</v>
+      </c>
+      <c r="E115" t="s">
+        <v>65</v>
+      </c>
+      <c r="F115" t="s">
+        <v>68</v>
+      </c>
+      <c r="G115">
+        <v>101</v>
+      </c>
+      <c r="H115" s="2">
+        <v>46230.18972222223</v>
+      </c>
+      <c r="I115" s="2">
+        <v>46230.22109953704</v>
+      </c>
+      <c r="J115">
+        <v>2.199635212306361</v>
+      </c>
+      <c r="K115">
+        <v>2.199635212306361</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" t="s">
+        <v>11</v>
+      </c>
+      <c r="B116" t="s">
+        <v>12</v>
+      </c>
+      <c r="C116" t="s">
+        <v>31</v>
+      </c>
+      <c r="D116" t="s">
+        <v>47</v>
+      </c>
+      <c r="E116" t="s">
+        <v>66</v>
+      </c>
+      <c r="F116" t="s">
+        <v>71</v>
+      </c>
+      <c r="G116">
+        <v>204</v>
+      </c>
+      <c r="H116" s="2">
+        <v>46230.18972222223</v>
+      </c>
+      <c r="I116" s="2">
+        <v>46230.22109953704</v>
+      </c>
+      <c r="J116">
+        <v>2.199635212306361</v>
+      </c>
+      <c r="K116">
+        <v>2.199635212306361</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" t="s">
+        <v>12</v>
+      </c>
+      <c r="C117" t="s">
+        <v>31</v>
+      </c>
+      <c r="D117" t="s">
+        <v>47</v>
+      </c>
+      <c r="E117" t="s">
+        <v>67</v>
+      </c>
+      <c r="F117" t="s">
+        <v>74</v>
+      </c>
+      <c r="G117">
+        <v>314</v>
+      </c>
+      <c r="H117" s="2">
+        <v>46230.18972222223</v>
+      </c>
+      <c r="I117" s="2">
+        <v>46230.22109953704</v>
+      </c>
+      <c r="J117">
+        <v>2.199635212306361</v>
+      </c>
+      <c r="K117">
+        <v>2.199635212306361</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" t="s">
+        <v>11</v>
+      </c>
+      <c r="B118" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" t="s">
+        <v>32</v>
+      </c>
+      <c r="D118" t="s">
+        <v>52</v>
+      </c>
+      <c r="E118" t="s">
+        <v>65</v>
+      </c>
+      <c r="F118" t="s">
+        <v>68</v>
+      </c>
+      <c r="G118">
+        <v>101</v>
+      </c>
+      <c r="H118" s="2">
+        <v>46228.93714120371</v>
+      </c>
+      <c r="I118" s="2">
+        <v>46230.8632175926</v>
+      </c>
+      <c r="J118">
+        <v>2.196097348217624</v>
+      </c>
+      <c r="K118">
+        <v>2.196097348217624</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" t="s">
+        <v>32</v>
+      </c>
+      <c r="D119" t="s">
+        <v>52</v>
+      </c>
+      <c r="E119" t="s">
+        <v>65</v>
+      </c>
+      <c r="F119" t="s">
+        <v>69</v>
+      </c>
+      <c r="G119">
+        <v>102</v>
+      </c>
+      <c r="H119" s="2">
+        <v>46237.39759259259</v>
+      </c>
+      <c r="I119" s="2">
+        <v>46239.48909722222</v>
+      </c>
+      <c r="J119">
+        <v>1.741277139936098</v>
+      </c>
+      <c r="K119">
+        <v>1.741277139936098</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" t="s">
+        <v>11</v>
+      </c>
+      <c r="B120" t="s">
+        <v>12</v>
+      </c>
+      <c r="C120" t="s">
+        <v>32</v>
+      </c>
+      <c r="D120" t="s">
+        <v>52</v>
+      </c>
+      <c r="E120" t="s">
+        <v>66</v>
+      </c>
+      <c r="F120" t="s">
+        <v>70</v>
+      </c>
+      <c r="G120">
+        <v>203</v>
+      </c>
+      <c r="H120" s="2">
+        <v>46228.93714120371</v>
+      </c>
+      <c r="I120" s="2">
+        <v>46228.94255787037</v>
+      </c>
+      <c r="J120">
+        <v>2.423426358493773</v>
+      </c>
+      <c r="K120">
+        <v>2.423426358493773</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" t="s">
+        <v>11</v>
+      </c>
+      <c r="B121" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" t="s">
+        <v>32</v>
+      </c>
+      <c r="D121" t="s">
+        <v>52</v>
+      </c>
+      <c r="E121" t="s">
+        <v>66</v>
+      </c>
+      <c r="F121" t="s">
+        <v>71</v>
+      </c>
+      <c r="G121">
+        <v>204</v>
+      </c>
+      <c r="H121" s="2">
+        <v>46230.7833912037</v>
+      </c>
+      <c r="I121" s="2">
+        <v>46230.8632175926</v>
+      </c>
+      <c r="J121">
+        <v>2.081802506775104</v>
+      </c>
+      <c r="K121">
+        <v>2.081802506775104</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" t="s">
+        <v>32</v>
+      </c>
+      <c r="D122" t="s">
+        <v>52</v>
+      </c>
+      <c r="E122" t="s">
+        <v>66</v>
+      </c>
+      <c r="F122" t="s">
+        <v>72</v>
+      </c>
+      <c r="G122">
+        <v>205</v>
+      </c>
+      <c r="H122" s="2">
+        <v>46237.39759259259</v>
+      </c>
+      <c r="I122" s="2">
+        <v>46239.48909722222</v>
+      </c>
+      <c r="J122">
+        <v>1.741277139936098</v>
+      </c>
+      <c r="K122">
+        <v>1.741277139936098</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" t="s">
+        <v>11</v>
+      </c>
+      <c r="B123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123" t="s">
+        <v>32</v>
+      </c>
+      <c r="D123" t="s">
+        <v>52</v>
+      </c>
+      <c r="E123" t="s">
+        <v>67</v>
+      </c>
+      <c r="F123" t="s">
+        <v>85</v>
+      </c>
+      <c r="G123">
+        <v>312</v>
+      </c>
+      <c r="H123" s="2">
+        <v>46228.93714120371</v>
+      </c>
+      <c r="I123" s="2">
+        <v>46228.94255787037</v>
+      </c>
+      <c r="J123">
+        <v>2.423426358493773</v>
+      </c>
+      <c r="K123">
+        <v>2.423426358493773</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" t="s">
+        <v>11</v>
+      </c>
+      <c r="B124" t="s">
+        <v>12</v>
+      </c>
+      <c r="C124" t="s">
+        <v>32</v>
+      </c>
+      <c r="D124" t="s">
+        <v>52</v>
+      </c>
+      <c r="E124" t="s">
+        <v>67</v>
+      </c>
+      <c r="F124" t="s">
+        <v>74</v>
+      </c>
+      <c r="G124">
+        <v>314</v>
+      </c>
+      <c r="H124" s="2">
+        <v>46230.7833912037</v>
+      </c>
+      <c r="I124" s="2">
+        <v>46230.8632175926</v>
+      </c>
+      <c r="J124">
+        <v>2.081802506775104</v>
+      </c>
+      <c r="K124">
+        <v>2.081802506775104</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125" t="s">
+        <v>11</v>
+      </c>
+      <c r="B125" t="s">
+        <v>12</v>
+      </c>
+      <c r="C125" t="s">
+        <v>32</v>
+      </c>
+      <c r="D125" t="s">
+        <v>52</v>
+      </c>
+      <c r="E125" t="s">
+        <v>67</v>
+      </c>
+      <c r="F125" t="s">
+        <v>84</v>
+      </c>
+      <c r="G125">
+        <v>321</v>
+      </c>
+      <c r="H125" s="2">
+        <v>46237.39759259259</v>
+      </c>
+      <c r="I125" s="2">
+        <v>46237.40302083334</v>
+      </c>
+      <c r="J125">
+        <v>1.699841446416683</v>
+      </c>
+      <c r="K125">
+        <v>1.699841446416683</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" t="s">
+        <v>11</v>
+      </c>
+      <c r="B126" t="s">
+        <v>12</v>
+      </c>
+      <c r="C126" t="s">
+        <v>32</v>
+      </c>
+      <c r="D126" t="s">
+        <v>52</v>
+      </c>
+      <c r="E126" t="s">
+        <v>67</v>
+      </c>
+      <c r="F126" t="s">
+        <v>75</v>
+      </c>
+      <c r="G126">
+        <v>322</v>
+      </c>
+      <c r="H126" s="2">
+        <v>46238.19202546297</v>
+      </c>
+      <c r="I126" s="2">
+        <v>46238.1974537037</v>
+      </c>
+      <c r="J126">
+        <v>1.79984862679152</v>
+      </c>
+      <c r="K126">
+        <v>1.79984862679152</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127" t="s">
+        <v>11</v>
+      </c>
+      <c r="B127" t="s">
+        <v>12</v>
+      </c>
+      <c r="C127" t="s">
+        <v>32</v>
+      </c>
+      <c r="D127" t="s">
+        <v>52</v>
+      </c>
+      <c r="E127" t="s">
+        <v>67</v>
+      </c>
+      <c r="F127" t="s">
+        <v>78</v>
+      </c>
+      <c r="G127">
+        <v>323</v>
+      </c>
+      <c r="H127" s="2">
+        <v>46239.48366898148</v>
+      </c>
+      <c r="I127" s="2">
+        <v>46239.48909722222</v>
+      </c>
+      <c r="J127">
+        <v>1.716739518084697</v>
+      </c>
+      <c r="K127">
+        <v>1.716739518084697</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128" t="s">
+        <v>11</v>
+      </c>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" t="s">
+        <v>33</v>
+      </c>
+      <c r="D128" t="s">
+        <v>54</v>
+      </c>
+      <c r="E128" t="s">
+        <v>65</v>
+      </c>
+      <c r="F128" t="s">
+        <v>68</v>
+      </c>
+      <c r="G128">
+        <v>101</v>
+      </c>
+      <c r="H128" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I128" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J128">
+        <v>2.371006469700295</v>
+      </c>
+      <c r="K128">
+        <v>2.371006469700295</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" t="s">
+        <v>11</v>
+      </c>
+      <c r="B129" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" t="s">
+        <v>33</v>
+      </c>
+      <c r="D129" t="s">
+        <v>54</v>
+      </c>
+      <c r="E129" t="s">
+        <v>66</v>
+      </c>
+      <c r="F129" t="s">
+        <v>86</v>
+      </c>
+      <c r="G129">
+        <v>201</v>
+      </c>
+      <c r="H129" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I129" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J129">
+        <v>2.371006469700295</v>
+      </c>
+      <c r="K129">
+        <v>2.371006469700295</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" t="s">
+        <v>11</v>
+      </c>
+      <c r="B130" t="s">
+        <v>13</v>
+      </c>
+      <c r="C130" t="s">
+        <v>33</v>
+      </c>
+      <c r="D130" t="s">
+        <v>54</v>
+      </c>
+      <c r="E130" t="s">
+        <v>67</v>
+      </c>
+      <c r="F130" t="s">
+        <v>87</v>
+      </c>
+      <c r="G130">
+        <v>301</v>
+      </c>
+      <c r="H130" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I130" s="2">
+        <v>46204.48143518518</v>
+      </c>
+      <c r="J130">
+        <v>2.67285918915458</v>
+      </c>
+      <c r="K130">
+        <v>2.67285918915458</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" t="s">
+        <v>11</v>
+      </c>
+      <c r="B131" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" t="s">
+        <v>33</v>
+      </c>
+      <c r="D131" t="s">
+        <v>54</v>
+      </c>
+      <c r="E131" t="s">
+        <v>67</v>
+      </c>
+      <c r="F131" t="s">
+        <v>88</v>
+      </c>
+      <c r="G131">
+        <v>302</v>
+      </c>
+      <c r="H131" s="2">
+        <v>46205.1180787037</v>
+      </c>
+      <c r="I131" s="2">
+        <v>46205.77965277778</v>
+      </c>
+      <c r="J131">
+        <v>2.353225669816371</v>
+      </c>
+      <c r="K131">
+        <v>2.353225669816371</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" t="s">
+        <v>11</v>
+      </c>
+      <c r="B132" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" t="s">
+        <v>33</v>
+      </c>
+      <c r="D132" t="s">
+        <v>54</v>
+      </c>
+      <c r="E132" t="s">
+        <v>67</v>
+      </c>
+      <c r="F132" t="s">
+        <v>89</v>
+      </c>
+      <c r="G132">
+        <v>303</v>
+      </c>
+      <c r="H132" s="2">
+        <v>46206.14086805555</v>
+      </c>
+      <c r="I132" s="2">
+        <v>46206.61196759259</v>
+      </c>
+      <c r="J132">
+        <v>2.508648197643544</v>
+      </c>
+      <c r="K132">
+        <v>2.508648197643544</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" t="s">
+        <v>11</v>
+      </c>
+      <c r="B133" t="s">
+        <v>13</v>
+      </c>
+      <c r="C133" t="s">
+        <v>33</v>
+      </c>
+      <c r="D133" t="s">
+        <v>54</v>
+      </c>
+      <c r="E133" t="s">
+        <v>67</v>
+      </c>
+      <c r="F133" t="s">
+        <v>90</v>
+      </c>
+      <c r="G133">
+        <v>304</v>
+      </c>
+      <c r="H133" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="I133" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J133">
+        <v>2.804250769071384</v>
+      </c>
+      <c r="K133">
+        <v>2.804250769071384</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134" t="s">
+        <v>11</v>
+      </c>
+      <c r="B134" t="s">
+        <v>13</v>
+      </c>
+      <c r="C134" t="s">
+        <v>33</v>
+      </c>
+      <c r="D134" t="s">
+        <v>55</v>
+      </c>
+      <c r="E134" t="s">
+        <v>65</v>
+      </c>
+      <c r="F134" t="s">
+        <v>68</v>
+      </c>
+      <c r="G134">
+        <v>101</v>
+      </c>
+      <c r="H134" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I134" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J134">
+        <v>2.547008202307568</v>
+      </c>
+      <c r="K134">
+        <v>2.547008202307568</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
+      <c r="A135" t="s">
+        <v>11</v>
+      </c>
+      <c r="B135" t="s">
+        <v>13</v>
+      </c>
+      <c r="C135" t="s">
+        <v>33</v>
+      </c>
+      <c r="D135" t="s">
+        <v>55</v>
+      </c>
+      <c r="E135" t="s">
+        <v>66</v>
+      </c>
+      <c r="F135" t="s">
+        <v>86</v>
+      </c>
+      <c r="G135">
+        <v>201</v>
+      </c>
+      <c r="H135" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I135" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J135">
+        <v>2.547008202307568</v>
+      </c>
+      <c r="K135">
+        <v>2.547008202307568</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
+      <c r="A136" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136" t="s">
+        <v>13</v>
+      </c>
+      <c r="C136" t="s">
+        <v>33</v>
+      </c>
+      <c r="D136" t="s">
+        <v>55</v>
+      </c>
+      <c r="E136" t="s">
+        <v>67</v>
+      </c>
+      <c r="F136" t="s">
+        <v>87</v>
+      </c>
+      <c r="G136">
+        <v>301</v>
+      </c>
+      <c r="H136" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I136" s="2">
+        <v>46204.48143518518</v>
+      </c>
+      <c r="J136">
+        <v>2.412718096413623</v>
+      </c>
+      <c r="K136">
+        <v>2.412718096413623</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="A137" t="s">
+        <v>11</v>
+      </c>
+      <c r="B137" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" t="s">
+        <v>33</v>
+      </c>
+      <c r="D137" t="s">
+        <v>55</v>
+      </c>
+      <c r="E137" t="s">
+        <v>67</v>
+      </c>
+      <c r="F137" t="s">
+        <v>88</v>
+      </c>
+      <c r="G137">
+        <v>302</v>
+      </c>
+      <c r="H137" s="2">
+        <v>46205.1180787037</v>
+      </c>
+      <c r="I137" s="2">
+        <v>46205.77965277778</v>
+      </c>
+      <c r="J137">
+        <v>2.757348303637914</v>
+      </c>
+      <c r="K137">
+        <v>2.757348303637914</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138" t="s">
+        <v>11</v>
+      </c>
+      <c r="B138" t="s">
+        <v>13</v>
+      </c>
+      <c r="C138" t="s">
+        <v>33</v>
+      </c>
+      <c r="D138" t="s">
+        <v>55</v>
+      </c>
+      <c r="E138" t="s">
+        <v>67</v>
+      </c>
+      <c r="F138" t="s">
+        <v>89</v>
+      </c>
+      <c r="G138">
+        <v>303</v>
+      </c>
+      <c r="H138" s="2">
+        <v>46206.14086805555</v>
+      </c>
+      <c r="I138" s="2">
+        <v>46206.61196759259</v>
+      </c>
+      <c r="J138">
+        <v>2.597410666279916</v>
+      </c>
+      <c r="K138">
+        <v>2.597410666279916</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="A139" t="s">
+        <v>11</v>
+      </c>
+      <c r="B139" t="s">
+        <v>13</v>
+      </c>
+      <c r="C139" t="s">
+        <v>33</v>
+      </c>
+      <c r="D139" t="s">
+        <v>55</v>
+      </c>
+      <c r="E139" t="s">
+        <v>67</v>
+      </c>
+      <c r="F139" t="s">
+        <v>90</v>
+      </c>
+      <c r="G139">
+        <v>304</v>
+      </c>
+      <c r="H139" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="I139" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J139">
+        <v>2.360111806550468</v>
+      </c>
+      <c r="K139">
+        <v>2.360111806550468</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140" t="s">
+        <v>11</v>
+      </c>
+      <c r="B140" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140" t="s">
+        <v>33</v>
+      </c>
+      <c r="D140" t="s">
+        <v>56</v>
+      </c>
+      <c r="E140" t="s">
+        <v>65</v>
+      </c>
+      <c r="F140" t="s">
+        <v>68</v>
+      </c>
+      <c r="G140">
+        <v>101</v>
+      </c>
+      <c r="H140" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I140" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J140">
+        <v>1.978853450574098</v>
+      </c>
+      <c r="K140">
+        <v>1.978853450574098</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11">
+      <c r="A141" t="s">
+        <v>11</v>
+      </c>
+      <c r="B141" t="s">
+        <v>13</v>
+      </c>
+      <c r="C141" t="s">
+        <v>33</v>
+      </c>
+      <c r="D141" t="s">
+        <v>56</v>
+      </c>
+      <c r="E141" t="s">
+        <v>66</v>
+      </c>
+      <c r="F141" t="s">
+        <v>86</v>
+      </c>
+      <c r="G141">
+        <v>201</v>
+      </c>
+      <c r="H141" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I141" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J141">
+        <v>1.978853450574098</v>
+      </c>
+      <c r="K141">
+        <v>1.978853450574098</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11">
+      <c r="A142" t="s">
+        <v>11</v>
+      </c>
+      <c r="B142" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" t="s">
+        <v>33</v>
+      </c>
+      <c r="D142" t="s">
+        <v>56</v>
+      </c>
+      <c r="E142" t="s">
+        <v>67</v>
+      </c>
+      <c r="F142" t="s">
+        <v>87</v>
+      </c>
+      <c r="G142">
+        <v>301</v>
+      </c>
+      <c r="H142" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I142" s="2">
+        <v>46204.48143518518</v>
+      </c>
+      <c r="J142">
+        <v>1.973329619411917</v>
+      </c>
+      <c r="K142">
+        <v>1.973329619411917</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11">
+      <c r="A143" t="s">
+        <v>11</v>
+      </c>
+      <c r="B143" t="s">
+        <v>13</v>
+      </c>
+      <c r="C143" t="s">
+        <v>33</v>
+      </c>
+      <c r="D143" t="s">
+        <v>56</v>
+      </c>
+      <c r="E143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F143" t="s">
+        <v>88</v>
+      </c>
+      <c r="G143">
+        <v>302</v>
+      </c>
+      <c r="H143" s="2">
+        <v>46205.1180787037</v>
+      </c>
+      <c r="I143" s="2">
+        <v>46205.77965277778</v>
+      </c>
+      <c r="J143">
+        <v>1.985517299327437</v>
+      </c>
+      <c r="K143">
+        <v>1.985517299327437</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11">
+      <c r="A144" t="s">
+        <v>11</v>
+      </c>
+      <c r="B144" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" t="s">
+        <v>33</v>
+      </c>
+      <c r="D144" t="s">
+        <v>56</v>
+      </c>
+      <c r="E144" t="s">
+        <v>67</v>
+      </c>
+      <c r="F144" t="s">
+        <v>89</v>
+      </c>
+      <c r="G144">
+        <v>303</v>
+      </c>
+      <c r="H144" s="2">
+        <v>46206.14086805555</v>
+      </c>
+      <c r="I144" s="2">
+        <v>46206.61196759259</v>
+      </c>
+      <c r="J144">
+        <v>2.071364974880914</v>
+      </c>
+      <c r="K144">
+        <v>2.071364974880914</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11">
+      <c r="A145" t="s">
+        <v>11</v>
+      </c>
+      <c r="B145" t="s">
+        <v>13</v>
+      </c>
+      <c r="C145" t="s">
+        <v>33</v>
+      </c>
+      <c r="D145" t="s">
+        <v>56</v>
+      </c>
+      <c r="E145" t="s">
+        <v>67</v>
+      </c>
+      <c r="F145" t="s">
+        <v>90</v>
+      </c>
+      <c r="G145">
+        <v>304</v>
+      </c>
+      <c r="H145" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="I145" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J145">
+        <v>2.492949601255396</v>
+      </c>
+      <c r="K145">
+        <v>2.492949601255396</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11">
+      <c r="A146" t="s">
+        <v>11</v>
+      </c>
+      <c r="B146" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" t="s">
+        <v>33</v>
+      </c>
+      <c r="D146" t="s">
+        <v>57</v>
+      </c>
+      <c r="E146" t="s">
+        <v>65</v>
+      </c>
+      <c r="F146" t="s">
+        <v>68</v>
+      </c>
+      <c r="G146">
+        <v>101</v>
+      </c>
+      <c r="H146" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I146" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J146">
+        <v>4.029575489602267</v>
+      </c>
+      <c r="K146">
+        <v>4.029575489602267</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11">
+      <c r="A147" t="s">
+        <v>11</v>
+      </c>
+      <c r="B147" t="s">
+        <v>13</v>
+      </c>
+      <c r="C147" t="s">
+        <v>33</v>
+      </c>
+      <c r="D147" t="s">
+        <v>57</v>
+      </c>
+      <c r="E147" t="s">
+        <v>66</v>
+      </c>
+      <c r="F147" t="s">
+        <v>86</v>
+      </c>
+      <c r="G147">
+        <v>201</v>
+      </c>
+      <c r="H147" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I147" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J147">
+        <v>4.029575489602267</v>
+      </c>
+      <c r="K147">
+        <v>4.029575489602267</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11">
+      <c r="A148" t="s">
+        <v>11</v>
+      </c>
+      <c r="B148" t="s">
+        <v>13</v>
+      </c>
+      <c r="C148" t="s">
+        <v>33</v>
+      </c>
+      <c r="D148" t="s">
+        <v>57</v>
+      </c>
+      <c r="E148" t="s">
+        <v>67</v>
+      </c>
+      <c r="F148" t="s">
+        <v>87</v>
+      </c>
+      <c r="G148">
+        <v>301</v>
+      </c>
+      <c r="H148" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I148" s="2">
+        <v>46204.48143518518</v>
+      </c>
+      <c r="J148">
+        <v>4.091144075229254</v>
+      </c>
+      <c r="K148">
+        <v>4.091144075229254</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11">
+      <c r="A149" t="s">
+        <v>11</v>
+      </c>
+      <c r="B149" t="s">
+        <v>13</v>
+      </c>
+      <c r="C149" t="s">
+        <v>33</v>
+      </c>
+      <c r="D149" t="s">
+        <v>57</v>
+      </c>
+      <c r="E149" t="s">
+        <v>67</v>
+      </c>
+      <c r="F149" t="s">
+        <v>88</v>
+      </c>
+      <c r="G149">
+        <v>302</v>
+      </c>
+      <c r="H149" s="2">
+        <v>46205.1180787037</v>
+      </c>
+      <c r="I149" s="2">
+        <v>46205.77965277778</v>
+      </c>
+      <c r="J149">
+        <v>3.974895780538705</v>
+      </c>
+      <c r="K149">
+        <v>3.974895780538705</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11">
+      <c r="A150" t="s">
+        <v>11</v>
+      </c>
+      <c r="B150" t="s">
+        <v>13</v>
+      </c>
+      <c r="C150" t="s">
+        <v>33</v>
+      </c>
+      <c r="D150" t="s">
+        <v>57</v>
+      </c>
+      <c r="E150" t="s">
+        <v>67</v>
+      </c>
+      <c r="F150" t="s">
+        <v>89</v>
+      </c>
+      <c r="G150">
+        <v>303</v>
+      </c>
+      <c r="H150" s="2">
+        <v>46206.14086805555</v>
+      </c>
+      <c r="I150" s="2">
+        <v>46206.61196759259</v>
+      </c>
+      <c r="J150">
+        <v>4.135629187404321</v>
+      </c>
+      <c r="K150">
+        <v>4.135629187404321</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11">
+      <c r="A151" t="s">
+        <v>11</v>
+      </c>
+      <c r="B151" t="s">
+        <v>13</v>
+      </c>
+      <c r="C151" t="s">
+        <v>33</v>
+      </c>
+      <c r="D151" t="s">
+        <v>57</v>
+      </c>
+      <c r="E151" t="s">
+        <v>67</v>
+      </c>
+      <c r="F151" t="s">
+        <v>90</v>
+      </c>
+      <c r="G151">
+        <v>304</v>
+      </c>
+      <c r="H151" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="I151" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J151">
+        <v>3.883137720480742</v>
+      </c>
+      <c r="K151">
+        <v>3.883137720480742</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11">
+      <c r="A152" t="s">
+        <v>11</v>
+      </c>
+      <c r="B152" t="s">
+        <v>13</v>
+      </c>
+      <c r="C152" t="s">
+        <v>33</v>
+      </c>
+      <c r="D152" t="s">
+        <v>58</v>
+      </c>
+      <c r="E152" t="s">
+        <v>65</v>
+      </c>
+      <c r="F152" t="s">
+        <v>68</v>
+      </c>
+      <c r="G152">
+        <v>101</v>
+      </c>
+      <c r="H152" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I152" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J152">
+        <v>1.798649079442733</v>
+      </c>
+      <c r="K152">
+        <v>1.798649079442733</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11">
+      <c r="A153" t="s">
+        <v>11</v>
+      </c>
+      <c r="B153" t="s">
+        <v>13</v>
+      </c>
+      <c r="C153" t="s">
+        <v>33</v>
+      </c>
+      <c r="D153" t="s">
+        <v>58</v>
+      </c>
+      <c r="E153" t="s">
+        <v>66</v>
+      </c>
+      <c r="F153" t="s">
+        <v>86</v>
+      </c>
+      <c r="G153">
+        <v>201</v>
+      </c>
+      <c r="H153" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I153" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J153">
+        <v>1.798649079442733</v>
+      </c>
+      <c r="K153">
+        <v>1.798649079442733</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
+      <c r="A154" t="s">
+        <v>11</v>
+      </c>
+      <c r="B154" t="s">
+        <v>13</v>
+      </c>
+      <c r="C154" t="s">
+        <v>33</v>
+      </c>
+      <c r="D154" t="s">
+        <v>58</v>
+      </c>
+      <c r="E154" t="s">
+        <v>67</v>
+      </c>
+      <c r="F154" t="s">
+        <v>87</v>
+      </c>
+      <c r="G154">
+        <v>301</v>
+      </c>
+      <c r="H154" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I154" s="2">
+        <v>46204.48143518518</v>
+      </c>
+      <c r="J154">
+        <v>1.413567962158086</v>
+      </c>
+      <c r="K154">
+        <v>1.413567962158086</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11">
+      <c r="A155" t="s">
+        <v>11</v>
+      </c>
+      <c r="B155" t="s">
+        <v>13</v>
+      </c>
+      <c r="C155" t="s">
+        <v>33</v>
+      </c>
+      <c r="D155" t="s">
+        <v>58</v>
+      </c>
+      <c r="E155" t="s">
+        <v>67</v>
+      </c>
+      <c r="F155" t="s">
+        <v>88</v>
+      </c>
+      <c r="G155">
+        <v>302</v>
+      </c>
+      <c r="H155" s="2">
+        <v>46205.1180787037</v>
+      </c>
+      <c r="I155" s="2">
+        <v>46205.77965277778</v>
+      </c>
+      <c r="J155">
+        <v>2.013994314162456</v>
+      </c>
+      <c r="K155">
+        <v>2.013994314162456</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11">
+      <c r="A156" t="s">
+        <v>11</v>
+      </c>
+      <c r="B156" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" t="s">
+        <v>33</v>
+      </c>
+      <c r="D156" t="s">
+        <v>58</v>
+      </c>
+      <c r="E156" t="s">
+        <v>67</v>
+      </c>
+      <c r="F156" t="s">
+        <v>89</v>
+      </c>
+      <c r="G156">
+        <v>303</v>
+      </c>
+      <c r="H156" s="2">
+        <v>46206.14086805555</v>
+      </c>
+      <c r="I156" s="2">
+        <v>46206.61196759259</v>
+      </c>
+      <c r="J156">
+        <v>2.378746212537681</v>
+      </c>
+      <c r="K156">
+        <v>2.378746212537681</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11">
+      <c r="A157" t="s">
+        <v>11</v>
+      </c>
+      <c r="B157" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" t="s">
+        <v>33</v>
+      </c>
+      <c r="D157" t="s">
+        <v>58</v>
+      </c>
+      <c r="E157" t="s">
+        <v>67</v>
+      </c>
+      <c r="F157" t="s">
+        <v>90</v>
+      </c>
+      <c r="G157">
+        <v>304</v>
+      </c>
+      <c r="H157" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="I157" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J157">
+        <v>3.011896468546829</v>
+      </c>
+      <c r="K157">
+        <v>3.011896468546829</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11">
+      <c r="A158" t="s">
+        <v>11</v>
+      </c>
+      <c r="B158" t="s">
+        <v>13</v>
+      </c>
+      <c r="C158" t="s">
+        <v>33</v>
+      </c>
+      <c r="D158" t="s">
+        <v>59</v>
+      </c>
+      <c r="E158" t="s">
+        <v>65</v>
+      </c>
+      <c r="F158" t="s">
+        <v>68</v>
+      </c>
+      <c r="G158">
+        <v>101</v>
+      </c>
+      <c r="H158" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I158" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J158">
+        <v>4.20316093081487</v>
+      </c>
+      <c r="K158">
+        <v>4.20316093081487</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11">
+      <c r="A159" t="s">
+        <v>11</v>
+      </c>
+      <c r="B159" t="s">
+        <v>13</v>
+      </c>
+      <c r="C159" t="s">
+        <v>33</v>
+      </c>
+      <c r="D159" t="s">
+        <v>59</v>
+      </c>
+      <c r="E159" t="s">
+        <v>66</v>
+      </c>
+      <c r="F159" t="s">
+        <v>86</v>
+      </c>
+      <c r="G159">
+        <v>201</v>
+      </c>
+      <c r="H159" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I159" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J159">
+        <v>4.20316093081487</v>
+      </c>
+      <c r="K159">
+        <v>4.20316093081487</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11">
+      <c r="A160" t="s">
+        <v>11</v>
+      </c>
+      <c r="B160" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160" t="s">
+        <v>33</v>
+      </c>
+      <c r="D160" t="s">
+        <v>59</v>
+      </c>
+      <c r="E160" t="s">
+        <v>67</v>
+      </c>
+      <c r="F160" t="s">
+        <v>87</v>
+      </c>
+      <c r="G160">
+        <v>301</v>
+      </c>
+      <c r="H160" s="2">
+        <v>46204.07336805556</v>
+      </c>
+      <c r="I160" s="2">
+        <v>46204.48143518518</v>
+      </c>
+      <c r="J160">
+        <v>5.266814649998149</v>
+      </c>
+      <c r="K160">
+        <v>5.266814649998149</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11">
+      <c r="A161" t="s">
+        <v>11</v>
+      </c>
+      <c r="B161" t="s">
+        <v>13</v>
+      </c>
+      <c r="C161" t="s">
+        <v>33</v>
+      </c>
+      <c r="D161" t="s">
+        <v>59</v>
+      </c>
+      <c r="E161" t="s">
+        <v>67</v>
+      </c>
+      <c r="F161" t="s">
+        <v>88</v>
+      </c>
+      <c r="G161">
+        <v>302</v>
+      </c>
+      <c r="H161" s="2">
+        <v>46205.1180787037</v>
+      </c>
+      <c r="I161" s="2">
+        <v>46205.77965277778</v>
+      </c>
+      <c r="J161">
+        <v>3.994991709466376</v>
+      </c>
+      <c r="K161">
+        <v>3.994991709466376</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11">
+      <c r="A162" t="s">
+        <v>11</v>
+      </c>
+      <c r="B162" t="s">
+        <v>13</v>
+      </c>
+      <c r="C162" t="s">
+        <v>33</v>
+      </c>
+      <c r="D162" t="s">
+        <v>59</v>
+      </c>
+      <c r="E162" t="s">
+        <v>67</v>
+      </c>
+      <c r="F162" t="s">
+        <v>89</v>
+      </c>
+      <c r="G162">
+        <v>303</v>
+      </c>
+      <c r="H162" s="2">
+        <v>46206.14086805555</v>
+      </c>
+      <c r="I162" s="2">
+        <v>46206.61196759259</v>
+      </c>
+      <c r="J162">
+        <v>4.173442424252205</v>
+      </c>
+      <c r="K162">
+        <v>4.173442424252205</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11">
+      <c r="A163" t="s">
+        <v>11</v>
+      </c>
+      <c r="B163" t="s">
+        <v>13</v>
+      </c>
+      <c r="C163" t="s">
+        <v>33</v>
+      </c>
+      <c r="D163" t="s">
+        <v>59</v>
+      </c>
+      <c r="E163" t="s">
+        <v>67</v>
+      </c>
+      <c r="F163" t="s">
+        <v>90</v>
+      </c>
+      <c r="G163">
+        <v>304</v>
+      </c>
+      <c r="H163" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="I163" s="2">
+        <v>46207.44892361111</v>
+      </c>
+      <c r="J163">
+        <v>4.600778541286321</v>
+      </c>
+      <c r="K163">
+        <v>4.600778541286321</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11">
+      <c r="A164" t="s">
+        <v>11</v>
+      </c>
+      <c r="B164" t="s">
+        <v>13</v>
+      </c>
+      <c r="C164" t="s">
+        <v>34</v>
+      </c>
+      <c r="D164" t="s">
+        <v>60</v>
+      </c>
+      <c r="E164" t="s">
+        <v>65</v>
+      </c>
+      <c r="F164" t="s">
+        <v>68</v>
+      </c>
+      <c r="G164">
+        <v>101</v>
+      </c>
+      <c r="H164" s="2">
+        <v>46204.02234953704</v>
+      </c>
+      <c r="I164" s="2">
+        <v>46207.3324074074</v>
+      </c>
+      <c r="J164">
+        <v>5.690980943853473</v>
+      </c>
+      <c r="K164">
+        <v>5.690980943853473</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11">
+      <c r="A165" t="s">
+        <v>11</v>
+      </c>
+      <c r="B165" t="s">
+        <v>13</v>
+      </c>
+      <c r="C165" t="s">
+        <v>34</v>
+      </c>
+      <c r="D165" t="s">
+        <v>60</v>
+      </c>
+      <c r="E165" t="s">
+        <v>66</v>
+      </c>
+      <c r="F165" t="s">
+        <v>86</v>
+      </c>
+      <c r="G165">
+        <v>201</v>
+      </c>
+      <c r="H165" s="2">
+        <v>46204.02234953704</v>
+      </c>
+      <c r="I165" s="2">
+        <v>46207.3324074074</v>
+      </c>
+      <c r="J165">
+        <v>5.690980943853473</v>
+      </c>
+      <c r="K165">
+        <v>5.690980943853473</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11">
+      <c r="A166" t="s">
+        <v>11</v>
+      </c>
+      <c r="B166" t="s">
+        <v>13</v>
+      </c>
+      <c r="C166" t="s">
+        <v>34</v>
+      </c>
+      <c r="D166" t="s">
+        <v>60</v>
+      </c>
+      <c r="E166" t="s">
+        <v>67</v>
+      </c>
+      <c r="F166" t="s">
+        <v>87</v>
+      </c>
+      <c r="G166">
+        <v>301</v>
+      </c>
+      <c r="H166" s="2">
+        <v>46204.02234953704</v>
+      </c>
+      <c r="I166" s="2">
+        <v>46204.45003472222</v>
+      </c>
+      <c r="J166">
+        <v>5.867270425380308</v>
+      </c>
+      <c r="K166">
+        <v>5.867270425380308</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11">
+      <c r="A167" t="s">
+        <v>11</v>
+      </c>
+      <c r="B167" t="s">
+        <v>13</v>
+      </c>
+      <c r="C167" t="s">
+        <v>34</v>
+      </c>
+      <c r="D167" t="s">
+        <v>60</v>
+      </c>
+      <c r="E167" t="s">
+        <v>67</v>
+      </c>
+      <c r="F167" t="s">
+        <v>88</v>
+      </c>
+      <c r="G167">
+        <v>302</v>
+      </c>
+      <c r="H167" s="2">
+        <v>46205.02739583333</v>
+      </c>
+      <c r="I167" s="2">
+        <v>46205.74840277778</v>
+      </c>
+      <c r="J167">
+        <v>5.002728289455207</v>
+      </c>
+      <c r="K167">
+        <v>5.002728289455207</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11">
+      <c r="A168" t="s">
+        <v>11</v>
+      </c>
+      <c r="B168" t="s">
+        <v>13</v>
+      </c>
+      <c r="C168" t="s">
+        <v>34</v>
+      </c>
+      <c r="D168" t="s">
+        <v>60</v>
+      </c>
+      <c r="E168" t="s">
+        <v>67</v>
+      </c>
+      <c r="F168" t="s">
+        <v>89</v>
+      </c>
+      <c r="G168">
+        <v>303</v>
+      </c>
+      <c r="H168" s="2">
+        <v>46206.09667824074</v>
+      </c>
+      <c r="I168" s="2">
+        <v>46206.6680324074</v>
+      </c>
+      <c r="J168">
+        <v>6.868403886344059</v>
+      </c>
+      <c r="K168">
+        <v>6.868403886344059</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11">
+      <c r="A169" t="s">
+        <v>11</v>
+      </c>
+      <c r="B169" t="s">
+        <v>13</v>
+      </c>
+      <c r="C169" t="s">
+        <v>34</v>
+      </c>
+      <c r="D169" t="s">
+        <v>60</v>
+      </c>
+      <c r="E169" t="s">
+        <v>67</v>
+      </c>
+      <c r="F169" t="s">
+        <v>90</v>
+      </c>
+      <c r="G169">
+        <v>304</v>
+      </c>
+      <c r="H169" s="2">
+        <v>46207.26863425926</v>
+      </c>
+      <c r="I169" s="2">
+        <v>46207.3324074074</v>
+      </c>
+      <c r="J169">
+        <v>7.350097511109873</v>
+      </c>
+      <c r="K169">
+        <v>7.350097511109873</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
+      <c r="A170" t="s">
+        <v>11</v>
+      </c>
+      <c r="B170" t="s">
+        <v>13</v>
+      </c>
+      <c r="C170" t="s">
+        <v>34</v>
+      </c>
+      <c r="D170" t="s">
+        <v>61</v>
+      </c>
+      <c r="E170" t="s">
+        <v>65</v>
+      </c>
+      <c r="F170" t="s">
+        <v>68</v>
+      </c>
+      <c r="G170">
+        <v>101</v>
+      </c>
+      <c r="H170" s="2">
+        <v>46204.02234953704</v>
+      </c>
+      <c r="I170" s="2">
+        <v>46207.3324074074</v>
+      </c>
+      <c r="J170">
+        <v>2.208761678473779</v>
+      </c>
+      <c r="K170">
+        <v>2.208761678473779</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
+      <c r="A171" t="s">
+        <v>11</v>
+      </c>
+      <c r="B171" t="s">
+        <v>13</v>
+      </c>
+      <c r="C171" t="s">
+        <v>34</v>
+      </c>
+      <c r="D171" t="s">
+        <v>61</v>
+      </c>
+      <c r="E171" t="s">
+        <v>66</v>
+      </c>
+      <c r="F171" t="s">
+        <v>86</v>
+      </c>
+      <c r="G171">
+        <v>201</v>
+      </c>
+      <c r="H171" s="2">
+        <v>46204.02234953704</v>
+      </c>
+      <c r="I171" s="2">
+        <v>46207.3324074074</v>
+      </c>
+      <c r="J171">
+        <v>2.208761678473779</v>
+      </c>
+      <c r="K171">
+        <v>2.208761678473779</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11">
+      <c r="A172" t="s">
+        <v>11</v>
+      </c>
+      <c r="B172" t="s">
+        <v>13</v>
+      </c>
+      <c r="C172" t="s">
+        <v>34</v>
+      </c>
+      <c r="D172" t="s">
+        <v>61</v>
+      </c>
+      <c r="E172" t="s">
+        <v>67</v>
+      </c>
+      <c r="F172" t="s">
+        <v>87</v>
+      </c>
+      <c r="G172">
+        <v>301</v>
+      </c>
+      <c r="H172" s="2">
+        <v>46204.02234953704</v>
+      </c>
+      <c r="I172" s="2">
+        <v>46204.45003472222</v>
+      </c>
+      <c r="J172">
+        <v>2.274661641857774</v>
+      </c>
+      <c r="K172">
+        <v>2.274661641857774</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11">
+      <c r="A173" t="s">
+        <v>11</v>
+      </c>
+      <c r="B173" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" t="s">
+        <v>34</v>
+      </c>
+      <c r="D173" t="s">
+        <v>61</v>
+      </c>
+      <c r="E173" t="s">
+        <v>67</v>
+      </c>
+      <c r="F173" t="s">
+        <v>88</v>
+      </c>
+      <c r="G173">
+        <v>302</v>
+      </c>
+      <c r="H173" s="2">
+        <v>46205.02739583333</v>
+      </c>
+      <c r="I173" s="2">
+        <v>46205.74840277778</v>
+      </c>
+      <c r="J173">
+        <v>2.296125331809375</v>
+      </c>
+      <c r="K173">
+        <v>2.296125331809375</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
+      <c r="A174" t="s">
+        <v>11</v>
+      </c>
+      <c r="B174" t="s">
+        <v>13</v>
+      </c>
+      <c r="C174" t="s">
+        <v>34</v>
+      </c>
+      <c r="D174" t="s">
+        <v>61</v>
+      </c>
+      <c r="E174" t="s">
+        <v>67</v>
+      </c>
+      <c r="F174" t="s">
+        <v>89</v>
+      </c>
+      <c r="G174">
+        <v>303</v>
+      </c>
+      <c r="H174" s="2">
+        <v>46206.09667824074</v>
+      </c>
+      <c r="I174" s="2">
+        <v>46206.6680324074</v>
+      </c>
+      <c r="J174">
+        <v>2.021466357144072</v>
+      </c>
+      <c r="K174">
+        <v>2.021466357144072</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
+      <c r="A175" t="s">
+        <v>11</v>
+      </c>
+      <c r="B175" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" t="s">
+        <v>34</v>
+      </c>
+      <c r="D175" t="s">
+        <v>61</v>
+      </c>
+      <c r="E175" t="s">
+        <v>67</v>
+      </c>
+      <c r="F175" t="s">
+        <v>90</v>
+      </c>
+      <c r="G175">
+        <v>304</v>
+      </c>
+      <c r="H175" s="2">
+        <v>46207.26863425926</v>
+      </c>
+      <c r="I175" s="2">
+        <v>46207.3324074074</v>
+      </c>
+      <c r="J175">
+        <v>2.425228097784525</v>
+      </c>
+      <c r="K175">
+        <v>2.425228097784525</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
+      <c r="A176" t="s">
+        <v>11</v>
+      </c>
+      <c r="B176" t="s">
+        <v>13</v>
+      </c>
+      <c r="C176" t="s">
+        <v>34</v>
+      </c>
+      <c r="D176" t="s">
+        <v>62</v>
+      </c>
+      <c r="E176" t="s">
+        <v>65</v>
+      </c>
+      <c r="F176" t="s">
+        <v>68</v>
+      </c>
+      <c r="G176">
+        <v>101</v>
+      </c>
+      <c r="H176" s="2">
+        <v>46204.02232638889</v>
+      </c>
+      <c r="I176" s="2">
+        <v>46207.33239583333</v>
+      </c>
+      <c r="J176">
+        <v>5.037977720289904</v>
+      </c>
+      <c r="K176">
+        <v>5.037977720289904</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
+      <c r="A177" t="s">
+        <v>11</v>
+      </c>
+      <c r="B177" t="s">
+        <v>13</v>
+      </c>
+      <c r="C177" t="s">
+        <v>34</v>
+      </c>
+      <c r="D177" t="s">
+        <v>62</v>
+      </c>
+      <c r="E177" t="s">
+        <v>66</v>
+      </c>
+      <c r="F177" t="s">
+        <v>86</v>
+      </c>
+      <c r="G177">
+        <v>201</v>
+      </c>
+      <c r="H177" s="2">
+        <v>46204.02232638889</v>
+      </c>
+      <c r="I177" s="2">
+        <v>46207.33239583333</v>
+      </c>
+      <c r="J177">
+        <v>5.037977720289904</v>
+      </c>
+      <c r="K177">
+        <v>5.037977720289904</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
+      <c r="A178" t="s">
+        <v>11</v>
+      </c>
+      <c r="B178" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178" t="s">
+        <v>34</v>
+      </c>
+      <c r="D178" t="s">
+        <v>62</v>
+      </c>
+      <c r="E178" t="s">
+        <v>67</v>
+      </c>
+      <c r="F178" t="s">
+        <v>87</v>
+      </c>
+      <c r="G178">
+        <v>301</v>
+      </c>
+      <c r="H178" s="2">
+        <v>46204.02232638889</v>
+      </c>
+      <c r="I178" s="2">
+        <v>46204.45002314815</v>
+      </c>
+      <c r="J178">
+        <v>5.08846397087053</v>
+      </c>
+      <c r="K178">
+        <v>5.08846397087053</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11">
+      <c r="A179" t="s">
+        <v>11</v>
+      </c>
+      <c r="B179" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179" t="s">
+        <v>34</v>
+      </c>
+      <c r="D179" t="s">
+        <v>62</v>
+      </c>
+      <c r="E179" t="s">
+        <v>67</v>
+      </c>
+      <c r="F179" t="s">
+        <v>88</v>
+      </c>
+      <c r="G179">
+        <v>302</v>
+      </c>
+      <c r="H179" s="2">
+        <v>46205.02738425926</v>
+      </c>
+      <c r="I179" s="2">
+        <v>46205.74839120371</v>
+      </c>
+      <c r="J179">
+        <v>5.850465480446285</v>
+      </c>
+      <c r="K179">
+        <v>5.850465480446285</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11">
+      <c r="A180" t="s">
+        <v>11</v>
+      </c>
+      <c r="B180" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" t="s">
+        <v>34</v>
+      </c>
+      <c r="D180" t="s">
+        <v>62</v>
+      </c>
+      <c r="E180" t="s">
+        <v>67</v>
+      </c>
+      <c r="F180" t="s">
+        <v>89</v>
+      </c>
+      <c r="G180">
+        <v>303</v>
+      </c>
+      <c r="H180" s="2">
+        <v>46206.09666666666</v>
+      </c>
+      <c r="I180" s="2">
+        <v>46206.66802083333</v>
+      </c>
+      <c r="J180">
+        <v>5.3490013510671</v>
+      </c>
+      <c r="K180">
+        <v>5.3490013510671</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11">
+      <c r="A181" t="s">
+        <v>11</v>
+      </c>
+      <c r="B181" t="s">
+        <v>13</v>
+      </c>
+      <c r="C181" t="s">
+        <v>34</v>
+      </c>
+      <c r="D181" t="s">
+        <v>62</v>
+      </c>
+      <c r="E181" t="s">
+        <v>67</v>
+      </c>
+      <c r="F181" t="s">
+        <v>90</v>
+      </c>
+      <c r="G181">
+        <v>304</v>
+      </c>
+      <c r="H181" s="2">
+        <v>46207.26862268519</v>
+      </c>
+      <c r="I181" s="2">
+        <v>46207.33239583333</v>
+      </c>
+      <c r="J181">
+        <v>6.303252623230003</v>
+      </c>
+      <c r="K181">
+        <v>6.303252623230003</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11">
+      <c r="A182" t="s">
+        <v>11</v>
+      </c>
+      <c r="B182" t="s">
+        <v>13</v>
+      </c>
+      <c r="C182" t="s">
+        <v>34</v>
+      </c>
+      <c r="D182" t="s">
+        <v>63</v>
+      </c>
+      <c r="E182" t="s">
+        <v>65</v>
+      </c>
+      <c r="F182" t="s">
+        <v>68</v>
+      </c>
+      <c r="G182">
+        <v>101</v>
+      </c>
+      <c r="H182" s="2">
+        <v>46204.02232638889</v>
+      </c>
+      <c r="I182" s="2">
+        <v>46207.33239583333</v>
+      </c>
+      <c r="J182">
+        <v>3.09010363110375</v>
+      </c>
+      <c r="K182">
+        <v>3.09010363110375</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11">
+      <c r="A183" t="s">
+        <v>11</v>
+      </c>
+      <c r="B183" t="s">
+        <v>13</v>
+      </c>
+      <c r="C183" t="s">
+        <v>34</v>
+      </c>
+      <c r="D183" t="s">
+        <v>63</v>
+      </c>
+      <c r="E183" t="s">
+        <v>66</v>
+      </c>
+      <c r="F183" t="s">
+        <v>86</v>
+      </c>
+      <c r="G183">
+        <v>201</v>
+      </c>
+      <c r="H183" s="2">
+        <v>46204.02232638889</v>
+      </c>
+      <c r="I183" s="2">
+        <v>46207.33239583333</v>
+      </c>
+      <c r="J183">
+        <v>3.09010363110375</v>
+      </c>
+      <c r="K183">
+        <v>3.09010363110375</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11">
+      <c r="A184" t="s">
+        <v>11</v>
+      </c>
+      <c r="B184" t="s">
+        <v>13</v>
+      </c>
+      <c r="C184" t="s">
+        <v>34</v>
+      </c>
+      <c r="D184" t="s">
+        <v>63</v>
+      </c>
+      <c r="E184" t="s">
+        <v>67</v>
+      </c>
+      <c r="F184" t="s">
+        <v>87</v>
+      </c>
+      <c r="G184">
+        <v>301</v>
+      </c>
+      <c r="H184" s="2">
+        <v>46204.02232638889</v>
+      </c>
+      <c r="I184" s="2">
+        <v>46204.45002314815</v>
+      </c>
+      <c r="J184">
+        <v>3.055046313277442</v>
+      </c>
+      <c r="K184">
+        <v>3.055046313277442</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11">
+      <c r="A185" t="s">
+        <v>11</v>
+      </c>
+      <c r="B185" t="s">
+        <v>13</v>
+      </c>
+      <c r="C185" t="s">
+        <v>34</v>
+      </c>
+      <c r="D185" t="s">
+        <v>63</v>
+      </c>
+      <c r="E185" t="s">
+        <v>67</v>
+      </c>
+      <c r="F185" t="s">
+        <v>88</v>
+      </c>
+      <c r="G185">
+        <v>302</v>
+      </c>
+      <c r="H185" s="2">
+        <v>46205.02738425926</v>
+      </c>
+      <c r="I185" s="2">
+        <v>46205.74839120371</v>
+      </c>
+      <c r="J185">
+        <v>3.205586147890944</v>
+      </c>
+      <c r="K185">
+        <v>3.205586147890944</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11">
+      <c r="A186" t="s">
+        <v>11</v>
+      </c>
+      <c r="B186" t="s">
+        <v>13</v>
+      </c>
+      <c r="C186" t="s">
+        <v>34</v>
+      </c>
+      <c r="D186" t="s">
+        <v>63</v>
+      </c>
+      <c r="E186" t="s">
+        <v>67</v>
+      </c>
+      <c r="F186" t="s">
+        <v>89</v>
+      </c>
+      <c r="G186">
+        <v>303</v>
+      </c>
+      <c r="H186" s="2">
+        <v>46206.09666666666</v>
+      </c>
+      <c r="I186" s="2">
+        <v>46206.66802083333</v>
+      </c>
+      <c r="J186">
+        <v>3.078750218465228</v>
+      </c>
+      <c r="K186">
+        <v>3.078750218465228</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11">
+      <c r="A187" t="s">
+        <v>11</v>
+      </c>
+      <c r="B187" t="s">
+        <v>13</v>
+      </c>
+      <c r="C187" t="s">
+        <v>34</v>
+      </c>
+      <c r="D187" t="s">
+        <v>63</v>
+      </c>
+      <c r="E187" t="s">
+        <v>67</v>
+      </c>
+      <c r="F187" t="s">
+        <v>90</v>
+      </c>
+      <c r="G187">
+        <v>304</v>
+      </c>
+      <c r="H187" s="2">
+        <v>46207.26862268519</v>
+      </c>
+      <c r="I187" s="2">
+        <v>46207.33239583333</v>
+      </c>
+      <c r="J187">
+        <v>3.349614353845518</v>
+      </c>
+      <c r="K187">
+        <v>3.349614353845518</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11">
+      <c r="A188" t="s">
+        <v>11</v>
+      </c>
+      <c r="B188" t="s">
+        <v>13</v>
+      </c>
+      <c r="C188" t="s">
+        <v>34</v>
+      </c>
+      <c r="D188" t="s">
+        <v>64</v>
+      </c>
+      <c r="E188" t="s">
+        <v>65</v>
+      </c>
+      <c r="F188" t="s">
+        <v>68</v>
+      </c>
+      <c r="G188">
+        <v>101</v>
+      </c>
+      <c r="H188" s="2">
+        <v>46204.02231481481</v>
+      </c>
+      <c r="I188" s="2">
+        <v>46207.33238425926</v>
+      </c>
+      <c r="J188">
+        <v>1.865612698518206</v>
+      </c>
+      <c r="K188">
+        <v>1.865612698518206</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11">
+      <c r="A189" t="s">
+        <v>11</v>
+      </c>
+      <c r="B189" t="s">
+        <v>13</v>
+      </c>
+      <c r="C189" t="s">
+        <v>34</v>
+      </c>
+      <c r="D189" t="s">
+        <v>64</v>
+      </c>
+      <c r="E189" t="s">
+        <v>66</v>
+      </c>
+      <c r="F189" t="s">
+        <v>86</v>
+      </c>
+      <c r="G189">
+        <v>201</v>
+      </c>
+      <c r="H189" s="2">
+        <v>46204.02231481481</v>
+      </c>
+      <c r="I189" s="2">
+        <v>46207.33238425926</v>
+      </c>
+      <c r="J189">
+        <v>1.865612698518206</v>
+      </c>
+      <c r="K189">
+        <v>1.865612698518206</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11">
+      <c r="A190" t="s">
+        <v>11</v>
+      </c>
+      <c r="B190" t="s">
+        <v>13</v>
+      </c>
+      <c r="C190" t="s">
+        <v>34</v>
+      </c>
+      <c r="D190" t="s">
+        <v>64</v>
+      </c>
+      <c r="E190" t="s">
+        <v>67</v>
+      </c>
+      <c r="F190" t="s">
+        <v>87</v>
+      </c>
+      <c r="G190">
+        <v>301</v>
+      </c>
+      <c r="H190" s="2">
+        <v>46204.02231481481</v>
+      </c>
+      <c r="I190" s="2">
+        <v>46204.45001157407</v>
+      </c>
+      <c r="J190">
+        <v>1.809970793828339</v>
+      </c>
+      <c r="K190">
+        <v>1.809970793828339</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11">
+      <c r="A191" t="s">
+        <v>11</v>
+      </c>
+      <c r="B191" t="s">
+        <v>13</v>
+      </c>
+      <c r="C191" t="s">
+        <v>34</v>
+      </c>
+      <c r="D191" t="s">
+        <v>64</v>
+      </c>
+      <c r="E191" t="s">
+        <v>67</v>
+      </c>
+      <c r="F191" t="s">
+        <v>88</v>
+      </c>
+      <c r="G191">
+        <v>302</v>
+      </c>
+      <c r="H191" s="2">
+        <v>46205.02737268519</v>
+      </c>
+      <c r="I191" s="2">
+        <v>46205.74837962963</v>
+      </c>
+      <c r="J191">
+        <v>1.905368949999892</v>
+      </c>
+      <c r="K191">
+        <v>1.905368949999892</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11">
+      <c r="A192" t="s">
+        <v>11</v>
+      </c>
+      <c r="B192" t="s">
+        <v>13</v>
+      </c>
+      <c r="C192" t="s">
+        <v>34</v>
+      </c>
+      <c r="D192" t="s">
+        <v>64</v>
+      </c>
+      <c r="E192" t="s">
+        <v>67</v>
+      </c>
+      <c r="F192" t="s">
+        <v>89</v>
+      </c>
+      <c r="G192">
+        <v>303</v>
+      </c>
+      <c r="H192" s="2">
+        <v>46206.0966550926</v>
+      </c>
+      <c r="I192" s="2">
+        <v>46206.66800925926</v>
+      </c>
+      <c r="J192">
+        <v>1.823397200919778</v>
+      </c>
+      <c r="K192">
+        <v>1.823397200919778</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11">
+      <c r="A193" t="s">
+        <v>11</v>
+      </c>
+      <c r="B193" t="s">
+        <v>13</v>
+      </c>
+      <c r="C193" t="s">
+        <v>34</v>
+      </c>
+      <c r="D193" t="s">
+        <v>64</v>
+      </c>
+      <c r="E193" t="s">
+        <v>67</v>
+      </c>
+      <c r="F193" t="s">
+        <v>90</v>
+      </c>
+      <c r="G193">
+        <v>304</v>
+      </c>
+      <c r="H193" s="2">
+        <v>46207.26861111111</v>
+      </c>
+      <c r="I193" s="2">
+        <v>46207.33238425926</v>
+      </c>
+      <c r="J193">
+        <v>1.972364653958022</v>
+      </c>
+      <c r="K193">
+        <v>1.972364653958022</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11">
+      <c r="A194" t="s">
+        <v>11</v>
+      </c>
+      <c r="B194" t="s">
+        <v>14</v>
+      </c>
+      <c r="C194" t="s">
+        <v>35</v>
+      </c>
+      <c r="D194" t="s">
+        <v>46</v>
+      </c>
+      <c r="E194" t="s">
+        <v>65</v>
+      </c>
+      <c r="F194" t="s">
+        <v>68</v>
+      </c>
+      <c r="G194">
+        <v>101</v>
+      </c>
+      <c r="H194" s="2">
+        <v>46207.11439814815</v>
+      </c>
+      <c r="I194" s="2">
+        <v>46208.49990740741</v>
+      </c>
+      <c r="J194">
+        <v>1.718623046793465</v>
+      </c>
+      <c r="K194">
+        <v>1.718623046793465</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11">
+      <c r="A195" t="s">
+        <v>11</v>
+      </c>
+      <c r="B195" t="s">
+        <v>14</v>
+      </c>
+      <c r="C195" t="s">
+        <v>35</v>
+      </c>
+      <c r="D195" t="s">
+        <v>46</v>
+      </c>
+      <c r="E195" t="s">
+        <v>66</v>
+      </c>
+      <c r="F195" t="s">
+        <v>86</v>
+      </c>
+      <c r="G195">
+        <v>201</v>
+      </c>
+      <c r="H195" s="2">
+        <v>46207.11439814815</v>
+      </c>
+      <c r="I195" s="2">
+        <v>46208.49990740741</v>
+      </c>
+      <c r="J195">
+        <v>1.718623046793465</v>
+      </c>
+      <c r="K195">
+        <v>1.718623046793465</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11">
+      <c r="A196" t="s">
+        <v>11</v>
+      </c>
+      <c r="B196" t="s">
+        <v>14</v>
+      </c>
+      <c r="C196" t="s">
+        <v>35</v>
+      </c>
+      <c r="D196" t="s">
+        <v>46</v>
+      </c>
+      <c r="E196" t="s">
+        <v>67</v>
+      </c>
+      <c r="F196" t="s">
+        <v>90</v>
+      </c>
+      <c r="G196">
+        <v>304</v>
+      </c>
+      <c r="H196" s="2">
+        <v>46207.11439814815</v>
+      </c>
+      <c r="I196" s="2">
+        <v>46207.13734953704</v>
+      </c>
+      <c r="J196">
+        <v>1.970153994820802</v>
+      </c>
+      <c r="K196">
+        <v>1.970153994820802</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11">
+      <c r="A197" t="s">
+        <v>11</v>
+      </c>
+      <c r="B197" t="s">
+        <v>14</v>
+      </c>
+      <c r="C197" t="s">
+        <v>35</v>
+      </c>
+      <c r="D197" t="s">
+        <v>46</v>
+      </c>
+      <c r="E197" t="s">
+        <v>67</v>
+      </c>
+      <c r="F197" t="s">
+        <v>91</v>
+      </c>
+      <c r="G197">
+        <v>305</v>
+      </c>
+      <c r="H197" s="2">
+        <v>46208.47668981482</v>
+      </c>
+      <c r="I197" s="2">
+        <v>46208.49990740741</v>
+      </c>
+      <c r="J197">
+        <v>1.735084218293082</v>
+      </c>
+      <c r="K197">
+        <v>1.735084218293082</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11">
+      <c r="A198" t="s">
+        <v>11</v>
+      </c>
+      <c r="B198" t="s">
+        <v>14</v>
+      </c>
+      <c r="C198" t="s">
+        <v>36</v>
+      </c>
+      <c r="D198" t="s">
+        <v>52</v>
+      </c>
+      <c r="E198" t="s">
+        <v>65</v>
+      </c>
+      <c r="F198" t="s">
+        <v>68</v>
+      </c>
+      <c r="G198">
+        <v>101</v>
+      </c>
+      <c r="H198" s="2">
+        <v>46204.54361111111</v>
+      </c>
+      <c r="I198" s="2">
+        <v>46208.3160300926</v>
+      </c>
+      <c r="J198">
+        <v>1.528077702610358</v>
+      </c>
+      <c r="K198">
+        <v>1.528077702610358</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11">
+      <c r="A199" t="s">
+        <v>11</v>
+      </c>
+      <c r="B199" t="s">
+        <v>14</v>
+      </c>
+      <c r="C199" t="s">
+        <v>36</v>
+      </c>
+      <c r="D199" t="s">
+        <v>52</v>
+      </c>
+      <c r="E199" t="s">
+        <v>66</v>
+      </c>
+      <c r="F199" t="s">
+        <v>86</v>
+      </c>
+      <c r="G199">
+        <v>201</v>
+      </c>
+      <c r="H199" s="2">
+        <v>46204.54361111111</v>
+      </c>
+      <c r="I199" s="2">
+        <v>46208.3160300926</v>
+      </c>
+      <c r="J199">
+        <v>1.528077702610358</v>
+      </c>
+      <c r="K199">
+        <v>1.528077702610358</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11">
+      <c r="A200" t="s">
+        <v>11</v>
+      </c>
+      <c r="B200" t="s">
+        <v>14</v>
+      </c>
+      <c r="C200" t="s">
+        <v>36</v>
+      </c>
+      <c r="D200" t="s">
+        <v>52</v>
+      </c>
+      <c r="E200" t="s">
+        <v>67</v>
+      </c>
+      <c r="F200" t="s">
+        <v>87</v>
+      </c>
+      <c r="G200">
+        <v>301</v>
+      </c>
+      <c r="H200" s="2">
+        <v>46204.54361111111</v>
+      </c>
+      <c r="I200" s="2">
+        <v>46204.55734953703</v>
+      </c>
+      <c r="J200">
+        <v>1.544236547921107</v>
+      </c>
+      <c r="K200">
+        <v>1.544236547921107</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11">
+      <c r="A201" t="s">
+        <v>11</v>
+      </c>
+      <c r="B201" t="s">
+        <v>14</v>
+      </c>
+      <c r="C201" t="s">
+        <v>36</v>
+      </c>
+      <c r="D201" t="s">
+        <v>52</v>
+      </c>
+      <c r="E201" t="s">
+        <v>67</v>
+      </c>
+      <c r="F201" t="s">
+        <v>89</v>
+      </c>
+      <c r="G201">
+        <v>303</v>
+      </c>
+      <c r="H201" s="2">
+        <v>46206.9258449074</v>
+      </c>
+      <c r="I201" s="2">
+        <v>46206.93956018519</v>
+      </c>
+      <c r="J201">
+        <v>1.603204582758952</v>
+      </c>
+      <c r="K201">
+        <v>1.603204582758952</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11">
+      <c r="A202" t="s">
+        <v>11</v>
+      </c>
+      <c r="B202" t="s">
+        <v>14</v>
+      </c>
+      <c r="C202" t="s">
+        <v>36</v>
+      </c>
+      <c r="D202" t="s">
+        <v>52</v>
+      </c>
+      <c r="E202" t="s">
+        <v>67</v>
+      </c>
+      <c r="F202" t="s">
+        <v>91</v>
+      </c>
+      <c r="G202">
+        <v>305</v>
+      </c>
+      <c r="H202" s="2">
+        <v>46208.30229166667</v>
+      </c>
+      <c r="I202" s="2">
+        <v>46208.3160300926</v>
+      </c>
+      <c r="J202">
+        <v>1.409765383271333</v>
+      </c>
+      <c r="K202">
+        <v>1.409765383271333</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11">
+      <c r="A203" t="s">
+        <v>11</v>
+      </c>
+      <c r="B203" t="s">
+        <v>14</v>
+      </c>
+      <c r="C203" t="s">
+        <v>37</v>
+      </c>
+      <c r="D203" t="s">
+        <v>49</v>
+      </c>
+      <c r="E203" t="s">
+        <v>65</v>
+      </c>
+      <c r="F203" t="s">
+        <v>68</v>
+      </c>
+      <c r="G203">
+        <v>101</v>
+      </c>
+      <c r="H203" s="2">
+        <v>46207.23271990741</v>
+      </c>
+      <c r="I203" s="2">
+        <v>46207.23274305555</v>
+      </c>
+      <c r="J203">
+        <v>1.461178078579722</v>
+      </c>
+      <c r="K203">
+        <v>1.461178078579722</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11">
+      <c r="A204" t="s">
+        <v>11</v>
+      </c>
+      <c r="B204" t="s">
+        <v>14</v>
+      </c>
+      <c r="C204" t="s">
+        <v>37</v>
+      </c>
+      <c r="D204" t="s">
+        <v>49</v>
+      </c>
+      <c r="E204" t="s">
+        <v>66</v>
+      </c>
+      <c r="F204" t="s">
+        <v>86</v>
+      </c>
+      <c r="G204">
+        <v>201</v>
+      </c>
+      <c r="H204" s="2">
+        <v>46207.23271990741</v>
+      </c>
+      <c r="I204" s="2">
+        <v>46207.23274305555</v>
+      </c>
+      <c r="J204">
+        <v>1.461178078579722</v>
+      </c>
+      <c r="K204">
+        <v>1.461178078579722</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11">
+      <c r="A205" t="s">
+        <v>11</v>
+      </c>
+      <c r="B205" t="s">
+        <v>14</v>
+      </c>
+      <c r="C205" t="s">
+        <v>37</v>
+      </c>
+      <c r="D205" t="s">
+        <v>49</v>
+      </c>
+      <c r="E205" t="s">
+        <v>67</v>
+      </c>
+      <c r="F205" t="s">
+        <v>90</v>
+      </c>
+      <c r="G205">
+        <v>304</v>
+      </c>
+      <c r="H205" s="2">
+        <v>46207.23271990741</v>
+      </c>
+      <c r="I205" s="2">
+        <v>46207.23274305555</v>
+      </c>
+      <c r="J205">
+        <v>1.461178078579722</v>
+      </c>
+      <c r="K205">
+        <v>1.461178078579722</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11">
+      <c r="A206" t="s">
+        <v>11</v>
+      </c>
+      <c r="B206" t="s">
+        <v>14</v>
+      </c>
+      <c r="C206" t="s">
+        <v>37</v>
+      </c>
+      <c r="D206" t="s">
+        <v>50</v>
+      </c>
+      <c r="E206" t="s">
+        <v>65</v>
+      </c>
+      <c r="F206" t="s">
+        <v>68</v>
+      </c>
+      <c r="G206">
+        <v>101</v>
+      </c>
+      <c r="H206" s="2">
+        <v>46207.23271990741</v>
+      </c>
+      <c r="I206" s="2">
+        <v>46207.23274305555</v>
+      </c>
+      <c r="J206">
+        <v>1.990153757485191</v>
+      </c>
+      <c r="K206">
+        <v>1.990153757485191</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11">
+      <c r="A207" t="s">
+        <v>11</v>
+      </c>
+      <c r="B207" t="s">
+        <v>14</v>
+      </c>
+      <c r="C207" t="s">
+        <v>37</v>
+      </c>
+      <c r="D207" t="s">
+        <v>50</v>
+      </c>
+      <c r="E207" t="s">
+        <v>66</v>
+      </c>
+      <c r="F207" t="s">
+        <v>86</v>
+      </c>
+      <c r="G207">
+        <v>201</v>
+      </c>
+      <c r="H207" s="2">
+        <v>46207.23271990741</v>
+      </c>
+      <c r="I207" s="2">
+        <v>46207.23274305555</v>
+      </c>
+      <c r="J207">
+        <v>1.990153757485191</v>
+      </c>
+      <c r="K207">
+        <v>1.990153757485191</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11">
+      <c r="A208" t="s">
+        <v>11</v>
+      </c>
+      <c r="B208" t="s">
+        <v>14</v>
+      </c>
+      <c r="C208" t="s">
+        <v>37</v>
+      </c>
+      <c r="D208" t="s">
+        <v>50</v>
+      </c>
+      <c r="E208" t="s">
+        <v>67</v>
+      </c>
+      <c r="F208" t="s">
+        <v>90</v>
+      </c>
+      <c r="G208">
+        <v>304</v>
+      </c>
+      <c r="H208" s="2">
+        <v>46207.23271990741</v>
+      </c>
+      <c r="I208" s="2">
+        <v>46207.23274305555</v>
+      </c>
+      <c r="J208">
+        <v>1.990153757485191</v>
+      </c>
+      <c r="K208">
+        <v>1.990153757485191</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11">
+      <c r="A209" t="s">
+        <v>11</v>
+      </c>
+      <c r="B209" t="s">
+        <v>14</v>
+      </c>
+      <c r="C209" t="s">
+        <v>38</v>
+      </c>
+      <c r="D209" t="s">
+        <v>51</v>
+      </c>
+      <c r="E209" t="s">
+        <v>65</v>
+      </c>
+      <c r="F209" t="s">
+        <v>68</v>
+      </c>
+      <c r="G209">
+        <v>101</v>
+      </c>
+      <c r="H209" s="2">
+        <v>46207.66858796297</v>
+      </c>
+      <c r="I209" s="2">
+        <v>46207.68778935185</v>
+      </c>
+      <c r="J209">
+        <v>2.128471896743432</v>
+      </c>
+      <c r="K209">
+        <v>2.128471896743432</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11">
+      <c r="A210" t="s">
+        <v>11</v>
+      </c>
+      <c r="B210" t="s">
+        <v>14</v>
+      </c>
+      <c r="C210" t="s">
+        <v>38</v>
+      </c>
+      <c r="D210" t="s">
+        <v>51</v>
+      </c>
+      <c r="E210" t="s">
+        <v>66</v>
+      </c>
+      <c r="F210" t="s">
+        <v>86</v>
+      </c>
+      <c r="G210">
+        <v>201</v>
+      </c>
+      <c r="H210" s="2">
+        <v>46207.66858796297</v>
+      </c>
+      <c r="I210" s="2">
+        <v>46207.68778935185</v>
+      </c>
+      <c r="J210">
+        <v>2.128471896743432</v>
+      </c>
+      <c r="K210">
+        <v>2.128471896743432</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11">
+      <c r="A211" t="s">
+        <v>11</v>
+      </c>
+      <c r="B211" t="s">
+        <v>14</v>
+      </c>
+      <c r="C211" t="s">
+        <v>38</v>
+      </c>
+      <c r="D211" t="s">
+        <v>51</v>
+      </c>
+      <c r="E211" t="s">
+        <v>67</v>
+      </c>
+      <c r="F211" t="s">
+        <v>90</v>
+      </c>
+      <c r="G211">
+        <v>304</v>
+      </c>
+      <c r="H211" s="2">
+        <v>46207.66858796297</v>
+      </c>
+      <c r="I211" s="2">
+        <v>46207.68778935185</v>
+      </c>
+      <c r="J211">
+        <v>2.128471896743432</v>
+      </c>
+      <c r="K211">
+        <v>2.128471896743432</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11">
+      <c r="A212" t="s">
+        <v>11</v>
+      </c>
+      <c r="B212" t="s">
+        <v>14</v>
+      </c>
+      <c r="C212" t="s">
+        <v>39</v>
+      </c>
+      <c r="D212" t="s">
+        <v>46</v>
+      </c>
+      <c r="E212" t="s">
+        <v>65</v>
+      </c>
+      <c r="F212" t="s">
+        <v>68</v>
+      </c>
+      <c r="G212">
+        <v>101</v>
+      </c>
+      <c r="H212" s="2">
+        <v>46209.17533564815</v>
+      </c>
+      <c r="I212" s="2">
+        <v>46209.19881944444</v>
+      </c>
+      <c r="J212">
+        <v>3.287749400794237</v>
+      </c>
+      <c r="K212">
+        <v>3.287749400794237</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11">
+      <c r="A213" t="s">
+        <v>11</v>
+      </c>
+      <c r="B213" t="s">
+        <v>14</v>
+      </c>
+      <c r="C213" t="s">
+        <v>39</v>
+      </c>
+      <c r="D213" t="s">
+        <v>46</v>
+      </c>
+      <c r="E213" t="s">
+        <v>66</v>
+      </c>
+      <c r="F213" t="s">
+        <v>92</v>
+      </c>
+      <c r="G213">
+        <v>202</v>
+      </c>
+      <c r="H213" s="2">
+        <v>46209.17533564815</v>
+      </c>
+      <c r="I213" s="2">
+        <v>46209.19881944444</v>
+      </c>
+      <c r="J213">
+        <v>3.287749400794237</v>
+      </c>
+      <c r="K213">
+        <v>3.287749400794237</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11">
+      <c r="A214" t="s">
+        <v>11</v>
+      </c>
+      <c r="B214" t="s">
+        <v>14</v>
+      </c>
+      <c r="C214" t="s">
+        <v>39</v>
+      </c>
+      <c r="D214" t="s">
+        <v>46</v>
+      </c>
+      <c r="E214" t="s">
+        <v>67</v>
+      </c>
+      <c r="F214" t="s">
+        <v>93</v>
+      </c>
+      <c r="G214">
+        <v>306</v>
+      </c>
+      <c r="H214" s="2">
+        <v>46209.17533564815</v>
+      </c>
+      <c r="I214" s="2">
+        <v>46209.19881944444</v>
+      </c>
+      <c r="J214">
+        <v>3.287749400794237</v>
+      </c>
+      <c r="K214">
+        <v>3.287749400794237</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11">
+      <c r="A215" t="s">
+        <v>11</v>
+      </c>
+      <c r="B215" t="s">
+        <v>14</v>
+      </c>
+      <c r="C215" t="s">
+        <v>40</v>
+      </c>
+      <c r="D215" t="s">
+        <v>49</v>
+      </c>
+      <c r="E215" t="s">
+        <v>65</v>
+      </c>
+      <c r="F215" t="s">
+        <v>68</v>
+      </c>
+      <c r="G215">
+        <v>101</v>
+      </c>
+      <c r="H215" s="2">
+        <v>46210.58523148148</v>
+      </c>
+      <c r="I215" s="2">
+        <v>46210.61064814815</v>
+      </c>
+      <c r="J215">
+        <v>1.647806404612758</v>
+      </c>
+      <c r="K215">
+        <v>1.647806404612758</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11">
+      <c r="A216" t="s">
+        <v>11</v>
+      </c>
+      <c r="B216" t="s">
+        <v>14</v>
+      </c>
+      <c r="C216" t="s">
+        <v>40</v>
+      </c>
+      <c r="D216" t="s">
+        <v>49</v>
+      </c>
+      <c r="E216" t="s">
+        <v>66</v>
+      </c>
+      <c r="F216" t="s">
+        <v>92</v>
+      </c>
+      <c r="G216">
+        <v>202</v>
+      </c>
+      <c r="H216" s="2">
+        <v>46210.58523148148</v>
+      </c>
+      <c r="I216" s="2">
+        <v>46210.61064814815</v>
+      </c>
+      <c r="J216">
+        <v>1.647806404612758</v>
+      </c>
+      <c r="K216">
+        <v>1.647806404612758</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11">
+      <c r="A217" t="s">
+        <v>11</v>
+      </c>
+      <c r="B217" t="s">
+        <v>14</v>
+      </c>
+      <c r="C217" t="s">
+        <v>40</v>
+      </c>
+      <c r="D217" t="s">
+        <v>49</v>
+      </c>
+      <c r="E217" t="s">
+        <v>67</v>
+      </c>
+      <c r="F217" t="s">
+        <v>94</v>
+      </c>
+      <c r="G217">
+        <v>307</v>
+      </c>
+      <c r="H217" s="2">
+        <v>46210.58523148148</v>
+      </c>
+      <c r="I217" s="2">
+        <v>46210.61064814815</v>
+      </c>
+      <c r="J217">
+        <v>1.647806404612758</v>
+      </c>
+      <c r="K217">
+        <v>1.647806404612758</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11">
+      <c r="A218" t="s">
+        <v>11</v>
+      </c>
+      <c r="B218" t="s">
+        <v>14</v>
+      </c>
+      <c r="C218" t="s">
+        <v>40</v>
+      </c>
+      <c r="D218" t="s">
+        <v>50</v>
+      </c>
+      <c r="E218" t="s">
+        <v>65</v>
+      </c>
+      <c r="F218" t="s">
+        <v>68</v>
+      </c>
+      <c r="G218">
+        <v>101</v>
+      </c>
+      <c r="H218" s="2">
+        <v>46210.58523148148</v>
+      </c>
+      <c r="I218" s="2">
+        <v>46210.61064814815</v>
+      </c>
+      <c r="J218">
+        <v>2.26867574331909</v>
+      </c>
+      <c r="K218">
+        <v>2.26867574331909</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11">
+      <c r="A219" t="s">
+        <v>11</v>
+      </c>
+      <c r="B219" t="s">
+        <v>14</v>
+      </c>
+      <c r="C219" t="s">
+        <v>40</v>
+      </c>
+      <c r="D219" t="s">
+        <v>50</v>
+      </c>
+      <c r="E219" t="s">
+        <v>66</v>
+      </c>
+      <c r="F219" t="s">
+        <v>92</v>
+      </c>
+      <c r="G219">
+        <v>202</v>
+      </c>
+      <c r="H219" s="2">
+        <v>46210.58523148148</v>
+      </c>
+      <c r="I219" s="2">
+        <v>46210.61064814815</v>
+      </c>
+      <c r="J219">
+        <v>2.26867574331909</v>
+      </c>
+      <c r="K219">
+        <v>2.26867574331909</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11">
+      <c r="A220" t="s">
+        <v>11</v>
+      </c>
+      <c r="B220" t="s">
+        <v>14</v>
+      </c>
+      <c r="C220" t="s">
+        <v>40</v>
+      </c>
+      <c r="D220" t="s">
+        <v>50</v>
+      </c>
+      <c r="E220" t="s">
+        <v>67</v>
+      </c>
+      <c r="F220" t="s">
+        <v>94</v>
+      </c>
+      <c r="G220">
+        <v>307</v>
+      </c>
+      <c r="H220" s="2">
+        <v>46210.58523148148</v>
+      </c>
+      <c r="I220" s="2">
+        <v>46210.61064814815</v>
+      </c>
+      <c r="J220">
+        <v>2.26867574331909</v>
+      </c>
+      <c r="K220">
+        <v>2.26867574331909</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11">
+      <c r="A221" t="s">
+        <v>11</v>
+      </c>
+      <c r="B221" t="s">
+        <v>14</v>
+      </c>
+      <c r="C221" t="s">
+        <v>41</v>
+      </c>
+      <c r="D221" t="s">
+        <v>51</v>
+      </c>
+      <c r="E221" t="s">
+        <v>65</v>
+      </c>
+      <c r="F221" t="s">
+        <v>68</v>
+      </c>
+      <c r="G221">
+        <v>101</v>
+      </c>
+      <c r="H221" s="2">
+        <v>46210.86798611111</v>
+      </c>
+      <c r="I221" s="2">
+        <v>46210.88290509259</v>
+      </c>
+      <c r="J221">
+        <v>2.721736457511896</v>
+      </c>
+      <c r="K221">
+        <v>2.721736457511896</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11">
+      <c r="A222" t="s">
+        <v>11</v>
+      </c>
+      <c r="B222" t="s">
+        <v>14</v>
+      </c>
+      <c r="C222" t="s">
+        <v>41</v>
+      </c>
+      <c r="D222" t="s">
+        <v>51</v>
+      </c>
+      <c r="E222" t="s">
+        <v>66</v>
+      </c>
+      <c r="F222" t="s">
+        <v>92</v>
+      </c>
+      <c r="G222">
+        <v>202</v>
+      </c>
+      <c r="H222" s="2">
+        <v>46210.86798611111</v>
+      </c>
+      <c r="I222" s="2">
+        <v>46210.88290509259</v>
+      </c>
+      <c r="J222">
+        <v>2.721736457511896</v>
+      </c>
+      <c r="K222">
+        <v>2.721736457511896</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11">
+      <c r="A223" t="s">
+        <v>11</v>
+      </c>
+      <c r="B223" t="s">
+        <v>14</v>
+      </c>
+      <c r="C223" t="s">
+        <v>41</v>
+      </c>
+      <c r="D223" t="s">
+        <v>51</v>
+      </c>
+      <c r="E223" t="s">
+        <v>67</v>
+      </c>
+      <c r="F223" t="s">
+        <v>94</v>
+      </c>
+      <c r="G223">
+        <v>307</v>
+      </c>
+      <c r="H223" s="2">
+        <v>46210.86798611111</v>
+      </c>
+      <c r="I223" s="2">
+        <v>46210.88290509259</v>
+      </c>
+      <c r="J223">
+        <v>2.721736457511896</v>
+      </c>
+      <c r="K223">
+        <v>2.721736457511896</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11">
+      <c r="A224" t="s">
+        <v>11</v>
+      </c>
+      <c r="B224" t="s">
+        <v>14</v>
+      </c>
+      <c r="C224" t="s">
+        <v>42</v>
+      </c>
+      <c r="D224" t="s">
+        <v>52</v>
+      </c>
+      <c r="E224" t="s">
+        <v>65</v>
+      </c>
+      <c r="F224" t="s">
+        <v>68</v>
+      </c>
+      <c r="G224">
+        <v>101</v>
+      </c>
+      <c r="H224" s="2">
+        <v>46206.20539351852</v>
+      </c>
+      <c r="I224" s="2">
+        <v>46207.26991898148</v>
+      </c>
+      <c r="J224">
+        <v>1.718217672992258</v>
+      </c>
+      <c r="K224">
+        <v>1.718217672992258</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11">
+      <c r="A225" t="s">
+        <v>11</v>
+      </c>
+      <c r="B225" t="s">
+        <v>14</v>
+      </c>
+      <c r="C225" t="s">
+        <v>42</v>
+      </c>
+      <c r="D225" t="s">
+        <v>52</v>
+      </c>
+      <c r="E225" t="s">
+        <v>66</v>
+      </c>
+      <c r="F225" t="s">
+        <v>86</v>
+      </c>
+      <c r="G225">
+        <v>201</v>
+      </c>
+      <c r="H225" s="2">
+        <v>46206.20539351852</v>
+      </c>
+      <c r="I225" s="2">
+        <v>46207.26991898148</v>
+      </c>
+      <c r="J225">
+        <v>1.718217672992258</v>
+      </c>
+      <c r="K225">
+        <v>1.718217672992258</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11">
+      <c r="A226" t="s">
+        <v>11</v>
+      </c>
+      <c r="B226" t="s">
+        <v>14</v>
+      </c>
+      <c r="C226" t="s">
+        <v>42</v>
+      </c>
+      <c r="D226" t="s">
+        <v>52</v>
+      </c>
+      <c r="E226" t="s">
+        <v>67</v>
+      </c>
+      <c r="F226" t="s">
+        <v>89</v>
+      </c>
+      <c r="G226">
+        <v>303</v>
+      </c>
+      <c r="H226" s="2">
+        <v>46206.20539351852</v>
+      </c>
+      <c r="I226" s="2">
+        <v>46206.21914351852</v>
+      </c>
+      <c r="J226">
+        <v>1.66438975798056</v>
+      </c>
+      <c r="K226">
+        <v>1.66438975798056</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11">
+      <c r="A227" t="s">
+        <v>11</v>
+      </c>
+      <c r="B227" t="s">
+        <v>14</v>
+      </c>
+      <c r="C227" t="s">
+        <v>42</v>
+      </c>
+      <c r="D227" t="s">
+        <v>52</v>
+      </c>
+      <c r="E227" t="s">
+        <v>67</v>
+      </c>
+      <c r="F227" t="s">
+        <v>90</v>
+      </c>
+      <c r="G227">
+        <v>304</v>
+      </c>
+      <c r="H227" s="2">
+        <v>46207.25616898148</v>
+      </c>
+      <c r="I227" s="2">
+        <v>46207.26991898148</v>
+      </c>
+      <c r="J227">
+        <v>1.77599308064014</v>
+      </c>
+      <c r="K227">
+        <v>1.77599308064014</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11">
+      <c r="A228" t="s">
+        <v>11</v>
+      </c>
+      <c r="B228" t="s">
+        <v>14</v>
+      </c>
+      <c r="C228" t="s">
+        <v>43</v>
+      </c>
+      <c r="D228" t="s">
+        <v>49</v>
+      </c>
+      <c r="E228" t="s">
+        <v>65</v>
+      </c>
+      <c r="F228" t="s">
+        <v>68</v>
+      </c>
+      <c r="G228">
+        <v>101</v>
+      </c>
+      <c r="H228" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I228" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J228">
+        <v>1.834107090255503</v>
+      </c>
+      <c r="K228">
+        <v>1.834107090255503</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11">
+      <c r="A229" t="s">
+        <v>11</v>
+      </c>
+      <c r="B229" t="s">
+        <v>14</v>
+      </c>
+      <c r="C229" t="s">
+        <v>43</v>
+      </c>
+      <c r="D229" t="s">
+        <v>49</v>
+      </c>
+      <c r="E229" t="s">
+        <v>66</v>
+      </c>
+      <c r="F229" t="s">
+        <v>86</v>
+      </c>
+      <c r="G229">
+        <v>201</v>
+      </c>
+      <c r="H229" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I229" s="2">
+        <v>46207.50067129629</v>
+      </c>
+      <c r="J229">
+        <v>1.655153302224898</v>
+      </c>
+      <c r="K229">
+        <v>1.655153302224898</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11">
+      <c r="A230" t="s">
+        <v>11</v>
+      </c>
+      <c r="B230" t="s">
+        <v>14</v>
+      </c>
+      <c r="C230" t="s">
+        <v>43</v>
+      </c>
+      <c r="D230" t="s">
+        <v>49</v>
+      </c>
+      <c r="E230" t="s">
+        <v>66</v>
+      </c>
+      <c r="F230" t="s">
+        <v>92</v>
+      </c>
+      <c r="G230">
+        <v>202</v>
+      </c>
+      <c r="H230" s="2">
+        <v>46211.69054398148</v>
+      </c>
+      <c r="I230" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J230">
+        <v>2.077295089828365</v>
+      </c>
+      <c r="K230">
+        <v>2.077295089828365</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11">
+      <c r="A231" t="s">
+        <v>11</v>
+      </c>
+      <c r="B231" t="s">
+        <v>14</v>
+      </c>
+      <c r="C231" t="s">
+        <v>43</v>
+      </c>
+      <c r="D231" t="s">
+        <v>49</v>
+      </c>
+      <c r="E231" t="s">
+        <v>67</v>
+      </c>
+      <c r="F231" t="s">
+        <v>90</v>
+      </c>
+      <c r="G231">
+        <v>304</v>
+      </c>
+      <c r="H231" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I231" s="2">
+        <v>46207.50067129629</v>
+      </c>
+      <c r="J231">
+        <v>1.655153302224898</v>
+      </c>
+      <c r="K231">
+        <v>1.655153302224898</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11">
+      <c r="A232" t="s">
+        <v>11</v>
+      </c>
+      <c r="B232" t="s">
+        <v>14</v>
+      </c>
+      <c r="C232" t="s">
+        <v>43</v>
+      </c>
+      <c r="D232" t="s">
+        <v>49</v>
+      </c>
+      <c r="E232" t="s">
+        <v>67</v>
+      </c>
+      <c r="F232" t="s">
+        <v>95</v>
+      </c>
+      <c r="G232">
+        <v>308</v>
+      </c>
+      <c r="H232" s="2">
+        <v>46211.69054398148</v>
+      </c>
+      <c r="I232" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J232">
+        <v>2.077295089828365</v>
+      </c>
+      <c r="K232">
+        <v>2.077295089828365</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11">
+      <c r="A233" t="s">
+        <v>11</v>
+      </c>
+      <c r="B233" t="s">
+        <v>14</v>
+      </c>
+      <c r="C233" t="s">
+        <v>43</v>
+      </c>
+      <c r="D233" t="s">
+        <v>50</v>
+      </c>
+      <c r="E233" t="s">
+        <v>65</v>
+      </c>
+      <c r="F233" t="s">
+        <v>68</v>
+      </c>
+      <c r="G233">
+        <v>101</v>
+      </c>
+      <c r="H233" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I233" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J233">
+        <v>2.231945425056128</v>
+      </c>
+      <c r="K233">
+        <v>2.231945425056128</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11">
+      <c r="A234" t="s">
+        <v>11</v>
+      </c>
+      <c r="B234" t="s">
+        <v>14</v>
+      </c>
+      <c r="C234" t="s">
+        <v>43</v>
+      </c>
+      <c r="D234" t="s">
+        <v>50</v>
+      </c>
+      <c r="E234" t="s">
+        <v>66</v>
+      </c>
+      <c r="F234" t="s">
+        <v>86</v>
+      </c>
+      <c r="G234">
+        <v>201</v>
+      </c>
+      <c r="H234" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I234" s="2">
+        <v>46207.50067129629</v>
+      </c>
+      <c r="J234">
+        <v>2.095109041186042</v>
+      </c>
+      <c r="K234">
+        <v>2.095109041186042</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11">
+      <c r="A235" t="s">
+        <v>11</v>
+      </c>
+      <c r="B235" t="s">
+        <v>14</v>
+      </c>
+      <c r="C235" t="s">
+        <v>43</v>
+      </c>
+      <c r="D235" t="s">
+        <v>50</v>
+      </c>
+      <c r="E235" t="s">
+        <v>66</v>
+      </c>
+      <c r="F235" t="s">
+        <v>92</v>
+      </c>
+      <c r="G235">
+        <v>202</v>
+      </c>
+      <c r="H235" s="2">
+        <v>46211.69054398148</v>
+      </c>
+      <c r="I235" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J235">
+        <v>2.439675648934623</v>
+      </c>
+      <c r="K235">
+        <v>2.439675648934623</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11">
+      <c r="A236" t="s">
+        <v>11</v>
+      </c>
+      <c r="B236" t="s">
+        <v>14</v>
+      </c>
+      <c r="C236" t="s">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>50</v>
+      </c>
+      <c r="E236" t="s">
+        <v>67</v>
+      </c>
+      <c r="F236" t="s">
+        <v>90</v>
+      </c>
+      <c r="G236">
+        <v>304</v>
+      </c>
+      <c r="H236" s="2">
+        <v>46207.46722222222</v>
+      </c>
+      <c r="I236" s="2">
+        <v>46207.50067129629</v>
+      </c>
+      <c r="J236">
+        <v>2.095109041186042</v>
+      </c>
+      <c r="K236">
+        <v>2.095109041186042</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11">
+      <c r="A237" t="s">
+        <v>11</v>
+      </c>
+      <c r="B237" t="s">
+        <v>14</v>
+      </c>
+      <c r="C237" t="s">
+        <v>43</v>
+      </c>
+      <c r="D237" t="s">
+        <v>50</v>
+      </c>
+      <c r="E237" t="s">
+        <v>67</v>
+      </c>
+      <c r="F237" t="s">
+        <v>95</v>
+      </c>
+      <c r="G237">
+        <v>308</v>
+      </c>
+      <c r="H237" s="2">
+        <v>46211.69054398148</v>
+      </c>
+      <c r="I237" s="2">
+        <v>46211.70959490741</v>
+      </c>
+      <c r="J237">
+        <v>2.439675648934623</v>
+      </c>
+      <c r="K237">
+        <v>2.439675648934623</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11">
+      <c r="A238" t="s">
+        <v>11</v>
+      </c>
+      <c r="B238" t="s">
+        <v>14</v>
+      </c>
+      <c r="C238" t="s">
+        <v>44</v>
+      </c>
+      <c r="D238" t="s">
+        <v>51</v>
+      </c>
+      <c r="E238" t="s">
+        <v>65</v>
+      </c>
+      <c r="F238" t="s">
+        <v>68</v>
+      </c>
+      <c r="G238">
+        <v>101</v>
+      </c>
+      <c r="H238" s="2">
+        <v>46209.54386574074</v>
+      </c>
+      <c r="I238" s="2">
+        <v>46214.6469212963</v>
+      </c>
+      <c r="J238">
+        <v>4.481333785255094</v>
+      </c>
+      <c r="K238">
+        <v>4.481333785255094</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11">
+      <c r="A239" t="s">
+        <v>11</v>
+      </c>
+      <c r="B239" t="s">
+        <v>14</v>
+      </c>
+      <c r="C239" t="s">
+        <v>44</v>
+      </c>
+      <c r="D239" t="s">
+        <v>51</v>
+      </c>
+      <c r="E239" t="s">
+        <v>66</v>
+      </c>
+      <c r="F239" t="s">
+        <v>92</v>
+      </c>
+      <c r="G239">
+        <v>202</v>
+      </c>
+      <c r="H239" s="2">
+        <v>46209.54386574074</v>
+      </c>
+      <c r="I239" s="2">
+        <v>46214.6469212963</v>
+      </c>
+      <c r="J239">
+        <v>4.481333785255094</v>
+      </c>
+      <c r="K239">
+        <v>4.481333785255094</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11">
+      <c r="A240" t="s">
+        <v>11</v>
+      </c>
+      <c r="B240" t="s">
+        <v>14</v>
+      </c>
+      <c r="C240" t="s">
+        <v>44</v>
+      </c>
+      <c r="D240" t="s">
+        <v>51</v>
+      </c>
+      <c r="E240" t="s">
+        <v>67</v>
+      </c>
+      <c r="F240" t="s">
+        <v>93</v>
+      </c>
+      <c r="G240">
+        <v>306</v>
+      </c>
+      <c r="H240" s="2">
+        <v>46209.54386574074</v>
+      </c>
+      <c r="I240" s="2">
+        <v>46209.56375</v>
+      </c>
+      <c r="J240">
+        <v>4.85241903773101</v>
+      </c>
+      <c r="K240">
+        <v>4.85241903773101</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11">
+      <c r="A241" t="s">
+        <v>11</v>
+      </c>
+      <c r="B241" t="s">
+        <v>14</v>
+      </c>
+      <c r="C241" t="s">
+        <v>44</v>
+      </c>
+      <c r="D241" t="s">
+        <v>51</v>
+      </c>
+      <c r="E241" t="s">
+        <v>67</v>
+      </c>
+      <c r="F241" t="s">
+        <v>96</v>
+      </c>
+      <c r="G241">
+        <v>309</v>
+      </c>
+      <c r="H241" s="2">
+        <v>46212.04517361111</v>
+      </c>
+      <c r="I241" s="2">
+        <v>46212.06122685185</v>
+      </c>
+      <c r="J241">
+        <v>6.128563787472934</v>
+      </c>
+      <c r="K241">
+        <v>6.128563787472934</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11">
+      <c r="A242" t="s">
+        <v>11</v>
+      </c>
+      <c r="B242" t="s">
+        <v>14</v>
+      </c>
+      <c r="C242" t="s">
+        <v>44</v>
+      </c>
+      <c r="D242" t="s">
+        <v>51</v>
+      </c>
+      <c r="E242" t="s">
+        <v>67</v>
+      </c>
+      <c r="F242" t="s">
+        <v>97</v>
+      </c>
+      <c r="G242">
+        <v>310</v>
+      </c>
+      <c r="H242" s="2">
+        <v>46214.64324074074</v>
+      </c>
+      <c r="I242" s="2">
+        <v>46214.6469212963</v>
+      </c>
+      <c r="J242">
+        <v>6.26483090226033</v>
+      </c>
+      <c r="K242">
+        <v>6.26483090226033</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11">
+      <c r="A243" t="s">
+        <v>11</v>
+      </c>
+      <c r="B243" t="s">
+        <v>14</v>
+      </c>
+      <c r="C243" t="s">
+        <v>45</v>
+      </c>
+      <c r="D243" t="s">
+        <v>46</v>
+      </c>
+      <c r="E243" t="s">
+        <v>65</v>
+      </c>
+      <c r="F243" t="s">
+        <v>68</v>
+      </c>
+      <c r="G243">
+        <v>101</v>
+      </c>
+      <c r="H243" s="2">
+        <v>46209.94287037037</v>
+      </c>
+      <c r="I243" s="2">
+        <v>46212.06846064814</v>
+      </c>
+      <c r="J243">
+        <v>1.583345850457788</v>
+      </c>
+      <c r="K243">
+        <v>1.583345850457788</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11">
+      <c r="A244" t="s">
+        <v>11</v>
+      </c>
+      <c r="B244" t="s">
+        <v>14</v>
+      </c>
+      <c r="C244" t="s">
+        <v>45</v>
+      </c>
+      <c r="D244" t="s">
+        <v>46</v>
+      </c>
+      <c r="E244" t="s">
+        <v>66</v>
+      </c>
+      <c r="F244" t="s">
+        <v>92</v>
+      </c>
+      <c r="G244">
+        <v>202</v>
+      </c>
+      <c r="H244" s="2">
+        <v>46209.94287037037</v>
+      </c>
+      <c r="I244" s="2">
+        <v>46212.06846064814</v>
+      </c>
+      <c r="J244">
+        <v>1.583345850457788</v>
+      </c>
+      <c r="K244">
+        <v>1.583345850457788</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11">
+      <c r="A245" t="s">
+        <v>11</v>
+      </c>
+      <c r="B245" t="s">
+        <v>14</v>
+      </c>
+      <c r="C245" t="s">
+        <v>45</v>
+      </c>
+      <c r="D245" t="s">
+        <v>46</v>
+      </c>
+      <c r="E245" t="s">
+        <v>67</v>
+      </c>
+      <c r="F245" t="s">
+        <v>93</v>
+      </c>
+      <c r="G245">
+        <v>306</v>
+      </c>
+      <c r="H245" s="2">
+        <v>46209.94287037037</v>
+      </c>
+      <c r="I245" s="2">
+        <v>46209.95513888889</v>
+      </c>
+      <c r="J245">
+        <v>1.886380431790312</v>
+      </c>
+      <c r="K245">
+        <v>1.886380431790312</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11">
+      <c r="A246" t="s">
+        <v>11</v>
+      </c>
+      <c r="B246" t="s">
+        <v>14</v>
+      </c>
+      <c r="C246" t="s">
+        <v>45</v>
+      </c>
+      <c r="D246" t="s">
+        <v>46</v>
+      </c>
+      <c r="E246" t="s">
+        <v>67</v>
+      </c>
+      <c r="F246" t="s">
+        <v>96</v>
+      </c>
+      <c r="G246">
+        <v>309</v>
+      </c>
+      <c r="H246" s="2">
+        <v>46212.05592592592</v>
+      </c>
+      <c r="I246" s="2">
+        <v>46212.06846064814</v>
+      </c>
+      <c r="J246">
+        <v>1.611175198849116</v>
+      </c>
+      <c r="K246">
+        <v>1.611175198849116</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M626/spc_cpk_detail.xlsx
+++ b/resources/M626/spc_cpk_detail.xlsx
@@ -1375,10 +1375,10 @@
         <v>46227.67450231482</v>
       </c>
       <c r="J20">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
       <c r="K20">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1480,10 +1480,10 @@
         <v>46227.67450231482</v>
       </c>
       <c r="J23">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
       <c r="K23">
-        <v>2.610324736578182</v>
+        <v>2.610324736578181</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2950,10 +2950,10 @@
         <v>46234.05206018518</v>
       </c>
       <c r="J65">
-        <v>2.414612658349697</v>
+        <v>2.414612658349698</v>
       </c>
       <c r="K65">
-        <v>2.414612658349697</v>
+        <v>2.414612658349698</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3020,10 +3020,10 @@
         <v>46234.05206018518</v>
       </c>
       <c r="J67">
-        <v>2.414612658349697</v>
+        <v>2.414612658349698</v>
       </c>
       <c r="K67">
-        <v>2.414612658349697</v>
+        <v>2.414612658349698</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3090,10 +3090,10 @@
         <v>46234.05206018518</v>
       </c>
       <c r="J69">
-        <v>2.414612658349697</v>
+        <v>2.414612658349698</v>
       </c>
       <c r="K69">
-        <v>2.414612658349697</v>
+        <v>2.414612658349698</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3650,10 +3650,10 @@
         <v>46236.78883101852</v>
       </c>
       <c r="J85">
-        <v>1.508683391254824</v>
+        <v>1.508683391254823</v>
       </c>
       <c r="K85">
-        <v>1.508683391254824</v>
+        <v>1.508683391254823</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4875,10 +4875,10 @@
         <v>46239.94284722222</v>
       </c>
       <c r="J120">
-        <v>1.924317845875284</v>
+        <v>1.924317845875285</v>
       </c>
       <c r="K120">
-        <v>1.924317845875284</v>
+        <v>1.924317845875285</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -4945,10 +4945,10 @@
         <v>46239.94284722222</v>
       </c>
       <c r="J122">
-        <v>1.924317845875284</v>
+        <v>1.924317845875285</v>
       </c>
       <c r="K122">
-        <v>1.924317845875284</v>
+        <v>1.924317845875285</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -5785,10 +5785,10 @@
         <v>46237.40302083334</v>
       </c>
       <c r="J146">
-        <v>1.699841446416682</v>
+        <v>1.699841446416683</v>
       </c>
       <c r="K146">
-        <v>1.699841446416682</v>
+        <v>1.699841446416683</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -6520,10 +6520,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J167">
-        <v>2.492949601255396</v>
+        <v>2.492949601255395</v>
       </c>
       <c r="K167">
-        <v>2.492949601255396</v>
+        <v>2.492949601255395</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -7045,10 +7045,10 @@
         <v>46204.48143518518</v>
       </c>
       <c r="J182">
-        <v>5.266814649998151</v>
+        <v>5.266814649998149</v>
       </c>
       <c r="K182">
-        <v>5.266814649998151</v>
+        <v>5.266814649998149</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -7325,10 +7325,10 @@
         <v>46206.6680324074</v>
       </c>
       <c r="J190">
-        <v>6.868403886344061</v>
+        <v>6.868403886344059</v>
       </c>
       <c r="K190">
-        <v>6.868403886344061</v>
+        <v>6.868403886344059</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -7815,10 +7815,10 @@
         <v>46207.33239583333</v>
       </c>
       <c r="J204">
-        <v>3.09010363110375</v>
+        <v>3.090103631103751</v>
       </c>
       <c r="K204">
-        <v>3.09010363110375</v>
+        <v>3.090103631103751</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -7850,10 +7850,10 @@
         <v>46207.33239583333</v>
       </c>
       <c r="J205">
-        <v>3.09010363110375</v>
+        <v>3.090103631103751</v>
       </c>
       <c r="K205">
-        <v>3.09010363110375</v>
+        <v>3.090103631103751</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -7920,10 +7920,10 @@
         <v>46205.74839120371</v>
       </c>
       <c r="J207">
-        <v>3.205586147890944</v>
+        <v>3.205586147890943</v>
       </c>
       <c r="K207">
-        <v>3.205586147890944</v>
+        <v>3.205586147890943</v>
       </c>
     </row>
     <row r="208" spans="1:11">

--- a/resources/M626/spc_cpk_detail.xlsx
+++ b/resources/M626/spc_cpk_detail.xlsx
@@ -775,10 +775,10 @@
         <v>46230.72840277778</v>
       </c>
       <c r="J2">
-        <v>1.783316479126941</v>
+        <v>1.783316479126942</v>
       </c>
       <c r="K2">
-        <v>1.783316479126941</v>
+        <v>1.783316479126942</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1090,10 +1090,10 @@
         <v>46238.89697916667</v>
       </c>
       <c r="J11">
-        <v>1.142303932752752</v>
+        <v>1.142303932752751</v>
       </c>
       <c r="K11">
-        <v>1.142303932752752</v>
+        <v>1.142303932752751</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1195,10 +1195,10 @@
         <v>46238.89697916667</v>
       </c>
       <c r="J14">
-        <v>1.142303932752752</v>
+        <v>1.142303932752751</v>
       </c>
       <c r="K14">
-        <v>1.142303932752752</v>
+        <v>1.142303932752751</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1300,10 +1300,10 @@
         <v>46238.89697916667</v>
       </c>
       <c r="J17">
-        <v>1.142303932752752</v>
+        <v>1.142303932752751</v>
       </c>
       <c r="K17">
-        <v>1.142303932752752</v>
+        <v>1.142303932752751</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1650,10 +1650,10 @@
         <v>46239.94694444445</v>
       </c>
       <c r="J27">
-        <v>2.567108211495931</v>
+        <v>2.567108211495932</v>
       </c>
       <c r="K27">
-        <v>2.567108211495931</v>
+        <v>2.567108211495932</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2070,10 +2070,10 @@
         <v>46230.99207175926</v>
       </c>
       <c r="J39">
-        <v>2.066936758739829</v>
+        <v>2.066936758739828</v>
       </c>
       <c r="K39">
-        <v>2.066936758739829</v>
+        <v>2.066936758739828</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2595,10 +2595,10 @@
         <v>46240.07295138889</v>
       </c>
       <c r="J54">
-        <v>1.788942081069504</v>
+        <v>1.788942081069503</v>
       </c>
       <c r="K54">
-        <v>1.788942081069504</v>
+        <v>1.788942081069503</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2665,10 +2665,10 @@
         <v>46240.07295138889</v>
       </c>
       <c r="J56">
-        <v>1.788942081069504</v>
+        <v>1.788942081069503</v>
       </c>
       <c r="K56">
-        <v>1.788942081069504</v>
+        <v>1.788942081069503</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2735,10 +2735,10 @@
         <v>46240.07295138889</v>
       </c>
       <c r="J58">
-        <v>1.788942081069504</v>
+        <v>1.788942081069503</v>
       </c>
       <c r="K58">
-        <v>1.788942081069504</v>
+        <v>1.788942081069503</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2980,10 +2980,10 @@
         <v>46240.72226851852</v>
       </c>
       <c r="J65">
-        <v>2.891429183460564</v>
+        <v>2.891429183460563</v>
       </c>
       <c r="K65">
-        <v>2.891429183460564</v>
+        <v>2.891429183460563</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3505,10 +3505,10 @@
         <v>46233.92318287037</v>
       </c>
       <c r="J80">
-        <v>1.213053007796703</v>
+        <v>1.299305092733524</v>
       </c>
       <c r="K80">
-        <v>1.213053007796703</v>
+        <v>1.299305092733524</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3540,10 +3540,10 @@
         <v>46241.44989583334</v>
       </c>
       <c r="J81">
-        <v>1.332850779869144</v>
+        <v>1.433809347294185</v>
       </c>
       <c r="K81">
-        <v>1.332850779869144</v>
+        <v>1.433809347294185</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3575,10 +3575,10 @@
         <v>46233.92318287037</v>
       </c>
       <c r="J82">
-        <v>1.213053007796703</v>
+        <v>1.299305092733524</v>
       </c>
       <c r="K82">
-        <v>1.213053007796703</v>
+        <v>1.299305092733524</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3610,10 +3610,10 @@
         <v>46241.44989583334</v>
       </c>
       <c r="J83">
-        <v>1.332850779869144</v>
+        <v>1.433809347294185</v>
       </c>
       <c r="K83">
-        <v>1.332850779869144</v>
+        <v>1.433809347294185</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3645,10 +3645,10 @@
         <v>46233.92318287037</v>
       </c>
       <c r="J84">
-        <v>1.213053007796703</v>
+        <v>1.299305092733524</v>
       </c>
       <c r="K84">
-        <v>1.213053007796703</v>
+        <v>1.299305092733524</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3680,10 +3680,10 @@
         <v>46241.44989583334</v>
       </c>
       <c r="J85">
-        <v>1.332850779869144</v>
+        <v>1.433809347294185</v>
       </c>
       <c r="K85">
-        <v>1.332850779869144</v>
+        <v>1.433809347294185</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4205,10 +4205,10 @@
         <v>46238.68879629629</v>
       </c>
       <c r="J100">
-        <v>2.905559116600224</v>
+        <v>2.905559116600223</v>
       </c>
       <c r="K100">
-        <v>2.905559116600224</v>
+        <v>2.905559116600223</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -4345,10 +4345,10 @@
         <v>46238.74305555555</v>
       </c>
       <c r="J104">
-        <v>2.853604283911436</v>
+        <v>2.853604283911435</v>
       </c>
       <c r="K104">
-        <v>2.853604283911436</v>
+        <v>2.853604283911435</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4555,10 +4555,10 @@
         <v>46242.52304398148</v>
       </c>
       <c r="J110">
-        <v>1.275138537961697</v>
+        <v>1.451262023593705</v>
       </c>
       <c r="K110">
-        <v>1.275138537961697</v>
+        <v>1.451262023593705</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4590,10 +4590,10 @@
         <v>46242.52304398148</v>
       </c>
       <c r="J111">
-        <v>1.275138537961697</v>
+        <v>1.451262023593705</v>
       </c>
       <c r="K111">
-        <v>1.275138537961697</v>
+        <v>1.451262023593705</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4625,10 +4625,10 @@
         <v>46238.74305555555</v>
       </c>
       <c r="J112">
-        <v>1.199874216297309</v>
+        <v>1.358568807624723</v>
       </c>
       <c r="K112">
-        <v>1.199874216297309</v>
+        <v>1.358568807624723</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -4660,10 +4660,10 @@
         <v>46242.52304398148</v>
       </c>
       <c r="J113">
-        <v>1.337787016703079</v>
+        <v>1.490845501850582</v>
       </c>
       <c r="K113">
-        <v>1.337787016703079</v>
+        <v>1.490845501850582</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -4905,10 +4905,10 @@
         <v>46237.2683912037</v>
       </c>
       <c r="J120">
-        <v>1.683802188892684</v>
+        <v>1.683802188892685</v>
       </c>
       <c r="K120">
-        <v>1.683802188892684</v>
+        <v>1.683802188892685</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -4940,10 +4940,10 @@
         <v>46240.58334490741</v>
       </c>
       <c r="J121">
-        <v>1.476682718879129</v>
+        <v>1.476682718879128</v>
       </c>
       <c r="K121">
-        <v>1.476682718879129</v>
+        <v>1.476682718879128</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -5360,10 +5360,10 @@
         <v>46240.66833333333</v>
       </c>
       <c r="J133">
-        <v>1.895099538835158</v>
+        <v>1.895099538835159</v>
       </c>
       <c r="K133">
-        <v>1.895099538835158</v>
+        <v>1.895099538835159</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -5395,10 +5395,10 @@
         <v>46242.51028935185</v>
       </c>
       <c r="J134">
-        <v>1.232890123162044</v>
+        <v>1.232890123162045</v>
       </c>
       <c r="K134">
-        <v>1.232890123162044</v>
+        <v>1.232890123162045</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -5885,10 +5885,10 @@
         <v>46243.8480787037</v>
       </c>
       <c r="J148">
-        <v>1.250385759207341</v>
+        <v>1.362323444544703</v>
       </c>
       <c r="K148">
-        <v>1.250385759207341</v>
+        <v>1.362323444544703</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -5920,10 +5920,10 @@
         <v>46243.8480787037</v>
       </c>
       <c r="J149">
-        <v>1.250385759207341</v>
+        <v>1.362323444544703</v>
       </c>
       <c r="K149">
-        <v>1.250385759207341</v>
+        <v>1.362323444544703</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -5955,10 +5955,10 @@
         <v>46243.8480787037</v>
       </c>
       <c r="J150">
-        <v>1.250385759207341</v>
+        <v>1.362323444544703</v>
       </c>
       <c r="K150">
-        <v>1.250385759207341</v>
+        <v>1.362323444544703</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -7530,10 +7530,10 @@
         <v>46237.40302083334</v>
       </c>
       <c r="J195">
-        <v>1.699841446416683</v>
+        <v>1.699841446416682</v>
       </c>
       <c r="K195">
-        <v>1.699841446416683</v>
+        <v>1.699841446416682</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -8195,10 +8195,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J214">
-        <v>1.978853450574099</v>
+        <v>1.978853450574098</v>
       </c>
       <c r="K214">
-        <v>1.978853450574099</v>
+        <v>1.978853450574098</v>
       </c>
     </row>
     <row r="215" spans="1:11">
@@ -8230,10 +8230,10 @@
         <v>46207.44892361111</v>
       </c>
       <c r="J215">
-        <v>1.978853450574099</v>
+        <v>1.978853450574098</v>
       </c>
       <c r="K215">
-        <v>1.978853450574099</v>
+        <v>1.978853450574098</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -8720,10 +8720,10 @@
         <v>46205.77965277778</v>
       </c>
       <c r="J229">
-        <v>2.013994314162455</v>
+        <v>2.013994314162456</v>
       </c>
       <c r="K229">
-        <v>2.013994314162455</v>
+        <v>2.013994314162456</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -8895,10 +8895,10 @@
         <v>46204.48143518518</v>
       </c>
       <c r="J234">
-        <v>5.266814649998149</v>
+        <v>5.26681464999815</v>
       </c>
       <c r="K234">
-        <v>5.266814649998149</v>
+        <v>5.26681464999815</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -9560,10 +9560,10 @@
         <v>46205.74839120371</v>
       </c>
       <c r="J253">
-        <v>5.850465480446285</v>
+        <v>5.850465480446287</v>
       </c>
       <c r="K253">
-        <v>5.850465480446285</v>
+        <v>5.850465480446287</v>
       </c>
     </row>
     <row r="254" spans="1:11">
@@ -9805,10 +9805,10 @@
         <v>46206.66802083333</v>
       </c>
       <c r="J260">
-        <v>3.078750218465228</v>
+        <v>3.078750218465227</v>
       </c>
       <c r="K260">
-        <v>3.078750218465228</v>
+        <v>3.078750218465227</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -10505,10 +10505,10 @@
         <v>46207.23274305555</v>
       </c>
       <c r="J280">
-        <v>1.990153757485192</v>
+        <v>1.990153757485191</v>
       </c>
       <c r="K280">
-        <v>1.990153757485192</v>
+        <v>1.990153757485191</v>
       </c>
     </row>
     <row r="281" spans="1:11">
@@ -10540,10 +10540,10 @@
         <v>46207.23274305555</v>
       </c>
       <c r="J281">
-        <v>1.990153757485192</v>
+        <v>1.990153757485191</v>
       </c>
       <c r="K281">
-        <v>1.990153757485192</v>
+        <v>1.990153757485191</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -10575,10 +10575,10 @@
         <v>46207.23274305555</v>
       </c>
       <c r="J282">
-        <v>1.990153757485192</v>
+        <v>1.990153757485191</v>
       </c>
       <c r="K282">
-        <v>1.990153757485192</v>
+        <v>1.990153757485191</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -11695,10 +11695,10 @@
         <v>46209.56375</v>
       </c>
       <c r="J314">
-        <v>4.852419037731009</v>
+        <v>4.85241903773101</v>
       </c>
       <c r="K314">
-        <v>4.852419037731009</v>
+        <v>4.85241903773101</v>
       </c>
     </row>
     <row r="315" spans="1:11">
@@ -11870,10 +11870,10 @@
         <v>46209.95513888889</v>
       </c>
       <c r="J319">
-        <v>1.886380431790312</v>
+        <v>1.886380431790313</v>
       </c>
       <c r="K319">
-        <v>1.886380431790312</v>
+        <v>1.886380431790313</v>
       </c>
     </row>
     <row r="320" spans="1:11">
